--- a/tests/workbooks/test_bonds.xlsx
+++ b/tests/workbooks/test_bonds.xlsx
@@ -8,23 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6695F9E2-73C9-4290-88B1-F38E45AEE320}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804525A8-9446-4835-9374-D51F9E284B26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="32370" windowHeight="9360" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabs" sheetId="1" r:id="rId1"/>
-    <sheet name="Bond" sheetId="3" r:id="rId2"/>
-    <sheet name="ZeroCouponBond" sheetId="4" r:id="rId3"/>
-    <sheet name="FixedRateBond" sheetId="5" r:id="rId4"/>
-    <sheet name="AmortizingFixedRateBond" sheetId="6" r:id="rId5"/>
-    <sheet name="AmortizingFloatingRateBond" sheetId="7" r:id="rId6"/>
-    <sheet name="FloatingRateBond" sheetId="8" r:id="rId7"/>
-    <sheet name="CmsRateBond" sheetId="9" r:id="rId8"/>
-    <sheet name="AmortizingCmsRateBond" sheetId="10" r:id="rId9"/>
-    <sheet name="CallableFixedRateBond" sheetId="13" r:id="rId10"/>
-    <sheet name="CallableZeroCouponBond" sheetId="14" r:id="rId11"/>
-    <sheet name="CPIBond" sheetId="17" r:id="rId12"/>
+    <sheet name="BondPrice" sheetId="18" r:id="rId2"/>
+    <sheet name="Bond" sheetId="3" r:id="rId3"/>
+    <sheet name="ZeroCouponBond" sheetId="4" r:id="rId4"/>
+    <sheet name="FixedRateBond" sheetId="5" r:id="rId5"/>
+    <sheet name="AmortizingFixedRateBond" sheetId="6" r:id="rId6"/>
+    <sheet name="AmortizingFloatingRateBond" sheetId="7" r:id="rId7"/>
+    <sheet name="FloatingRateBond" sheetId="8" r:id="rId8"/>
+    <sheet name="CmsRateBond" sheetId="9" r:id="rId9"/>
+    <sheet name="AmortizingCmsRateBond" sheetId="10" r:id="rId10"/>
+    <sheet name="Callability" sheetId="21" r:id="rId11"/>
+    <sheet name="CallableFixedRateBond" sheetId="13" r:id="rId12"/>
+    <sheet name="CallableZeroCouponBond" sheetId="14" r:id="rId13"/>
+    <sheet name="CPIBond" sheetId="17" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="135">
   <si>
     <t>Bond</t>
   </si>
@@ -390,6 +392,57 @@
   </si>
   <si>
     <t>BlackCallableFixedRateBondEngine</t>
+  </si>
+  <si>
+    <t>BondPrice</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>clean</t>
+  </si>
+  <si>
+    <t>qlBondPrice</t>
+  </si>
+  <si>
+    <t>qlBondPriceAmount</t>
+  </si>
+  <si>
+    <t>qlBondPriceType</t>
+  </si>
+  <si>
+    <t>qlBondPriceIsValid</t>
+  </si>
+  <si>
+    <t>Callability</t>
+  </si>
+  <si>
+    <t>price (qlBondPrice)</t>
+  </si>
+  <si>
+    <t>callability_type</t>
+  </si>
+  <si>
+    <t>put</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>qlCallability</t>
+  </si>
+  <si>
+    <t>qlCallabilityPrice</t>
+  </si>
+  <si>
+    <t>qlCallabilityDate</t>
+  </si>
+  <si>
+    <t>qlCallabilityType</t>
   </si>
 </sst>
 </file>
@@ -451,7 +504,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -554,11 +607,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -605,6 +671,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -614,9 +686,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -931,7 +1000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F1B31AC-6B78-4845-B599-86FA814CB2D7}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="16"/>
@@ -946,11 +1015,11 @@
       <c r="B2" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="27"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="33"/>
     </row>
     <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="18"/>
@@ -965,18 +1034,16 @@
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" s="22"/>
-      <c r="E4" s="23"/>
+      <c r="B4" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>114</v>
@@ -986,7 +1053,7 @@
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>114</v>
@@ -996,7 +1063,7 @@
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="22" t="s">
         <v>114</v>
@@ -1006,7 +1073,7 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>114</v>
@@ -1016,7 +1083,7 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" s="22" t="s">
         <v>114</v>
@@ -1026,7 +1093,7 @@
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="22" t="s">
         <v>114</v>
@@ -1035,8 +1102,8 @@
       <c r="E10" s="23"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="31" t="s">
-        <v>7</v>
+      <c r="B11" s="21" t="s">
+        <v>6</v>
       </c>
       <c r="C11" s="22" t="s">
         <v>114</v>
@@ -1045,28 +1112,46 @@
       <c r="E11" s="23"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="22"/>
+      <c r="B12" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>114</v>
+      </c>
       <c r="D12" s="22"/>
       <c r="E12" s="23"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="29" t="s">
-        <v>9</v>
+      <c r="B13" s="28" t="s">
+        <v>126</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="22"/>
       <c r="E13" s="23"/>
     </row>
-    <row r="14" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="30" t="s">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="23"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="23"/>
+    </row>
+    <row r="16" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="25"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1078,6 +1163,929 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28ABD84F-1436-4AE1-BC17-091C65B56114}">
+  <dimension ref="A1:C67"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="48.5703125" customWidth="1"/>
+    <col min="2" max="2" width="69.140625" customWidth="1"/>
+    <col min="3" max="3" width="71.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2">
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="3">
+        <v>103</v>
+      </c>
+      <c r="C5" s="3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="34"/>
+      <c r="B6" s="3">
+        <v>102</v>
+      </c>
+      <c r="C6" s="3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="34"/>
+      <c r="B7" s="3">
+        <v>101</v>
+      </c>
+      <c r="C7" s="3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="12">
+        <v>45665</v>
+      </c>
+      <c r="C8" s="12">
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="12">
+        <v>46030</v>
+      </c>
+      <c r="C9" s="12">
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="6" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C11" s="6" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="6">
+        <v>0</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="3" t="str">
+        <f>_xll.qlSchedule(B8,B9,B10,B11,B12,B13,B14,B15)</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R16C2Schedule,A</v>
+      </c>
+      <c r="C16" s="3" t="str">
+        <f>_xll.qlSchedule(C8,C9,C10,C11,C12,C13,C14,C15)</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R16C3Schedule,A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="6">
+        <v>2</v>
+      </c>
+      <c r="C19" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="6" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C21" s="6" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="6" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R25C2Euribor,A</v>
+      </c>
+      <c r="C25" s="6" t="str">
+        <f>_xll.qlEuribor("3M")</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R25C3Euribor,A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="6" t="str">
+        <f>_xll.qlFlatForward(#REF!,0.03,"Actual360","Compounded","Quarterly")</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R26C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C26" s="6" t="str">
+        <f>_xll.qlFlatForward(#REF!,0.03,"Actual360","Compounded","Quarterly")</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R26C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="3" t="str">
+        <f>_xll.qlSwapIndex(B17,B18,B19,B20,B21,B22,B23,B24,B25,B26)</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R27C2SwapIndex,A</v>
+      </c>
+      <c r="C27" s="3" t="str">
+        <f>_xll.qlSwapIndex(C17,C18,C19,C20,C21,C22,C23,C24,C25,C26)</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R27C3SwapIndex,A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="2">
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" t="str">
+        <f>_xll.qlAmortizingCmsRateBond(B4,B5:B7,B16,B27,B28)</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R37C2AmortizingCmsRateBond,A</v>
+      </c>
+      <c r="C37" t="str">
+        <f>_xll.qlAmortizingCmsRateBond(C4,C5:C7,C16,C27,C28,C29,C30,C31,C32,C33,C34,C35,C36)</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R37C3AmortizingCmsRateBond,A</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="3">
+        <f>_xll.qlBondNextCouponRate(B37)</f>
+        <v>0</v>
+      </c>
+      <c r="C38" s="3">
+        <f>_xll.qlBondNextCouponRate(C37)</f>
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="3">
+        <f>_xll.qlBondPreviousCouponRate(B37)</f>
+        <v>0</v>
+      </c>
+      <c r="C39" s="3">
+        <f>_xll.qlBondPreviousCouponRate(C37)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" s="2">
+        <f>_xll.qlBondNextCashFlowDate(B37)</f>
+        <v>45755</v>
+      </c>
+      <c r="C40" s="2">
+        <f>_xll.qlBondNextCashFlowDate(C37)</f>
+        <v>45755</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" s="2">
+        <f>_xll.qlBondPreviousCashFlowDate(B37)</f>
+        <v>0</v>
+      </c>
+      <c r="C41" s="2">
+        <f>_xll.qlBondPreviousCashFlowDate(C37)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" s="3">
+        <f>_xll.qlBondSettlementDays(B37)</f>
+        <v>2</v>
+      </c>
+      <c r="C42" s="3">
+        <f>_xll.qlBondSettlementDays(C37)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" s="2">
+        <f>_xll.qlBondSettlementDate(B37)</f>
+        <v>45667</v>
+      </c>
+      <c r="C43" s="2">
+        <f>_xll.qlBondSettlementDate(C37)</f>
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B44" s="3" t="b">
+        <f>_xll.qlBondIsTradable(B37)</f>
+        <v>1</v>
+      </c>
+      <c r="C44" s="3" t="b">
+        <f>_xll.qlBondIsTradable(C37)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B45" s="2">
+        <f>_xll.qlBondStartDate(B37)</f>
+        <v>45665</v>
+      </c>
+      <c r="C45" s="2">
+        <f>_xll.qlBondStartDate(C37)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" s="2">
+        <f>_xll.qlBondMaturityDate(B37)</f>
+        <v>46030</v>
+      </c>
+      <c r="C46" s="2">
+        <f>_xll.qlBondMaturityDate(C37)</f>
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B47" s="3">
+        <f>_xll.qlBondIssueDate(B37)</f>
+        <v>0</v>
+      </c>
+      <c r="C47" s="3">
+        <f>_xll.qlBondIssueDate(C37)</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B48" s="3" t="str">
+        <f>_xll.qlBondCashFlows(B37)</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R48C2CashFlow,A</v>
+      </c>
+      <c r="C48" s="3" t="str">
+        <f>_xll.qlBondCashFlows(C37)</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R48C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" s="3" t="str">
+        <f>_xll.qlBondRedemption(B37)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 326, in qlBondRedemption
+    return bond.redemption()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
+    return _QuantLib.Bond_redemption(self)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
+RuntimeError: multiple redemption cash flows given
+</v>
+      </c>
+      <c r="C49" s="3" t="str">
+        <f>_xll.qlBondRedemption(C37)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 326, in qlBondRedemption
+    return bond.redemption()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
+    return _QuantLib.Bond_redemption(self)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
+RuntimeError: multiple redemption cash flows given
+</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="3" t="str">
+        <f>_xll.qlBondRedemptions(B37)</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R50C2CashFlow,A</v>
+      </c>
+      <c r="C50" s="3" t="str">
+        <f>_xll.qlBondRedemptions(C37)</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R50C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B51" s="3" t="str">
+        <f>_xll.qlBondCalendar(B37)</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C51" s="3" t="str">
+        <f>_xll.qlBondCalendar(C37)</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B52" s="3">
+        <f>_xll.qlBondNotional(B37)</f>
+        <v>103</v>
+      </c>
+      <c r="C52" s="3">
+        <f>_xll.qlBondNotional(C37)</f>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="3">
+        <f>_xll.qlBondNotionals(B37)</f>
+        <v>103</v>
+      </c>
+      <c r="C53" s="3">
+        <f>_xll.qlBondNotionals(C37)</f>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="3" t="str">
+        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R54C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C54" s="3" t="str">
+        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R54C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B55" s="3" t="str">
+        <f>_xll.qlBondSetDiscountingEngine(B37,B54)</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R55C2DiscountingBondEngine,A</v>
+      </c>
+      <c r="C55" s="3" t="str">
+        <f>_xll.qlBondSetDiscountingEngine(C37,C54)</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R55C3DiscountingBondEngine,A</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B56" s="10">
+        <f>_xll.qlBondCleanPrice(B37)</f>
+        <v>74.994672295319077</v>
+      </c>
+      <c r="C56" s="10">
+        <f>_xll.qlBondCleanPrice(C37)</f>
+        <v>75.244545975491022</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="10">
+        <v>0.28928264971926221</v>
+      </c>
+      <c r="C57" s="10">
+        <v>0.28928264971926221</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B58" s="10">
+        <f>_xll.qlBondCleanPrice2(B37,B57,"actual360","continuous")</f>
+        <v>74.994672041966595</v>
+      </c>
+      <c r="C58" s="10">
+        <f>_xll.qlBondCleanPrice2(C37,C57,"actual360","continuous")</f>
+        <v>75.244545721623112</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B59" s="10">
+        <f>_xll.qlBondDirtyPrice(B37)</f>
+        <v>74.994672295319077</v>
+      </c>
+      <c r="C59" s="10">
+        <f>_xll.qlBondDirtyPrice(C37)</f>
+        <v>75.246212642157701</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" s="10">
+        <f>_xll.qlBondDirtyPrice2(B37,B57,"actual360","CONTINUOUS","annual")</f>
+        <v>74.994672041966595</v>
+      </c>
+      <c r="C60" s="10">
+        <f>_xll.qlBondDirtyPrice2(C37,C57,"actual360","CONTINUOUS","annual")</f>
+        <v>75.246212388289791</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="10" t="str">
+        <f>_xll.qlBondYield(B37,"actual360","CONTINUOUS","annual")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondYield
+    return bond.bondYield(
+           ~~~~~~~~~~~~~~^
+        dc,
+        ^^^
+    ...&lt;3 lines&gt;...
+        max_evaluations
+        ^^^^^^^^^^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+      <c r="C61" s="10">
+        <f>_xll.qlBondYield(C37,"actual360","CONTINUOUS","annual")</f>
+        <v>0.28928264793774228</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B62" s="10" t="str">
+        <f>_xll.qlBondPrice(B56,"clean")</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R62C2BondPrice,A</v>
+      </c>
+      <c r="C62" s="10" t="str">
+        <f>_xll.qlBondPrice(C56,"clean")</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R62C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" s="10">
+        <f>_xll.qlBondYield2(B37,B62,"actual360","CONTINUOUS","annual")</f>
+        <v>0.28928264826921379</v>
+      </c>
+      <c r="C63" s="10">
+        <f>_xll.qlBondYield2(C37,C62,"actual360","CONTINUOUS","annual")</f>
+        <v>0.28930497525756377</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B64" s="2">
+        <v>45667</v>
+      </c>
+      <c r="C64" s="2">
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="10">
+        <f>_xll.qlBondAccruedAmount(B37,B64)</f>
+        <v>0</v>
+      </c>
+      <c r="C65" s="10">
+        <f>_xll.qlBondAccruedAmount(C37,C64)</f>
+        <v>1.6666666666775853E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="10" t="str">
+        <f>_xll.qlBondSettlementValue(B37)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+      <c r="C66" s="10" t="str">
+        <f>_xll.qlBondSettlementValue(C37)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="10">
+        <f>_xll.qlBondSettlementValue2(B37,B56)</f>
+        <v>77.244512464178655</v>
+      </c>
+      <c r="C67" s="10">
+        <f>_xll.qlBondSettlementValue2(C37,C56)</f>
+        <v>77.503599021422431</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:A7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F09BC366-53EA-43EA-8BCB-0489C1B271E0}">
+  <dimension ref="A3:B12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="45.42578125" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" t="str">
+        <f>_xll.qlBondPrice(100,"clean")</f>
+        <v>欣[test_bonds.xlsx]Callability!R3C2BondPrice,A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="9">
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" t="str">
+        <f>_xll.qlCallability(B3,B4,B5)</f>
+        <v>欣[test_bonds.xlsx]Callability!R6C2Callability,A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" t="str">
+        <f>_xll.qlCallabilityPrice(B6)</f>
+        <v>欣[test_bonds.xlsx]Callability!R7C2BondPrice,A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="9">
+        <f>_xll.qlCallabilityDate(B6)</f>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" t="str">
+        <f>_xll.qlCallabilityType(B6)</f>
+        <v>PUT</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F0A1FE9-B1FE-4762-AEA9-E4B3F6C519F7}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1086,7 +2094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4EF9C2-FD4D-4E7F-8154-C8E782972C6B}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1095,7 +2103,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCE8D14D-DD7E-4024-86F3-1C5FBF784E5F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1105,8 +2113,75 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44B77307-DD7A-406E-AD93-A17357F921C0}">
+  <dimension ref="A3:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.5703125" customWidth="1"/>
+    <col min="2" max="2" width="46" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="3" t="str">
+        <f>_xll.qlBondPrice(B3,B4)</f>
+        <v>欣[test_bonds.xlsx]BondPrice!R5C2BondPrice,A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="3">
+        <f>_xll.qlBondPriceAmount(B5)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="3" t="str">
+        <f>_xll.qlBondPriceType(B5)</f>
+        <v>CLEAN</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <f>_xll.qlBondPriceIsValid(B5)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8683113-FD1C-4D88-8D42-F7763B404E4F}">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -1615,9 +2690,18 @@
       <c r="A47" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="10" t="str">
         <f>_xll.qlBondDirtyPrice(B25)</f>
-        <v>2.3346336353520432</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 418, in qlBondDirtyPrice
+    return bond.dirtyPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
+    return _QuantLib.Bond_dirtyPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
       <c r="C47" s="10">
         <f>_xll.qlBondDirtyPrice(C25)</f>
@@ -1651,64 +2735,86 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B50" s="10" t="str">
+        <f>_xll.qlBondPrice(B44,"clean")</f>
+        <v>欣[test_bonds.xlsx]Bond!R50C2BondPrice,A</v>
+      </c>
+      <c r="C50" s="10" t="str">
+        <f>_xll.qlBondPrice(C44,"clean")</f>
+        <v>欣[test_bonds.xlsx]Bond!R50C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="10">
-        <f>_xll.qlBondYield2(B25,B47,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426559332721</v>
-      </c>
-      <c r="C50" s="10">
-        <f>_xll.qlBondYield2(C25,C47,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426559332721</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
+      <c r="B51" s="10">
+        <f>_xll.qlBondYield2(B25,B50,"actual360","CONTINUOUS","annual")</f>
+        <v>0.26946953931176648</v>
+      </c>
+      <c r="C51" s="10">
+        <f>_xll.qlBondYield2(C25,C50,"actual360","CONTINUOUS","annual")</f>
+        <v>0.26946953931176648</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B52" s="2">
         <v>45667</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C52" s="2">
         <v>45667</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="10">
-        <f>_xll.qlBondAccruedAmount(B25,B51)</f>
-        <v>1.6666666666664831E-2</v>
-      </c>
-      <c r="C52" s="10">
-        <f>_xll.qlBondAccruedAmount(C25,C51)</f>
-        <v>1.6666666666664831E-2</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="10">
+        <f>_xll.qlBondAccruedAmount(B25,B52)</f>
+        <v>1.6666666666664831E-2</v>
+      </c>
+      <c r="C53" s="10">
+        <f>_xll.qlBondAccruedAmount(C25,C52)</f>
+        <v>1.6666666666664831E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B54" s="10" t="str">
         <f>_xll.qlBondSettlementValue(B25)</f>
-        <v>2.3346336353520432</v>
-      </c>
-      <c r="C53" s="10">
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+      <c r="C54" s="10">
         <f>_xll.qlBondSettlementValue(C25)</f>
         <v>2.3346336353520432</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B55" s="10">
         <f>_xll.qlBondSettlementValue2(B25,B44)</f>
         <v>2.3346336353520432</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C55" s="10">
         <f>_xll.qlBondSettlementValue2(C25,C44)</f>
         <v>2.3346336353520432</v>
       </c>
@@ -1719,13 +2825,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA0BDDB4-6035-4089-86B1-6246F3228CBC}">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
-    <col min="2" max="2" width="60" style="3" customWidth="1"/>
+    <col min="2" max="2" width="88.7109375" style="3" customWidth="1"/>
     <col min="3" max="3" width="59.28515625" style="3" customWidth="1"/>
     <col min="4" max="7" width="11.42578125" style="3"/>
   </cols>
@@ -1838,7 +2944,7 @@
         <f>_xll.qlBondNextCouponRate(B11)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2026
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 203, in qlBondNextCouponRate
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 209, in qlBondNextCouponRate
     return bond.nextCouponRate(date)
            ~~~~~~~~~~~~~~~~~~~^^^^^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
@@ -1851,7 +2957,7 @@
         <f>_xll.qlBondNextCouponRate(C11)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2026
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 203, in qlBondNextCouponRate
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 209, in qlBondNextCouponRate
     return bond.nextCouponRate(date)
            ~~~~~~~~~~~~~~~~~~~^^^^^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
@@ -2127,9 +3233,18 @@
         <f>_xll.qlBondDirtyPrice(B11)</f>
         <v>76.755078422532549</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="10" t="str">
         <f>_xll.qlBondDirtyPrice(C11)</f>
-        <v>92.106094107039056</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 418, in qlBondDirtyPrice
+    return bond.dirtyPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
+    return _QuantLib.Bond_dirtyPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2149,74 +3264,128 @@
       <c r="A35" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="10" t="str">
         <f>_xll.qlBondYield(B11,"actual360","CONTINUOUS","annual")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondYield
+    return bond.bondYield(
+           ~~~~~~~~~~~~~~^
+        dc,
+        ^^^
+    ...&lt;3 lines&gt;...
+        max_evaluations
+        ^^^^^^^^^^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+      <c r="C35" s="10" t="str">
+        <f>_xll.qlBondYield(C11,"actual360","CONTINUOUS","annual")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondYield
+    return bond.bondYield(
+           ~~~~~~~~~~~~~~^
+        dc,
+        ^^^
+    ...&lt;3 lines&gt;...
+        max_evaluations
+        ^^^^^^^^^^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" s="10" t="str">
+        <f>_xll.qlBondPrice(B30,"clean")</f>
+        <v>欣[test_bonds.xlsx]ZeroCouponBond!R36C2BondPrice,A</v>
+      </c>
+      <c r="C36" s="10" t="str">
+        <f>_xll.qlBondPrice(C30,"clean")</f>
+        <v>欣[test_bonds.xlsx]ZeroCouponBond!R36C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="10">
+        <f>_xll.qlBondYield2(B11,B36,"actual360","CONTINUOUS","annual")</f>
         <v>0.26236426417183883</v>
       </c>
-      <c r="C35" s="10">
-        <f>_xll.qlBondYield(C11,"actual360","CONTINUOUS","annual")</f>
+      <c r="C37" s="10">
+        <f>_xll.qlBondYield2(C11,C36,"actual360","CONTINUOUS","annual")</f>
         <v>0.26236426417183883</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="10">
-        <f>_xll.qlBondYield2(B11,B33,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
-      </c>
-      <c r="C36" s="10">
-        <f>_xll.qlBondYield2(C11,C33,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B38" s="2">
         <v>45667</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C38" s="2">
         <v>45667</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="10">
-        <f>_xll.qlBondAccruedAmount(B11,B37)</f>
-        <v>0</v>
-      </c>
-      <c r="C38" s="10">
-        <f>_xll.qlBondAccruedAmount(C11,C37)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="10">
+        <f>_xll.qlBondAccruedAmount(B11,B38)</f>
+        <v>0</v>
+      </c>
+      <c r="C39" s="10">
+        <f>_xll.qlBondAccruedAmount(C11,C38)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B40" s="10" t="str">
         <f>_xll.qlBondSettlementValue(B11)</f>
-        <v>76.755078422532549</v>
-      </c>
-      <c r="C39" s="10">
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+      <c r="C40" s="10">
         <f>_xll.qlBondSettlementValue(C11)</f>
         <v>92.106094107039056</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B41" s="10">
         <f>_xll.qlBondSettlementValue2(B11,B30)</f>
         <v>76.755078422532549</v>
       </c>
-      <c r="C40" s="10">
+      <c r="C41" s="10">
         <f>_xll.qlBondSettlementValue2(C11,C30)</f>
         <v>92.106094107039056</v>
       </c>
@@ -2226,9 +3395,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00EB77E5-949B-439C-BFA2-575F2A710E3C}">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
@@ -2379,7 +3548,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="34" t="s">
         <v>67</v>
       </c>
       <c r="B15" s="3">
@@ -2390,7 +3559,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="28"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="3">
         <v>0.5</v>
       </c>
@@ -2399,7 +3568,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="3">
         <v>0.6</v>
       </c>
@@ -2776,9 +3945,18 @@
         <f>_xll.qlBondDirtyPrice(B27)</f>
         <v>121.40429393805222</v>
       </c>
-      <c r="C49" s="10">
+      <c r="C49" s="10" t="str">
         <f>_xll.qlBondDirtyPrice(C27)</f>
-        <v>127.36781301760961</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 418, in qlBondDirtyPrice
+    return bond.dirtyPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
+    return _QuantLib.Bond_dirtyPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2798,61 +3976,106 @@
       <c r="A51" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="10" t="str">
         <f>_xll.qlBondYield(B27,"actual360","CONTINUOUS","annual")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondYield
+    return bond.bondYield(
+           ~~~~~~~~~~~~~~^
+        dc,
+        ^^^
+    ...&lt;3 lines&gt;...
+        max_evaluations
+        ^^^^^^^^^^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+      <c r="C51" s="10" t="str">
+        <f>_xll.qlBondYield(C27,"actual360","CONTINUOUS","annual")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondYield
+    return bond.bondYield(
+           ~~~~~~~~~~~~~~^
+        dc,
+        ^^^
+    ...&lt;3 lines&gt;...
+        max_evaluations
+        ^^^^^^^^^^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B52" s="10" t="str">
+        <f>_xll.qlBondPrice(B46,"clean")</f>
+        <v>欣[test_bonds.xlsx]FixedRateBond!R52C2BondPrice,A</v>
+      </c>
+      <c r="C52" s="10" t="str">
+        <f>_xll.qlBondPrice(C46,"clean")</f>
+        <v>欣[test_bonds.xlsx]FixedRateBond!R52C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="10">
+        <f>_xll.qlBondYield2(B27,B52,"actual360","CONTINUOUS","annual")</f>
         <v>0.26236426417183883</v>
       </c>
-      <c r="C51" s="10">
-        <f>_xll.qlBondYield(C27,"actual360","CONTINUOUS","annual")</f>
+      <c r="C53" s="10">
+        <f>_xll.qlBondYield2(C27,C52,"actual360","CONTINUOUS","annual")</f>
         <v>0.26236426417183883</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="10">
-        <f>_xll.qlBondYield2(B27,B49,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
-      </c>
-      <c r="C52" s="10">
-        <f>_xll.qlBondYield2(C27,C49,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B54" s="2">
         <v>45667</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C54" s="2">
         <v>45667</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="10">
-        <f>_xll.qlBondAccruedAmount(B27,B53)</f>
-        <v>0.22222222222221255</v>
-      </c>
-      <c r="C54" s="10">
-        <f>_xll.qlBondAccruedAmount(C27,C53)</f>
-        <v>-9.777777777777775</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="10">
+        <f>_xll.qlBondAccruedAmount(B27,B54)</f>
+        <v>0.22222222222221255</v>
+      </c>
+      <c r="C55" s="10">
+        <f>_xll.qlBondAccruedAmount(C27,C54)</f>
+        <v>-9.777777777777775</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B55" s="10" t="str">
+      <c r="B56" s="10" t="str">
         <f>_xll.qlBondSettlementValue(B27)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 529, in qlBondSettlementValue
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
     return bond.settlementValue()
            ~~~~~~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
@@ -2861,20 +4084,29 @@
 RuntimeError: null pricing engine
 </v>
       </c>
-      <c r="C55" s="10">
+      <c r="C56" s="10" t="str">
         <f>_xll.qlBondSettlementValue(C27)</f>
-        <v>127.36781301760961</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B57" s="10">
         <f>_xll.qlBondSettlementValue2(B27,B46)</f>
         <v>121.40429393805221</v>
       </c>
-      <c r="C56" s="10">
+      <c r="C57" s="10">
         <f>_xll.qlBondSettlementValue2(C27,C46)</f>
         <v>127.36781301760959</v>
       </c>
@@ -2887,9 +4119,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303A5445-988F-4FD7-9234-8C10A40DEB2F}">
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.42578125" customWidth="1"/>
@@ -2926,7 +4158,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="34" t="s">
         <v>84</v>
       </c>
       <c r="B5" s="3">
@@ -2937,7 +4169,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
+      <c r="A6" s="34"/>
       <c r="B6" s="3">
         <v>125</v>
       </c>
@@ -2946,7 +4178,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
+      <c r="A7" s="34"/>
       <c r="B7" s="3">
         <v>100</v>
       </c>
@@ -3058,7 +4290,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="34" t="s">
         <v>67</v>
       </c>
       <c r="B17" s="3">
@@ -3069,7 +4301,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="28"/>
+      <c r="A18" s="34"/>
       <c r="B18" s="3">
         <v>0.5</v>
       </c>
@@ -3078,7 +4310,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
+      <c r="A19" s="34"/>
       <c r="B19" s="3">
         <v>0.6</v>
       </c>
@@ -3147,7 +4379,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="34" t="s">
         <v>89</v>
       </c>
       <c r="C27" s="3">
@@ -3155,13 +4387,13 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="28"/>
+      <c r="A28" s="34"/>
       <c r="C28" s="3">
         <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="28"/>
+      <c r="A29" s="34"/>
       <c r="C29" s="3">
         <v>110</v>
       </c>
@@ -3330,7 +4562,7 @@
         <f>_xll.qlBondRedemption(B30)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 320, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 326, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -3343,7 +4575,7 @@
         <f>_xll.qlBondRedemption(C30)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 320, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 326, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -3476,9 +4708,18 @@
         <f>_xll.qlBondDirtyPrice(B30)</f>
         <v>116.28899295466947</v>
       </c>
-      <c r="C52" s="10">
+      <c r="C52" s="10" t="str">
         <f>_xll.qlBondDirtyPrice(C30)</f>
-        <v>115.0531622834792</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 418, in qlBondDirtyPrice
+    return bond.dirtyPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
+    return _QuantLib.Bond_dirtyPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -3502,70 +4743,117 @@
         <f>_xll.qlBondYield(B30,"actual360","CONTINUOUS","annual")</f>
         <v>0.26236426417183883</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C54" s="10" t="str">
         <f>_xll.qlBondYield(C30,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondYield
+    return bond.bondYield(
+           ~~~~~~~~~~~~~~^
+        dc,
+        ^^^
+    ...&lt;3 lines&gt;...
+        max_evaluations
+        ^^^^^^^^^^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" s="10" t="str">
+        <f>_xll.qlBondPrice(B49,"clean")</f>
+        <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R55C2BondPrice,A</v>
+      </c>
+      <c r="C55" s="10" t="str">
+        <f>_xll.qlBondPrice(C49,"clean")</f>
+        <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R55C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B55" s="10">
-        <f>_xll.qlBondYield2(B30,B52,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
-      </c>
-      <c r="C55" s="10">
-        <f>_xll.qlBondYield2(C30,C52,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="s">
+      <c r="B56" s="10">
+        <f>_xll.qlBondYield2(B30,B55,"actual360","CONTINUOUS","annual")</f>
+        <v>0.2650188827598095</v>
+      </c>
+      <c r="C56" s="10">
+        <f>_xll.qlBondYield2(C30,C55,"actual360","CONTINUOUS","annual")</f>
+        <v>0.1561166555979252</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B57" s="2">
         <v>45667</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C57" s="2">
         <v>45667</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="10">
-        <f>_xll.qlBondAccruedAmount(B30,B56)</f>
-        <v>0.22222222222221252</v>
-      </c>
-      <c r="C57" s="10">
-        <f>_xll.qlBondAccruedAmount(C30,C56)</f>
-        <v>-9.7777777777777732</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B58" s="10">
-        <f>_xll.qlBondSettlementValue(B30)</f>
-        <v>174.43348943200422</v>
+        <f>_xll.qlBondAccruedAmount(B30,B57)</f>
+        <v>0.22222222222221252</v>
       </c>
       <c r="C58" s="10">
-        <f>_xll.qlBondSettlementValue(C30)</f>
-        <v>172.57974342521879</v>
+        <f>_xll.qlBondAccruedAmount(C30,C57)</f>
+        <v>-9.7777777777777732</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B59" s="10" t="str">
+        <f>_xll.qlBondSettlementValue(B30)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+      <c r="C59" s="10" t="str">
+        <f>_xll.qlBondSettlementValue(C30)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B60" s="10">
         <f>_xll.qlBondSettlementValue2(B30,B49)</f>
         <v>174.43348943200419</v>
       </c>
-      <c r="C59" s="10">
+      <c r="C60" s="10">
         <f>_xll.qlBondSettlementValue2(C30,C49)</f>
         <v>172.57974342521879</v>
       </c>
@@ -3580,9 +4868,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F76F30CA-2F79-453E-B116-2A48310E361D}">
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.42578125" customWidth="1"/>
@@ -3619,7 +4907,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="34" t="s">
         <v>90</v>
       </c>
       <c r="B5" s="3">
@@ -3630,7 +4918,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
+      <c r="A6" s="34"/>
       <c r="B6" s="3">
         <v>125</v>
       </c>
@@ -3639,7 +4927,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
+      <c r="A7" s="34"/>
       <c r="B7" s="3">
         <v>100</v>
       </c>
@@ -4059,7 +5347,7 @@
         <f>_xll.qlBondRedemption(B34)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 320, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 326, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -4072,7 +5360,7 @@
         <f>_xll.qlBondRedemption(C34)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 320, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 326, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -4231,70 +5519,108 @@
         <f>_xll.qlBondYield(B34,"actual360","CONTINUOUS","annual")</f>
         <v>0.28928264971926221</v>
       </c>
-      <c r="C58" s="10">
+      <c r="C58" s="10" t="str">
         <f>_xll.qlBondYield(C34,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondYield
+    return bond.bondYield(
+           ~~~~~~~~~~~~~~^
+        dc,
+        ^^^
+    ...&lt;3 lines&gt;...
+        max_evaluations
+        ^^^^^^^^^^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B59" s="10" t="str">
+        <f>_xll.qlBondPrice(B53,"clean")</f>
+        <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R59C2BondPrice,A</v>
+      </c>
+      <c r="C59" s="10" t="str">
+        <f>_xll.qlBondPrice(C53,"clean")</f>
+        <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R59C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B59" s="10">
-        <f>_xll.qlBondYield2(B34,B56,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
-      </c>
-      <c r="C59" s="10">
-        <f>_xll.qlBondYield2(C34,C56,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="11" t="s">
+      <c r="B60" s="10">
+        <f>_xll.qlBondYield2(B34,B59,"actual360","CONTINUOUS","annual")</f>
+        <v>0.29158154279763698</v>
+      </c>
+      <c r="C60" s="10">
+        <f>_xll.qlBondYield2(C34,C59,"actual360","CONTINUOUS","annual")</f>
+        <v>0.19027274083304402</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B61" s="2">
         <v>45667</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C61" s="2">
         <v>45667</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="10">
-        <f>_xll.qlBondAccruedAmount(B34,B60)</f>
-        <v>0.16666666666666657</v>
-      </c>
-      <c r="C61" s="10">
-        <f>_xll.qlBondAccruedAmount(C34,C60)</f>
-        <v>-7.3333333333333286</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="10">
+        <f>_xll.qlBondAccruedAmount(B34,B61)</f>
+        <v>0.16666666666666657</v>
+      </c>
+      <c r="C62" s="10">
+        <f>_xll.qlBondAccruedAmount(C34,C61)</f>
+        <v>-7.3333333333333286</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B63" s="10" t="str">
         <f>_xll.qlBondSettlementValue(B34)</f>
-        <v>150.24592768168819</v>
-      </c>
-      <c r="C62" s="10">
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+      <c r="C63" s="10">
         <f>_xll.qlBondSettlementValue(C34)</f>
         <v>139.76397912193815</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="8" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B64" s="10">
         <f>_xll.qlBondSettlementValue2(B34,B53)</f>
         <v>150.24592768168822</v>
       </c>
-      <c r="C63" s="10">
+      <c r="C64" s="10">
         <f>_xll.qlBondSettlementValue2(C34,C53)</f>
         <v>139.76397912193815</v>
       </c>
@@ -4308,9 +5634,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05025377-E5EA-48F0-BE68-1C47A2C5C8E6}">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.28515625" customWidth="1"/>
@@ -4851,9 +6177,18 @@
         <f>_xll.qlBondCleanPrice(B31)</f>
         <v>99.998840118437755</v>
       </c>
-      <c r="C50" s="10">
+      <c r="C50" s="10" t="str">
         <f>_xll.qlBondCleanPrice(C31)</f>
-        <v>100.51087441193772</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 380, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -4884,9 +6219,18 @@
       <c r="A53" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="10" t="str">
         <f>_xll.qlBondDirtyPrice(B31)</f>
-        <v>100.16550678510443</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 418, in qlBondDirtyPrice
+    return bond.dirtyPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
+    return _QuantLib.Bond_dirtyPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
       <c r="C53" s="10">
         <f>_xll.qlBondDirtyPrice(C31)</f>
@@ -4914,72 +6258,171 @@
         <f>_xll.qlBondYield(B31,"actual360","CONTINUOUS","annual")</f>
         <v>0.28928264971926221</v>
       </c>
-      <c r="C55" s="10">
+      <c r="C55" s="10" t="str">
         <f>_xll.qlBondYield(C31,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondYield
+    return bond.bondYield(
+           ~~~~~~~~~~~~~~^
+        dc,
+        ^^^
+    ...&lt;3 lines&gt;...
+        max_evaluations
+        ^^^^^^^^^^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" s="10" t="str">
+        <f>_xll.qlBondPrice(B50,"clean")</f>
+        <v>欣[test_bonds.xlsx]FloatingRateBond!R56C2BondPrice,A</v>
+      </c>
+      <c r="C56" s="10" t="str">
+        <f>_xll.qlBondPrice(C50,"clean")</f>
+        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 380, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B56" s="10">
-        <f>_xll.qlBondYield2(B31,B53,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
-      </c>
-      <c r="C56" s="10">
-        <f>_xll.qlBondYield2(C31,C53,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
+      <c r="B57" s="10">
+        <f>_xll.qlBondYield2(B31,B56,"actual360","CONTINUOUS","annual")</f>
+        <v>0.29112129323880687</v>
+      </c>
+      <c r="C57" s="10" t="str">
+        <f>_xll.qlBondYield2(C31,C56,"actual360","CONTINUOUS","annual")</f>
+        <v xml:space="preserve">TypeError: TypeError: Wrong number or type of arguments for overloaded function 'Bond_bondYield'.
+  Possible C/C++ prototypes are:
+    Bond::yield(DayCounter const &amp;,Compounding,Frequency,Real,Size)
+    Bond::yield(DayCounter const &amp;,Compounding,Frequency,Real)
+    Bond::yield(DayCounter const &amp;,Compounding,Frequency)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real,Size,Real)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real,Size)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency)
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 505, in qlBondYield2
+    return bond.bondYield(
+           ~~~~~~~~~~~~~~^
+        price,
+        ^^^^^^
+    ...&lt;6 lines&gt;...
+        guess
+        ^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+TypeError: Wrong number or type of arguments for overloaded function 'Bond_bondYield'.
+  Possible C/C++ prototypes are:
+    Bond::yield(DayCounter const &amp;,Compounding,Frequency,Real,Size)
+    Bond::yield(DayCounter const &amp;,Compounding,Frequency,Real)
+    Bond::yield(DayCounter const &amp;,Compounding,Frequency)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real,Size,Real)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real,Size)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency)
+</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B58" s="2">
         <v>45667</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C58" s="2">
         <v>45667</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="10">
-        <f>_xll.qlBondAccruedAmount(B31,B57)</f>
-        <v>0.16666666666666657</v>
-      </c>
-      <c r="C58" s="10">
-        <f>_xll.qlBondAccruedAmount(C31,C57)</f>
-        <v>-7.3333333333333277</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B59" s="10">
-        <f>_xll.qlBondSettlementValue(B31)</f>
-        <v>100.16550678510443</v>
+        <f>_xll.qlBondAccruedAmount(B31,B58)</f>
+        <v>0.16666666666666657</v>
       </c>
       <c r="C59" s="10">
-        <f>_xll.qlBondSettlementValue(C31)</f>
-        <v>93.177541078604392</v>
+        <f>_xll.qlBondAccruedAmount(C31,C58)</f>
+        <v>-7.3333333333333277</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="10" t="str">
+        <f>_xll.qlBondSettlementValue(B31)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+      <c r="C60" s="10" t="str">
+        <f>_xll.qlBondSettlementValue(C31)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B61" s="10">
         <f>_xll.qlBondSettlementValue2(B31,B50)</f>
         <v>100.16550678510443</v>
       </c>
-      <c r="C60" s="10">
+      <c r="C61" s="10" t="str">
         <f>_xll.qlBondSettlementValue2(C31,C50)</f>
-        <v>93.177541078604392</v>
+        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 380, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float</v>
       </c>
     </row>
   </sheetData>
@@ -4987,9 +6430,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27515A30-3B44-433D-8DBF-ACC4ED7765FD}">
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.140625" customWidth="1"/>
@@ -5624,9 +7067,18 @@
         <f>_xll.qlBondCleanPrice(B36)</f>
         <v>158.97331982635237</v>
       </c>
-      <c r="C55" s="10">
+      <c r="C55" s="10" t="str">
         <f>_xll.qlBondCleanPrice(C36)</f>
-        <v>89.639709460333037</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 380, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -5657,13 +7109,31 @@
       <c r="A58" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="10" t="str">
         <f>_xll.qlBondDirtyPrice(B36)</f>
-        <v>159.52887538190791</v>
-      </c>
-      <c r="C58" s="10">
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 418, in qlBondDirtyPrice
+    return bond.dirtyPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
+    return _QuantLib.Bond_dirtyPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+      <c r="C58" s="10" t="str">
         <f>_xll.qlBondDirtyPrice(C36)</f>
-        <v>89.639709460333037</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 418, in qlBondDirtyPrice
+    return bond.dirtyPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
+    return _QuantLib.Bond_dirtyPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -5693,867 +7163,153 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B61" s="10" t="str">
+        <f>_xll.qlBondPrice(B55,"clean")</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R61C2BondPrice,A</v>
+      </c>
+      <c r="C61" s="10" t="str">
+        <f>_xll.qlBondPrice(C55,"clean")</f>
+        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 380, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B61" s="10">
-        <f>_xll.qlBondYield2(B36,B58,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
-      </c>
-      <c r="C61" s="10">
-        <f>_xll.qlBondYield2(C36,C58,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928265005463161</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="11" t="s">
+      <c r="B62" s="10">
+        <f>_xll.qlBondYield2(B36,B61,"actual360","CONTINUOUS","annual")</f>
+        <v>0.29367879784610279</v>
+      </c>
+      <c r="C62" s="10" t="str">
+        <f>_xll.qlBondYield2(C36,C61,"actual360","CONTINUOUS","annual")</f>
+        <v xml:space="preserve">TypeError: TypeError: Wrong number or type of arguments for overloaded function 'Bond_bondYield'.
+  Possible C/C++ prototypes are:
+    Bond::yield(DayCounter const &amp;,Compounding,Frequency,Real,Size)
+    Bond::yield(DayCounter const &amp;,Compounding,Frequency,Real)
+    Bond::yield(DayCounter const &amp;,Compounding,Frequency)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real,Size,Real)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real,Size)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency)
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 505, in qlBondYield2
+    return bond.bondYield(
+           ~~~~~~~~~~~~~~^
+        price,
+        ^^^^^^
+    ...&lt;6 lines&gt;...
+        guess
+        ^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+TypeError: Wrong number or type of arguments for overloaded function 'Bond_bondYield'.
+  Possible C/C++ prototypes are:
+    Bond::yield(DayCounter const &amp;,Compounding,Frequency,Real,Size)
+    Bond::yield(DayCounter const &amp;,Compounding,Frequency,Real)
+    Bond::yield(DayCounter const &amp;,Compounding,Frequency)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real,Size,Real)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real,Size)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;)
+    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency)
+</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B63" s="2">
         <v>45667</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C63" s="2">
         <v>45667</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="10">
-        <f>_xll.qlBondAccruedAmount(B36,B62)</f>
-        <v>0.55555555555555358</v>
-      </c>
-      <c r="C63" s="10">
-        <f>_xll.qlBondAccruedAmount(C36,C62)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B64" s="10">
-        <f>_xll.qlBondSettlementValue(B36)</f>
-        <v>159.52887538190791</v>
+        <f>_xll.qlBondAccruedAmount(B36,B63)</f>
+        <v>0.55555555555555358</v>
       </c>
       <c r="C64" s="10">
-        <f>_xll.qlBondSettlementValue(C36)</f>
-        <v>89.639709460333037</v>
+        <f>_xll.qlBondAccruedAmount(C36,C63)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B65" s="10" t="str">
+        <f>_xll.qlBondSettlementValue(B36)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+      <c r="C65" s="10" t="str">
+        <f>_xll.qlBondSettlementValue(C36)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B66" s="10">
         <f>_xll.qlBondSettlementValue2(B36,B55)</f>
         <v>159.52887538190791</v>
       </c>
-      <c r="C65" s="10">
+      <c r="C66" s="10" t="str">
         <f>_xll.qlBondSettlementValue2(C36,C55)</f>
-        <v>89.639709460333037</v>
+        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 380, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28ABD84F-1436-4AE1-BC17-091C65B56114}">
-  <dimension ref="A1:C66"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="48.5703125" customWidth="1"/>
-    <col min="2" max="2" width="69.140625" customWidth="1"/>
-    <col min="3" max="3" width="71.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="2">
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="2">
-        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="3">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="B5" s="3">
-        <v>103</v>
-      </c>
-      <c r="C5" s="3">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
-      <c r="B6" s="3">
-        <v>102</v>
-      </c>
-      <c r="C6" s="3">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="3">
-        <v>101</v>
-      </c>
-      <c r="C7" s="3">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="12">
-        <v>45665</v>
-      </c>
-      <c r="C8" s="12">
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="12">
-        <v>46030</v>
-      </c>
-      <c r="C9" s="12">
-        <v>46030</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="6" t="str">
-        <f>_xll.qlCalendar("TARGET")</f>
-        <v>TARGET</v>
-      </c>
-      <c r="C11" s="6" t="str">
-        <f>_xll.qlCalendar("TARGET")</f>
-        <v>TARGET</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="6">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="3" t="str">
-        <f>_xll.qlSchedule(B8,B9,B10,B11,B12,B13,B14,B15)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R16C2Schedule,A</v>
-      </c>
-      <c r="C16" s="3" t="str">
-        <f>_xll.qlSchedule(C8,C9,C10,C11,C12,C13,C14,C15)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R16C3Schedule,A</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="6">
-        <v>2</v>
-      </c>
-      <c r="C19" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" s="6" t="str">
-        <f>_xll.qlCalendar("TARGET")</f>
-        <v>TARGET</v>
-      </c>
-      <c r="C21" s="6" t="str">
-        <f>_xll.qlCalendar("TARGET")</f>
-        <v>TARGET</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="B25" s="6" t="str">
-        <f>_xll.qlEuribor("3M")</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R25C2Euribor,A</v>
-      </c>
-      <c r="C25" s="6" t="str">
-        <f>_xll.qlEuribor("3M")</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R25C3Euribor,A</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="B26" s="6" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"Actual360","Compounded","Quarterly")</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R26C2YieldTermStructureHandle,A</v>
-      </c>
-      <c r="C26" s="6" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.03,"Actual360","Compounded","Quarterly")</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R26C3YieldTermStructureHandle,A</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>102</v>
-      </c>
-      <c r="B27" s="3" t="str">
-        <f>_xll.qlSwapIndex(B17,B18,B19,B20,B21,B22,B23,B24,B25,B26)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R27C2SwapIndex,A</v>
-      </c>
-      <c r="C27" s="3" t="str">
-        <f>_xll.qlSwapIndex(C17,C18,C19,C20,C21,C22,C23,C24,C25,C26)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R27C3SwapIndex,A</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>92</v>
-      </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>97</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="2">
-        <v>45663</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B37" t="str">
-        <f>_xll.qlAmortizingCmsRateBond(B4,B5:B7,B16,B27,B28)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R37C2AmortizingCmsRateBond,A</v>
-      </c>
-      <c r="C37" t="str">
-        <f>_xll.qlAmortizingCmsRateBond(C4,C5:C7,C16,C27,C28,C29,C30,C31,C32,C33,C34,C35,C36)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R37C3AmortizingCmsRateBond,A</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B38" s="3">
-        <f>_xll.qlBondNextCouponRate(B37)</f>
-        <v>0</v>
-      </c>
-      <c r="C38" s="3">
-        <f>_xll.qlBondNextCouponRate(C37)</f>
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" s="3">
-        <f>_xll.qlBondPreviousCouponRate(B37)</f>
-        <v>0</v>
-      </c>
-      <c r="C39" s="3">
-        <f>_xll.qlBondPreviousCouponRate(C37)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B40" s="2">
-        <f>_xll.qlBondNextCashFlowDate(B37)</f>
-        <v>45755</v>
-      </c>
-      <c r="C40" s="2">
-        <f>_xll.qlBondNextCashFlowDate(C37)</f>
-        <v>45755</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B41" s="2">
-        <f>_xll.qlBondPreviousCashFlowDate(B37)</f>
-        <v>0</v>
-      </c>
-      <c r="C41" s="2">
-        <f>_xll.qlBondPreviousCashFlowDate(C37)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B42" s="3">
-        <f>_xll.qlBondSettlementDays(B37)</f>
-        <v>2</v>
-      </c>
-      <c r="C42" s="3">
-        <f>_xll.qlBondSettlementDays(C37)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B43" s="2">
-        <f>_xll.qlBondSettlementDate(B37)</f>
-        <v>45667</v>
-      </c>
-      <c r="C43" s="2">
-        <f>_xll.qlBondSettlementDate(C37)</f>
-        <v>45667</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B44" s="3" t="b">
-        <f>_xll.qlBondIsTradable(B37)</f>
-        <v>1</v>
-      </c>
-      <c r="C44" s="3" t="b">
-        <f>_xll.qlBondIsTradable(C37)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" s="2">
-        <f>_xll.qlBondStartDate(B37)</f>
-        <v>45665</v>
-      </c>
-      <c r="C45" s="2">
-        <f>_xll.qlBondStartDate(C37)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B46" s="2">
-        <f>_xll.qlBondMaturityDate(B37)</f>
-        <v>46030</v>
-      </c>
-      <c r="C46" s="2">
-        <f>_xll.qlBondMaturityDate(C37)</f>
-        <v>46030</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B47" s="3">
-        <f>_xll.qlBondIssueDate(B37)</f>
-        <v>0</v>
-      </c>
-      <c r="C47" s="3">
-        <f>_xll.qlBondIssueDate(C37)</f>
-        <v>45663</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B48" s="3" t="str">
-        <f>_xll.qlBondCashFlows(B37)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R48C2CashFlow,A</v>
-      </c>
-      <c r="C48" s="3" t="str">
-        <f>_xll.qlBondCashFlows(C37)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R48C3CashFlow,A</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B49" s="3" t="str">
-        <f>_xll.qlBondRedemption(B37)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 320, in qlBondRedemption
-    return bond.redemption()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
-    return _QuantLib.Bond_redemption(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: multiple redemption cash flows given
-</v>
-      </c>
-      <c r="C49" s="3" t="str">
-        <f>_xll.qlBondRedemption(C37)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 320, in qlBondRedemption
-    return bond.redemption()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
-    return _QuantLib.Bond_redemption(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: multiple redemption cash flows given
-</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B50" s="3" t="str">
-        <f>_xll.qlBondRedemptions(B37)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R50C2CashFlow,A</v>
-      </c>
-      <c r="C50" s="3" t="str">
-        <f>_xll.qlBondRedemptions(C37)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R50C3CashFlow,A</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B51" s="3" t="str">
-        <f>_xll.qlBondCalendar(B37)</f>
-        <v>TARGET</v>
-      </c>
-      <c r="C51" s="3" t="str">
-        <f>_xll.qlBondCalendar(C37)</f>
-        <v>TARGET</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B52" s="3">
-        <f>_xll.qlBondNotional(B37)</f>
-        <v>103</v>
-      </c>
-      <c r="C52" s="3">
-        <f>_xll.qlBondNotional(C37)</f>
-        <v>103</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="3">
-        <f>_xll.qlBondNotionals(B37)</f>
-        <v>103</v>
-      </c>
-      <c r="C53" s="3">
-        <f>_xll.qlBondNotionals(C37)</f>
-        <v>103</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B54" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R54C2YieldTermStructureHandle,A</v>
-      </c>
-      <c r="C54" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R54C3YieldTermStructureHandle,A</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B55" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(B37,B54)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R55C2DiscountingBondEngine,A</v>
-      </c>
-      <c r="C55" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(C37,C54)</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R55C3DiscountingBondEngine,A</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B56" s="10">
-        <f>_xll.qlBondCleanPrice(B37)</f>
-        <v>74.994672295319077</v>
-      </c>
-      <c r="C56" s="10">
-        <f>_xll.qlBondCleanPrice(C37)</f>
-        <v>75.244545975491022</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B57" s="10">
-        <v>0.28928264971926221</v>
-      </c>
-      <c r="C57" s="10">
-        <v>0.28928264971926221</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B58" s="10">
-        <f>_xll.qlBondCleanPrice2(B37,B57,"actual360","continuous")</f>
-        <v>74.994672041966595</v>
-      </c>
-      <c r="C58" s="10">
-        <f>_xll.qlBondCleanPrice2(C37,C57,"actual360","continuous")</f>
-        <v>75.244545721623112</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B59" s="10">
-        <f>_xll.qlBondDirtyPrice(B37)</f>
-        <v>74.994672295319077</v>
-      </c>
-      <c r="C59" s="10">
-        <f>_xll.qlBondDirtyPrice(C37)</f>
-        <v>75.246212642157701</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B60" s="10">
-        <f>_xll.qlBondDirtyPrice2(B37,B57,"actual360","CONTINUOUS","annual")</f>
-        <v>74.994672041966595</v>
-      </c>
-      <c r="C60" s="10">
-        <f>_xll.qlBondDirtyPrice2(C37,C57,"actual360","CONTINUOUS","annual")</f>
-        <v>75.246212388289791</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="10">
-        <f>_xll.qlBondYield(B37,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264826921379</v>
-      </c>
-      <c r="C61" s="10">
-        <f>_xll.qlBondYield(C37,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264793774228</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="10">
-        <f>_xll.qlBondYield2(B37,B59,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264826921379</v>
-      </c>
-      <c r="C62" s="10">
-        <f>_xll.qlBondYield2(C37,C59,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264793774228</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63" s="2">
-        <v>45667</v>
-      </c>
-      <c r="C63" s="2">
-        <v>45667</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="10">
-        <f>_xll.qlBondAccruedAmount(B37,B63)</f>
-        <v>0</v>
-      </c>
-      <c r="C64" s="10">
-        <f>_xll.qlBondAccruedAmount(C37,C63)</f>
-        <v>1.6666666666775853E-3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="10">
-        <f>_xll.qlBondSettlementValue(B37)</f>
-        <v>77.244512464178641</v>
-      </c>
-      <c r="C65" s="10">
-        <f>_xll.qlBondSettlementValue(C37)</f>
-        <v>77.503599021422431</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="10">
-        <f>_xll.qlBondSettlementValue2(B37,B56)</f>
-        <v>77.244512464178655</v>
-      </c>
-      <c r="C66" s="10">
-        <f>_xll.qlBondSettlementValue2(C37,C56)</f>
-        <v>77.503599021422431</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A5:A7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/tests/workbooks/test_bonds.xlsx
+++ b/tests/workbooks/test_bonds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804525A8-9446-4835-9374-D51F9E284B26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FF61BC-DA5F-472D-B229-DD580FBE5AA5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="32370" windowHeight="9360" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
   </bookViews>
@@ -1685,7 +1685,7 @@
         <f>_xll.qlBondIssueDate(B37)</f>
         <v>0</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="2">
         <f>_xll.qlBondIssueDate(C37)</f>
         <v>45663</v>
       </c>
@@ -1711,7 +1711,7 @@
         <f>_xll.qlBondRedemption(B37)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 326, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 402, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -1724,7 +1724,7 @@
         <f>_xll.qlBondRedemption(C37)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 326, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 402, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -1820,9 +1820,18 @@
         <f>_xll.qlBondCleanPrice(B37)</f>
         <v>74.994672295319077</v>
       </c>
-      <c r="C56" s="10">
+      <c r="C56" s="10" t="str">
         <f>_xll.qlBondCleanPrice(C37)</f>
-        <v>75.244545975491022</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1879,11 +1888,15 @@
       <c r="A61" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B61" s="10" t="str">
+      <c r="B61" s="10">
         <f>_xll.qlBondYield(B37,"actual360","CONTINUOUS","annual")</f>
+        <v>0.28928264826921379</v>
+      </c>
+      <c r="C61" s="10" t="str">
+        <f>_xll.qlBondYield(C37,"actual360","CONTINUOUS","annual")</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondYield
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
     return bond.bondYield(
            ~~~~~~~~~~~~~~^
         dc,
@@ -1899,10 +1912,6 @@
 RuntimeError: null pricing engine
 </v>
       </c>
-      <c r="C61" s="10">
-        <f>_xll.qlBondYield(C37,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264793774228</v>
-      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
@@ -1914,7 +1923,16 @@
       </c>
       <c r="C62" s="10" t="str">
         <f>_xll.qlBondPrice(C56,"clean")</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R62C3BondPrice,A</v>
+        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1925,9 +1943,18 @@
         <f>_xll.qlBondYield2(B37,B62,"actual360","CONTINUOUS","annual")</f>
         <v>0.28928264826921379</v>
       </c>
-      <c r="C63" s="10">
+      <c r="C63" s="10" t="str">
         <f>_xll.qlBondYield2(C37,C62,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28930497525756377</v>
+        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float': Expected cache string</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1958,11 +1985,15 @@
       <c r="A66" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B66" s="10" t="str">
+      <c r="B66" s="10">
         <f>_xll.qlBondSettlementValue(B37)</f>
+        <v>77.244512464178641</v>
+      </c>
+      <c r="C66" s="10" t="str">
+        <f>_xll.qlBondSettlementValue(C37)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 635, in qlBondSettlementValue
     return bond.settlementValue()
            ~~~~~~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
@@ -1971,19 +2002,6 @@
 RuntimeError: null pricing engine
 </v>
       </c>
-      <c r="C66" s="10" t="str">
-        <f>_xll.qlBondSettlementValue(C37)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
@@ -1993,9 +2011,18 @@
         <f>_xll.qlBondSettlementValue2(B37,B56)</f>
         <v>77.244512464178655</v>
       </c>
-      <c r="C67" s="10">
+      <c r="C67" s="10" t="str">
         <f>_xll.qlBondSettlementValue2(C37,C56)</f>
-        <v>77.503599021422431</v>
+        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float</v>
       </c>
     </row>
   </sheetData>
@@ -2012,7 +2039,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="45.42578125" customWidth="1"/>
+    <col min="2" max="2" width="45.42578125" style="3" customWidth="1"/>
     <col min="6" max="6" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2020,7 +2047,7 @@
       <c r="A3" t="s">
         <v>127</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B3" s="3" t="str">
         <f>_xll.qlBondPrice(100,"clean")</f>
         <v>欣[test_bonds.xlsx]Callability!R3C2BondPrice,A</v>
       </c>
@@ -2029,7 +2056,7 @@
       <c r="A4" t="s">
         <v>128</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2037,7 +2064,7 @@
       <c r="A5" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="2">
         <v>46357</v>
       </c>
     </row>
@@ -2045,7 +2072,7 @@
       <c r="A6" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B6" s="3" t="str">
         <f>_xll.qlCallability(B3,B4,B5)</f>
         <v>欣[test_bonds.xlsx]Callability!R6C2Callability,A</v>
       </c>
@@ -2054,7 +2081,7 @@
       <c r="A7" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B7" s="3" t="str">
         <f>_xll.qlCallabilityPrice(B6)</f>
         <v>欣[test_bonds.xlsx]Callability!R7C2BondPrice,A</v>
       </c>
@@ -2063,7 +2090,7 @@
       <c r="A8" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="2">
         <f>_xll.qlCallabilityDate(B6)</f>
         <v>46357</v>
       </c>
@@ -2072,7 +2099,7 @@
       <c r="A9" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B9" t="str">
+      <c r="B9" s="3" t="str">
         <f>_xll.qlCallabilityType(B6)</f>
         <v>PUT</v>
       </c>
@@ -2653,9 +2680,18 @@
       <c r="A44" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="10" t="str">
         <f>_xll.qlBondCleanPrice(B25)</f>
-        <v>2.3179669686853783</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
       <c r="C44" s="10">
         <f>_xll.qlBondCleanPrice(C25)</f>
@@ -2690,18 +2726,9 @@
       <c r="A47" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B47" s="10" t="str">
+      <c r="B47" s="10">
         <f>_xll.qlBondDirtyPrice(B25)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 418, in qlBondDirtyPrice
-    return bond.dirtyPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
-    return _QuantLib.Bond_dirtyPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>2.3346336353520432</v>
       </c>
       <c r="C47" s="10">
         <f>_xll.qlBondDirtyPrice(C25)</f>
@@ -2725,9 +2752,25 @@
       <c r="A49" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="10" t="str">
         <f>_xll.qlBondYield(B25,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426559332721</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
+    return bond.bondYield(
+           ~~~~~~~~~~~~~~^
+        dc,
+        ^^^
+    ...&lt;3 lines&gt;...
+        max_evaluations
+        ^^^^^^^^^^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
       <c r="C49" s="10">
         <f>_xll.qlBondYield(C25,"actual360","CONTINUOUS","annual")</f>
@@ -2740,7 +2783,16 @@
       </c>
       <c r="B50" s="10" t="str">
         <f>_xll.qlBondPrice(B44,"clean")</f>
-        <v>欣[test_bonds.xlsx]Bond!R50C2BondPrice,A</v>
+        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float</v>
       </c>
       <c r="C50" s="10" t="str">
         <f>_xll.qlBondPrice(C44,"clean")</f>
@@ -2751,9 +2803,18 @@
       <c r="A51" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="10" t="str">
         <f>_xll.qlBondYield2(B25,B50,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26946953931176648</v>
+        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float': Expected cache string</v>
       </c>
       <c r="C51" s="10">
         <f>_xll.qlBondYield2(C25,C50,"actual360","CONTINUOUS","annual")</f>
@@ -2788,11 +2849,15 @@
       <c r="A54" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B54" s="10" t="str">
+      <c r="B54" s="10">
         <f>_xll.qlBondSettlementValue(B25)</f>
+        <v>2.3346336353520432</v>
+      </c>
+      <c r="C54" s="10" t="str">
+        <f>_xll.qlBondSettlementValue(C25)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 635, in qlBondSettlementValue
     return bond.settlementValue()
            ~~~~~~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
@@ -2801,18 +2866,23 @@
 RuntimeError: null pricing engine
 </v>
       </c>
-      <c r="C54" s="10">
-        <f>_xll.qlBondSettlementValue(C25)</f>
-        <v>2.3346336353520432</v>
-      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="10" t="str">
         <f>_xll.qlBondSettlementValue2(B25,B44)</f>
-        <v>2.3346336353520432</v>
+        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float</v>
       </c>
       <c r="C55" s="10">
         <f>_xll.qlBondSettlementValue2(C25,C44)</f>
@@ -2944,7 +3014,7 @@
         <f>_xll.qlBondNextCouponRate(B11)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2026
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 209, in qlBondNextCouponRate
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 249, in qlBondNextCouponRate
     return bond.nextCouponRate(date)
            ~~~~~~~~~~~~~~~~~~~^^^^^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
@@ -2957,7 +3027,7 @@
         <f>_xll.qlBondNextCouponRate(C11)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2026
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 209, in qlBondNextCouponRate
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 249, in qlBondNextCouponRate
     return bond.nextCouponRate(date)
            ~~~~~~~~~~~~~~~~~~~^^^^^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
@@ -3196,9 +3266,18 @@
         <f>_xll.qlBondCleanPrice(B11)</f>
         <v>76.755078422532549</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="10" t="str">
         <f>_xll.qlBondCleanPrice(C11)</f>
-        <v>92.106094107039056</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -3229,15 +3308,11 @@
       <c r="A33" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="10" t="str">
         <f>_xll.qlBondDirtyPrice(B11)</f>
-        <v>76.755078422532549</v>
-      </c>
-      <c r="C33" s="10" t="str">
-        <f>_xll.qlBondDirtyPrice(C11)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 418, in qlBondDirtyPrice
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 511, in qlBondDirtyPrice
     return bond.dirtyPrice()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
@@ -3246,6 +3321,10 @@
 RuntimeError: null pricing engine
 </v>
       </c>
+      <c r="C33" s="10">
+        <f>_xll.qlBondDirtyPrice(C11)</f>
+        <v>92.106094107039056</v>
+      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
@@ -3268,7 +3347,7 @@
         <f>_xll.qlBondYield(B11,"actual360","CONTINUOUS","annual")</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondYield
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
     return bond.bondYield(
            ~~~~~~~~~~~~~~^
         dc,
@@ -3284,25 +3363,9 @@
 RuntimeError: null pricing engine
 </v>
       </c>
-      <c r="C35" s="10" t="str">
+      <c r="C35" s="10">
         <f>_xll.qlBondYield(C11,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondYield
-    return bond.bondYield(
-           ~~~~~~~~~~~~~~^
-        dc,
-        ^^^
-    ...&lt;3 lines&gt;...
-        max_evaluations
-        ^^^^^^^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>0.26236426417183883</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -3315,7 +3378,16 @@
       </c>
       <c r="C36" s="10" t="str">
         <f>_xll.qlBondPrice(C30,"clean")</f>
-        <v>欣[test_bonds.xlsx]ZeroCouponBond!R36C3BondPrice,A</v>
+        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -3326,9 +3398,18 @@
         <f>_xll.qlBondYield2(B11,B36,"actual360","CONTINUOUS","annual")</f>
         <v>0.26236426417183883</v>
       </c>
-      <c r="C37" s="10">
+      <c r="C37" s="10" t="str">
         <f>_xll.qlBondYield2(C11,C36,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
+        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float': Expected cache string</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -3363,7 +3444,7 @@
         <f>_xll.qlBondSettlementValue(B11)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 635, in qlBondSettlementValue
     return bond.settlementValue()
            ~~~~~~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
@@ -3385,9 +3466,18 @@
         <f>_xll.qlBondSettlementValue2(B11,B30)</f>
         <v>76.755078422532549</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="10" t="str">
         <f>_xll.qlBondSettlementValue2(C11,C30)</f>
-        <v>92.106094107039056</v>
+        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float</v>
       </c>
     </row>
   </sheetData>
@@ -3908,9 +3998,18 @@
         <f>_xll.qlBondCleanPrice(B27)</f>
         <v>121.40429393805222</v>
       </c>
-      <c r="C46" s="10">
+      <c r="C46" s="10" t="str">
         <f>_xll.qlBondCleanPrice(C27)</f>
-        <v>127.36781301760961</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -3945,18 +4044,9 @@
         <f>_xll.qlBondDirtyPrice(B27)</f>
         <v>121.40429393805222</v>
       </c>
-      <c r="C49" s="10" t="str">
+      <c r="C49" s="10">
         <f>_xll.qlBondDirtyPrice(C27)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 418, in qlBondDirtyPrice
-    return bond.dirtyPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
-    return _QuantLib.Bond_dirtyPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>127.36781301760961</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -3976,11 +4066,15 @@
       <c r="A51" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B51" s="10" t="str">
+      <c r="B51" s="10">
         <f>_xll.qlBondYield(B27,"actual360","CONTINUOUS","annual")</f>
+        <v>0.26236426417183883</v>
+      </c>
+      <c r="C51" s="10" t="str">
+        <f>_xll.qlBondYield(C27,"actual360","CONTINUOUS","annual")</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondYield
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
     return bond.bondYield(
            ~~~~~~~~~~~~~~^
         dc,
@@ -3996,26 +4090,6 @@
 RuntimeError: null pricing engine
 </v>
       </c>
-      <c r="C51" s="10" t="str">
-        <f>_xll.qlBondYield(C27,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondYield
-    return bond.bondYield(
-           ~~~~~~~~~~~~~~^
-        dc,
-        ^^^
-    ...&lt;3 lines&gt;...
-        max_evaluations
-        ^^^^^^^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
@@ -4027,7 +4101,16 @@
       </c>
       <c r="C52" s="10" t="str">
         <f>_xll.qlBondPrice(C46,"clean")</f>
-        <v>欣[test_bonds.xlsx]FixedRateBond!R52C3BondPrice,A</v>
+        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -4038,9 +4121,18 @@
         <f>_xll.qlBondYield2(B27,B52,"actual360","CONTINUOUS","annual")</f>
         <v>0.26236426417183883</v>
       </c>
-      <c r="C53" s="10">
+      <c r="C53" s="10" t="str">
         <f>_xll.qlBondYield2(C27,C52,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
+        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float': Expected cache string</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -4071,31 +4163,13 @@
       <c r="A56" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B56" s="10" t="str">
+      <c r="B56" s="10">
         <f>_xll.qlBondSettlementValue(B27)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C56" s="10" t="str">
+        <v>121.40429393805221</v>
+      </c>
+      <c r="C56" s="10">
         <f>_xll.qlBondSettlementValue(C27)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>127.36781301760961</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -4106,9 +4180,18 @@
         <f>_xll.qlBondSettlementValue2(B27,B46)</f>
         <v>121.40429393805221</v>
       </c>
-      <c r="C57" s="10">
+      <c r="C57" s="10" t="str">
         <f>_xll.qlBondSettlementValue2(C27,C46)</f>
-        <v>127.36781301760959</v>
+        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float</v>
       </c>
     </row>
   </sheetData>
@@ -4375,7 +4458,7 @@
         <v>73</v>
       </c>
       <c r="C26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -4562,7 +4645,7 @@
         <f>_xll.qlBondRedemption(B30)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 326, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 402, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -4575,7 +4658,7 @@
         <f>_xll.qlBondRedemption(C30)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 326, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 402, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -4708,18 +4791,9 @@
         <f>_xll.qlBondDirtyPrice(B30)</f>
         <v>116.28899295466947</v>
       </c>
-      <c r="C52" s="10" t="str">
+      <c r="C52" s="10">
         <f>_xll.qlBondDirtyPrice(C30)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 418, in qlBondDirtyPrice
-    return bond.dirtyPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
-    return _QuantLib.Bond_dirtyPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>115.0531622834792</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -4747,7 +4821,7 @@
         <f>_xll.qlBondYield(C30,"actual360","CONTINUOUS","annual")</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondYield
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
     return bond.bondYield(
            ~~~~~~~~~~~~~~^
         dc,
@@ -4818,31 +4892,13 @@
       <c r="A59" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B59" s="10" t="str">
+      <c r="B59" s="10">
         <f>_xll.qlBondSettlementValue(B30)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C59" s="10" t="str">
+        <v>174.43348943200422</v>
+      </c>
+      <c r="C59" s="10">
         <f>_xll.qlBondSettlementValue(C30)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>172.57974342521879</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -5192,7 +5248,7 @@
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R34C2AmortizingFloatingRateBond,A</v>
       </c>
       <c r="C34" s="3" t="str">
-        <f>_xll.qlAmortizingFloatingRateBond(C4,C5:C7,C16,C18,C19,C20,C21,C22,C23,,,C26,C27,C28,C29,C30,C31,C32,C33)</f>
+        <f>_xll.qlAmortizingFloatingRateBond(C4,C5:C7,C16,C18,C19,C20,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33)</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R34C3AmortizingFloatingRateBond,A</v>
       </c>
     </row>
@@ -5347,7 +5403,7 @@
         <f>_xll.qlBondRedemption(B34)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 326, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 402, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -5360,7 +5416,7 @@
         <f>_xll.qlBondRedemption(C34)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 326, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 402, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -5452,9 +5508,18 @@
       <c r="A53" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="10" t="str">
         <f>_xll.qlBondCleanPrice(B34)</f>
-        <v>99.997285121125458</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
       <c r="C53" s="10">
         <f>_xll.qlBondCleanPrice(C34)</f>
@@ -5489,9 +5554,18 @@
       <c r="A56" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="10" t="str">
         <f>_xll.qlBondDirtyPrice(B34)</f>
-        <v>100.16395178779213</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 511, in qlBondDirtyPrice
+    return bond.dirtyPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
+    return _QuantLib.Bond_dirtyPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
       <c r="C56" s="10">
         <f>_xll.qlBondDirtyPrice(C34)</f>
@@ -5515,15 +5589,11 @@
       <c r="A58" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="10" t="str">
         <f>_xll.qlBondYield(B34,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
-      </c>
-      <c r="C58" s="10" t="str">
-        <f>_xll.qlBondYield(C34,"actual360","CONTINUOUS","annual")</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondYield
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
     return bond.bondYield(
            ~~~~~~~~~~~~~~^
         dc,
@@ -5539,6 +5609,26 @@
 RuntimeError: null pricing engine
 </v>
       </c>
+      <c r="C58" s="10" t="str">
+        <f>_xll.qlBondYield(C34,"actual360","CONTINUOUS","annual")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
+    return bond.bondYield(
+           ~~~~~~~~~~~~~~^
+        dc,
+        ^^^
+    ...&lt;3 lines&gt;...
+        max_evaluations
+        ^^^^^^^^^^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
@@ -5546,7 +5636,16 @@
       </c>
       <c r="B59" s="10" t="str">
         <f>_xll.qlBondPrice(B53,"clean")</f>
-        <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R59C2BondPrice,A</v>
+        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float</v>
       </c>
       <c r="C59" s="10" t="str">
         <f>_xll.qlBondPrice(C53,"clean")</f>
@@ -5557,9 +5656,18 @@
       <c r="A60" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="10" t="str">
         <f>_xll.qlBondYield2(B34,B59,"actual360","CONTINUOUS","annual")</f>
-        <v>0.29158154279763698</v>
+        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float': Expected cache string</v>
       </c>
       <c r="C60" s="10">
         <f>_xll.qlBondYield2(C34,C59,"actual360","CONTINUOUS","annual")</f>
@@ -5598,7 +5706,7 @@
         <f>_xll.qlBondSettlementValue(B34)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 635, in qlBondSettlementValue
     return bond.settlementValue()
            ~~~~~~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
@@ -5616,9 +5724,18 @@
       <c r="A64" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B64" s="10" t="str">
         <f>_xll.qlBondSettlementValue2(B34,B53)</f>
-        <v>150.24592768168822</v>
+        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float</v>
       </c>
       <c r="C64" s="10">
         <f>_xll.qlBondSettlementValue2(C34,C53)</f>
@@ -5931,7 +6048,7 @@
         <v>欣[test_bonds.xlsx]FloatingRateBond!R31C2FloatingRateBond,A</v>
       </c>
       <c r="C31" s="3" t="str">
-        <f>_xll.qlFloatingRateBond(C4,C5,C14,C16,C17,C18,C19,C20,C21,,,C24,C25,C26,C27,C28,C29,C30)</f>
+        <f>_xll.qlFloatingRateBond(C4,C5,C14,C16,C17,C18,C19,C20,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30)</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R31C3FloatingRateBond,A</v>
       </c>
     </row>
@@ -6177,18 +6294,9 @@
         <f>_xll.qlBondCleanPrice(B31)</f>
         <v>99.998840118437755</v>
       </c>
-      <c r="C50" s="10" t="str">
+      <c r="C50" s="10">
         <f>_xll.qlBondCleanPrice(C31)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 380, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>100.51087441193772</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -6223,7 +6331,7 @@
         <f>_xll.qlBondDirtyPrice(B31)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 418, in qlBondDirtyPrice
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 511, in qlBondDirtyPrice
     return bond.dirtyPrice()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
@@ -6254,15 +6362,11 @@
       <c r="A55" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="10" t="str">
         <f>_xll.qlBondYield(B31,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
-      </c>
-      <c r="C55" s="10" t="str">
-        <f>_xll.qlBondYield(C31,"actual360","CONTINUOUS","annual")</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondYield
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
     return bond.bondYield(
            ~~~~~~~~~~~~~~^
         dc,
@@ -6278,74 +6382,51 @@
 RuntimeError: null pricing engine
 </v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B56" s="10" t="str">
-        <f>_xll.qlBondPrice(B50,"clean")</f>
-        <v>欣[test_bonds.xlsx]FloatingRateBond!R56C2BondPrice,A</v>
-      </c>
-      <c r="C56" s="10" t="str">
-        <f>_xll.qlBondPrice(C50,"clean")</f>
-        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+      <c r="C55" s="10" t="str">
+        <f>_xll.qlBondYield(C31,"actual360","CONTINUOUS","annual")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 380, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="10">
-        <f>_xll.qlBondYield2(B31,B56,"actual360","CONTINUOUS","annual")</f>
-        <v>0.29112129323880687</v>
-      </c>
-      <c r="C57" s="10" t="str">
-        <f>_xll.qlBondYield2(C31,C56,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">TypeError: TypeError: Wrong number or type of arguments for overloaded function 'Bond_bondYield'.
-  Possible C/C++ prototypes are:
-    Bond::yield(DayCounter const &amp;,Compounding,Frequency,Real,Size)
-    Bond::yield(DayCounter const &amp;,Compounding,Frequency,Real)
-    Bond::yield(DayCounter const &amp;,Compounding,Frequency)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real,Size,Real)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real,Size)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency)
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 505, in qlBondYield2
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
     return bond.bondYield(
            ~~~~~~~~~~~~~~^
-        price,
-        ^^^^^^
-    ...&lt;6 lines&gt;...
-        guess
-        ^^^^^
+        dc,
+        ^^^
+    ...&lt;3 lines&gt;...
+        max_evaluations
+        ^^^^^^^^^^^^^^^
     )
     ^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
     return _QuantLib.Bond_bondYield(self, *args)
            ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-TypeError: Wrong number or type of arguments for overloaded function 'Bond_bondYield'.
-  Possible C/C++ prototypes are:
-    Bond::yield(DayCounter const &amp;,Compounding,Frequency,Real,Size)
-    Bond::yield(DayCounter const &amp;,Compounding,Frequency,Real)
-    Bond::yield(DayCounter const &amp;,Compounding,Frequency)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real,Size,Real)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real,Size)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency)
+RuntimeError: null pricing engine
 </v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" s="10" t="str">
+        <f>_xll.qlBondPrice(B50,"clean")</f>
+        <v>欣[test_bonds.xlsx]FloatingRateBond!R56C2BondPrice,A</v>
+      </c>
+      <c r="C56" s="10" t="str">
+        <f>_xll.qlBondPrice(C50,"clean")</f>
+        <v>欣[test_bonds.xlsx]FloatingRateBond!R56C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="10">
+        <f>_xll.qlBondYield2(B31,B56,"actual360","CONTINUOUS","annual")</f>
+        <v>0.29112129323880687</v>
+      </c>
+      <c r="C57" s="10">
+        <f>_xll.qlBondYield2(C31,C56,"actual360","CONTINUOUS","annual")</f>
+        <v>0.21004909842705732</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -6380,7 +6461,7 @@
         <f>_xll.qlBondSettlementValue(B31)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 635, in qlBondSettlementValue
     return bond.settlementValue()
            ~~~~~~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
@@ -6393,7 +6474,7 @@
         <f>_xll.qlBondSettlementValue(C31)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 635, in qlBondSettlementValue
     return bond.settlementValue()
            ~~~~~~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
@@ -6411,18 +6492,9 @@
         <f>_xll.qlBondSettlementValue2(B31,B50)</f>
         <v>100.16550678510443</v>
       </c>
-      <c r="C61" s="10" t="str">
+      <c r="C61" s="10">
         <f>_xll.qlBondSettlementValue2(C31,C50)</f>
-        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 380, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float</v>
+        <v>93.177541078604392</v>
       </c>
     </row>
   </sheetData>
@@ -7063,15 +7135,11 @@
       <c r="A55" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="10" t="str">
         <f>_xll.qlBondCleanPrice(B36)</f>
-        <v>158.97331982635237</v>
-      </c>
-      <c r="C55" s="10" t="str">
-        <f>_xll.qlBondCleanPrice(C36)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 380, in qlBondCleanPrice
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
     return bond.cleanPrice()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
@@ -7080,6 +7148,10 @@
 RuntimeError: null pricing engine
 </v>
       </c>
+      <c r="C55" s="10">
+        <f>_xll.qlBondCleanPrice(C36)</f>
+        <v>89.639709460333037</v>
+      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
@@ -7113,7 +7185,7 @@
         <f>_xll.qlBondDirtyPrice(B36)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 418, in qlBondDirtyPrice
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 511, in qlBondDirtyPrice
     return bond.dirtyPrice()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
@@ -7122,18 +7194,9 @@
 RuntimeError: null pricing engine
 </v>
       </c>
-      <c r="C58" s="10" t="str">
+      <c r="C58" s="10">
         <f>_xll.qlBondDirtyPrice(C36)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 418, in qlBondDirtyPrice
-    return bond.dirtyPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
-    return _QuantLib.Bond_dirtyPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>89.639709460333037</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -7153,13 +7216,45 @@
       <c r="A60" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="10" t="str">
         <f>_xll.qlBondYield(B36,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
-      </c>
-      <c r="C60" s="10">
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
+    return bond.bondYield(
+           ~~~~~~~~~~~~~~^
+        dc,
+        ^^^
+    ...&lt;3 lines&gt;...
+        max_evaluations
+        ^^^^^^^^^^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+      <c r="C60" s="10" t="str">
         <f>_xll.qlBondYield(C36,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928265005463161</v>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
+    return bond.bondYield(
+           ~~~~~~~~~~~~~~^
+        dc,
+        ^^^
+    ...&lt;3 lines&gt;...
+        max_evaluations
+        ^^^^^^^^^^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -7168,13 +7263,9 @@
       </c>
       <c r="B61" s="10" t="str">
         <f>_xll.qlBondPrice(B55,"clean")</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R61C2BondPrice,A</v>
-      </c>
-      <c r="C61" s="10" t="str">
-        <f>_xll.qlBondPrice(C55,"clean")</f>
         <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 380, in qlBondCleanPrice
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
     return bond.cleanPrice()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
@@ -7183,52 +7274,31 @@
 RuntimeError: null pricing engine
 ': Expected float</v>
       </c>
+      <c r="C61" s="10" t="str">
+        <f>_xll.qlBondPrice(C55,"clean")</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R61C3BondPrice,A</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B62" s="10" t="str">
         <f>_xll.qlBondYield2(B36,B61,"actual360","CONTINUOUS","annual")</f>
-        <v>0.29367879784610279</v>
-      </c>
-      <c r="C62" s="10" t="str">
+        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float': Expected cache string</v>
+      </c>
+      <c r="C62" s="10">
         <f>_xll.qlBondYield2(C36,C61,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">TypeError: TypeError: Wrong number or type of arguments for overloaded function 'Bond_bondYield'.
-  Possible C/C++ prototypes are:
-    Bond::yield(DayCounter const &amp;,Compounding,Frequency,Real,Size)
-    Bond::yield(DayCounter const &amp;,Compounding,Frequency,Real)
-    Bond::yield(DayCounter const &amp;,Compounding,Frequency)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real,Size,Real)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real,Size)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency)
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 505, in qlBondYield2
-    return bond.bondYield(
-           ~~~~~~~~~~~~~~^
-        price,
-        ^^^^^^
-    ...&lt;6 lines&gt;...
-        guess
-        ^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-TypeError: Wrong number or type of arguments for overloaded function 'Bond_bondYield'.
-  Possible C/C++ prototypes are:
-    Bond::yield(DayCounter const &amp;,Compounding,Frequency,Real,Size)
-    Bond::yield(DayCounter const &amp;,Compounding,Frequency,Real)
-    Bond::yield(DayCounter const &amp;,Compounding,Frequency)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real,Size,Real)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real,Size)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;,Real)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency,Date const &amp;)
-    Bond::yield(BondPrice,DayCounter const &amp;,Compounding,Frequency)
-</v>
+        <v>0.28928265005463161</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -7263,7 +7333,7 @@
         <f>_xll.qlBondSettlementValue(B36)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 635, in qlBondSettlementValue
     return bond.settlementValue()
            ~~~~~~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
@@ -7276,7 +7346,7 @@
         <f>_xll.qlBondSettlementValue(C36)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 535, in qlBondSettlementValue
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 635, in qlBondSettlementValue
     return bond.settlementValue()
            ~~~~~~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
@@ -7290,15 +7360,11 @@
       <c r="A66" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B66" s="10" t="str">
         <f>_xll.qlBondSettlementValue2(B36,B55)</f>
-        <v>159.52887538190791</v>
-      </c>
-      <c r="C66" s="10" t="str">
-        <f>_xll.qlBondSettlementValue2(C36,C55)</f>
         <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 380, in qlBondCleanPrice
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
     return bond.cleanPrice()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
@@ -7307,6 +7373,10 @@
 RuntimeError: null pricing engine
 ': Expected float</v>
       </c>
+      <c r="C66" s="10">
+        <f>_xll.qlBondSettlementValue2(C36,C55)</f>
+        <v>89.639709460333037</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/tests/workbooks/test_bonds.xlsx
+++ b/tests/workbooks/test_bonds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FF61BC-DA5F-472D-B229-DD580FBE5AA5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD11E35-3656-452B-BDAE-A27D463BD4B8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="32370" windowHeight="9360" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="151">
   <si>
     <t>Bond</t>
   </si>
@@ -187,9 +187,6 @@
     <t>day counter</t>
   </si>
   <si>
-    <t>Actual360</t>
-  </si>
-  <si>
     <t>qlMakeSchedule</t>
   </si>
   <si>
@@ -283,9 +280,6 @@
     <t>Forward</t>
   </si>
   <si>
-    <t>actual360</t>
-  </si>
-  <si>
     <t>qlFixedRateBond</t>
   </si>
   <si>
@@ -443,6 +437,60 @@
   </si>
   <si>
     <t>qlCallabilityType</t>
+  </si>
+  <si>
+    <t>put_call_schedule</t>
+  </si>
+  <si>
+    <t>act/360</t>
+  </si>
+  <si>
+    <t>Put</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date </t>
+  </si>
+  <si>
+    <t>qlCallableFixedRateBond</t>
+  </si>
+  <si>
+    <t>qlBlackCallableFixedRateBondEngine</t>
+  </si>
+  <si>
+    <t>fwd_yield_vol</t>
+  </si>
+  <si>
+    <t>qlCallableBondCallability</t>
+  </si>
+  <si>
+    <t>qlCallableBondImpliedVolatility</t>
+  </si>
+  <si>
+    <t>qlCallableBondOAS</t>
+  </si>
+  <si>
+    <t>qlCallableBondCleanPriceOAS</t>
+  </si>
+  <si>
+    <t>qlCallableBondEffectiveDuration</t>
+  </si>
+  <si>
+    <t>qlCallableBondEffectiveConvexity</t>
+  </si>
+  <si>
+    <t>day_counter</t>
+  </si>
+  <si>
+    <t>qlCallableZeroCouponBond</t>
+  </si>
+  <si>
+    <t>UnAdjusted</t>
+  </si>
+  <si>
+    <t>12M</t>
+  </si>
+  <si>
+    <t>30/360</t>
   </si>
 </sst>
 </file>
@@ -452,7 +500,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,6 +537,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -624,7 +680,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -638,7 +694,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -671,12 +726,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1003,155 +1060,159 @@
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="16"/>
+    <col min="1" max="1" width="11.42578125" style="15"/>
     <col min="2" max="2" width="36.140625" customWidth="1"/>
     <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="33.85546875" customWidth="1"/>
     <col min="5" max="5" width="32.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="33"/>
+      <c r="E2" s="34"/>
+    </row>
+    <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="17"/>
+      <c r="C3" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="32" t="s">
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="33"/>
-    </row>
-    <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="18"/>
-      <c r="C3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="30"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="28"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="23"/>
+      <c r="B5" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="21"/>
+      <c r="E5" s="22"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="23"/>
+      <c r="C6" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="21"/>
+      <c r="E6" s="22"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23"/>
+      <c r="C7" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="23"/>
+      <c r="C8" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="21"/>
+      <c r="E8" s="22"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23"/>
+      <c r="C9" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23"/>
+      <c r="C10" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="21"/>
+      <c r="E10" s="22"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="23"/>
+      <c r="C11" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="21"/>
+      <c r="E11" s="22"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23"/>
+      <c r="C12" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="23"/>
+      <c r="B13" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="22"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="23"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="16" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="25"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1168,7 +1229,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.5703125" customWidth="1"/>
-    <col min="2" max="2" width="69.140625" customWidth="1"/>
+    <col min="2" max="2" width="73.85546875" customWidth="1"/>
     <col min="3" max="3" width="71.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1204,8 +1265,8 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
-        <v>84</v>
+      <c r="A5" s="35" t="s">
+        <v>82</v>
       </c>
       <c r="B5" s="3">
         <v>103</v>
@@ -1215,7 +1276,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="34"/>
+      <c r="A6" s="35"/>
       <c r="B6" s="3">
         <v>102</v>
       </c>
@@ -1224,7 +1285,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="3">
         <v>101</v>
       </c>
@@ -1234,24 +1295,24 @@
     </row>
     <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="12">
+        <v>73</v>
+      </c>
+      <c r="B8" s="11">
         <v>45665</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <v>45665</v>
       </c>
     </row>
     <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="12">
-        <v>46030</v>
-      </c>
-      <c r="C9" s="12">
-        <v>46030</v>
+        <v>74</v>
+      </c>
+      <c r="B9" s="11">
+        <v>49682</v>
+      </c>
+      <c r="C9" s="11">
+        <v>49682</v>
       </c>
     </row>
     <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -1259,15 +1320,15 @@
         <v>46</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" s="6" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
@@ -1283,37 +1344,37 @@
         <v>47</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B15" s="6">
         <v>0</v>
@@ -1324,7 +1385,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" s="3" t="str">
         <f>_xll.qlSchedule(B8,B9,B10,B11,B12,B13,B14,B15)</f>
@@ -1336,29 +1397,29 @@
       </c>
     </row>
     <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>103</v>
+      <c r="A17" s="13" t="s">
+        <v>101</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="13" t="s">
         <v>46</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="13" t="s">
         <v>14</v>
       </c>
       <c r="B19" s="6">
@@ -1369,19 +1430,19 @@
       </c>
     </row>
     <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>105</v>
+      <c r="A20" s="13" t="s">
+        <v>103</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>61</v>
+      <c r="A21" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="B21" s="6" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
@@ -1393,41 +1454,41 @@
       </c>
     </row>
     <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+      <c r="B24" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>111</v>
       </c>
       <c r="B25" s="6" t="str">
         <f>_xll.qlEuribor("3M")</f>
@@ -1439,8 +1500,8 @@
       </c>
     </row>
     <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>112</v>
+      <c r="A26" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="B26" s="6" t="str">
         <f>_xll.qlFlatForward(#REF!,0.03,"Actual360","Compounded","Quarterly")</f>
@@ -1453,7 +1514,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B27" s="3" t="str">
         <f>_xll.qlSwapIndex(B17,B18,B19,B20,B21,B22,B23,B24,B25,B26)</f>
@@ -1466,27 +1527,27 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3">
@@ -1494,8 +1555,8 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>93</v>
+      <c r="A31" s="12" t="s">
+        <v>91</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3">
@@ -1504,7 +1565,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3">
@@ -1512,8 +1573,8 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
-        <v>95</v>
+      <c r="A33" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3">
@@ -1521,8 +1582,8 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
-        <v>96</v>
+      <c r="A34" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3">
@@ -1531,7 +1592,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3">
@@ -1549,7 +1610,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B37" t="str">
         <f>_xll.qlAmortizingCmsRateBond(B4,B5:B7,B16,B27,B28)</f>
@@ -1587,16 +1648,16 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B40" s="2">
         <f>_xll.qlBondNextCashFlowDate(B37)</f>
-        <v>45755</v>
+        <v>46030</v>
       </c>
       <c r="C40" s="2">
         <f>_xll.qlBondNextCashFlowDate(C37)</f>
-        <v>45755</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1639,7 +1700,7 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B44" s="3" t="b">
@@ -1670,11 +1731,11 @@
       </c>
       <c r="B46" s="2">
         <f>_xll.qlBondMaturityDate(B37)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
       <c r="C46" s="2">
         <f>_xll.qlBondMaturityDate(C37)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1691,7 +1752,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="7" t="s">
         <v>30</v>
       </c>
       <c r="B48" s="3" t="str">
@@ -1705,13 +1766,13 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B49" s="3" t="str">
         <f>_xll.qlBondRedemption(B37)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 402, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 365, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -1724,7 +1785,7 @@
         <f>_xll.qlBondRedemption(C37)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 402, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 365, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -1736,7 +1797,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B50" s="3" t="str">
         <f>_xll.qlBondRedemptions(B37)</f>
@@ -1761,7 +1822,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B52" s="3">
@@ -1774,8 +1835,8 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
-        <v>60</v>
+      <c r="A53" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="B53" s="3">
         <f>_xll.qlBondNotionals(B37)</f>
@@ -1787,8 +1848,8 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
-        <v>56</v>
+      <c r="A54" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="B54" s="3" t="str">
         <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
@@ -1800,8 +1861,8 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
-        <v>52</v>
+      <c r="A55" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="B55" s="3" t="str">
         <f>_xll.qlBondSetDiscountingEngine(B37,B54)</f>
@@ -1813,153 +1874,110 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="9">
         <f>_xll.qlBondCleanPrice(B37)</f>
-        <v>74.994672295319077</v>
-      </c>
-      <c r="C56" s="10" t="str">
+        <v>5.159421325147961</v>
+      </c>
+      <c r="C56" s="9">
         <f>_xll.qlBondCleanPrice(C37)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>5.9932874425424671</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B57" s="10">
+      <c r="A57" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="9">
         <v>0.28928264971926221</v>
       </c>
-      <c r="C57" s="10">
+      <c r="C57" s="9">
         <v>0.28928264971926221</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="9">
         <f>_xll.qlBondCleanPrice2(B37,B57,"actual360","continuous")</f>
-        <v>74.994672041966595</v>
-      </c>
-      <c r="C58" s="10">
+        <v>5.1594211712767493</v>
+      </c>
+      <c r="C58" s="9">
         <f>_xll.qlBondCleanPrice2(C37,C57,"actual360","continuous")</f>
-        <v>75.244545721623112</v>
+        <v>5.9932872787070313</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="9">
         <f>_xll.qlBondDirtyPrice(B37)</f>
-        <v>74.994672295319077</v>
-      </c>
-      <c r="C59" s="10">
+        <v>5.159421325147961</v>
+      </c>
+      <c r="C59" s="9">
         <f>_xll.qlBondDirtyPrice(C37)</f>
-        <v>75.246212642157701</v>
+        <v>5.9949541092091447</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="9">
         <f>_xll.qlBondDirtyPrice2(B37,B57,"actual360","CONTINUOUS","annual")</f>
-        <v>74.994672041966595</v>
-      </c>
-      <c r="C60" s="10">
+        <v>5.1594211712767493</v>
+      </c>
+      <c r="C60" s="9">
         <f>_xll.qlBondDirtyPrice2(C37,C57,"actual360","CONTINUOUS","annual")</f>
-        <v>75.246212388289791</v>
+        <v>5.9949539453737088</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B61" s="9">
         <f>_xll.qlBondYield(B37,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264826921379</v>
-      </c>
-      <c r="C61" s="10" t="str">
+        <v>0.28928264139762888</v>
+      </c>
+      <c r="C61" s="9">
         <f>_xll.qlBondYield(C37,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
-    return bond.bondYield(
-           ~~~~~~~~~~~~~~^
-        dc,
-        ^^^
-    ...&lt;3 lines&gt;...
-        max_evaluations
-        ^^^^^^^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>0.28928264388044844</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B62" s="10" t="str">
+      <c r="A62" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B62" s="9" t="str">
         <f>_xll.qlBondPrice(B56,"clean")</f>
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R62C2BondPrice,A</v>
       </c>
-      <c r="C62" s="10" t="str">
+      <c r="C62" s="9" t="str">
         <f>_xll.qlBondPrice(C56,"clean")</f>
-        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float</v>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R62C3BondPrice,A</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B63" s="9">
         <f>_xll.qlBondYield2(B37,B62,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264826921379</v>
-      </c>
-      <c r="C63" s="10" t="str">
+        <v>0.28928264139762888</v>
+      </c>
+      <c r="C63" s="9">
         <f>_xll.qlBondYield2(C37,C62,"actual360","CONTINUOUS","annual")</f>
-        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float': Expected cache string</v>
+        <v>0.28931725029223304</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="11" t="s">
-        <v>55</v>
+      <c r="A64" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="B64" s="2">
         <v>45667</v>
@@ -1969,60 +1987,42 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="9">
         <f>_xll.qlBondAccruedAmount(B37,B64)</f>
         <v>0</v>
       </c>
-      <c r="C65" s="10">
+      <c r="C65" s="9">
         <f>_xll.qlBondAccruedAmount(C37,C64)</f>
         <v>1.6666666666775853E-3</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B66" s="9">
         <f>_xll.qlBondSettlementValue(B37)</f>
-        <v>77.244512464178641</v>
-      </c>
-      <c r="C66" s="10" t="str">
+        <v>5.3142039649023998</v>
+      </c>
+      <c r="C66" s="9">
         <f>_xll.qlBondSettlementValue(C37)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 635, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>6.1748027324854196</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="9">
         <f>_xll.qlBondSettlementValue2(B37,B56)</f>
-        <v>77.244512464178655</v>
-      </c>
-      <c r="C67" s="10" t="str">
+        <v>5.3142039649023998</v>
+      </c>
+      <c r="C67" s="9">
         <f>_xll.qlBondSettlementValue2(C37,C56)</f>
-        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float</v>
+        <v>6.1748027324854187</v>
       </c>
     </row>
   </sheetData>
@@ -2045,7 +2045,7 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B3" s="3" t="str">
         <f>_xll.qlBondPrice(100,"clean")</f>
@@ -2054,15 +2054,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B5" s="2">
         <v>46357</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B6" s="3" t="str">
         <f>_xll.qlCallability(B3,B4,B5)</f>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B7" s="3" t="str">
         <f>_xll.qlCallabilityPrice(B6)</f>
@@ -2088,7 +2088,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B8" s="2">
         <f>_xll.qlCallabilityDate(B6)</f>
@@ -2097,7 +2097,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B9" s="3" t="str">
         <f>_xll.qlCallabilityType(B6)</f>
@@ -2114,18 +2114,1729 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F0A1FE9-B1FE-4762-AEA9-E4B3F6C519F7}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="47.7109375" customWidth="1"/>
+    <col min="2" max="2" width="93.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="75.28515625" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2">
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="11">
+        <v>45665</v>
+      </c>
+      <c r="C6" s="11">
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="11">
+        <v>49682</v>
+      </c>
+      <c r="C7" s="11">
+        <v>49682</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="6" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C9" s="6" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="6">
+        <v>0</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="3" t="str">
+        <f>_xll.qlSchedule(B6,B7,B8,B9,B10,B11,B12,B13)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R14C2Schedule,A</v>
+      </c>
+      <c r="C14" s="3" t="str">
+        <f>_xll.qlSchedule(C6,C7,C8,C9,C10,C11,C12,C13)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R14C3Schedule,A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="35"/>
+      <c r="B16" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="35"/>
+      <c r="B17" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2">
+        <v>45665</v>
+      </c>
+      <c r="C21" s="2">
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" s="2" t="str">
+        <f>_xll.qlBondPrice(100,"CLEAN")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R22C2BondPrice,A</v>
+      </c>
+      <c r="C22" s="2" t="str">
+        <f>_xll.qlBondPrice(100,"CLEAN")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R22C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" s="2">
+        <v>47664</v>
+      </c>
+      <c r="C24" s="2">
+        <v>47664</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" s="3" t="str">
+        <f>_xll.qlCallability(B22,B23,B24)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R25C2Callability,A</v>
+      </c>
+      <c r="C25" s="3" t="str">
+        <f>_xll.qlCallability(C22,C23,C24)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R25C3Callability,A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="3" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" s="3" t="str">
+        <f>_xll.qlCallableFixedRateBond(B4,B5,B14,B15:B17,B18,B19,B20,B21,B25)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R30C2CallableFixedRateBond,A</v>
+      </c>
+      <c r="C30" s="3" t="str">
+        <f>_xll.qlCallableFixedRateBond(C4,C5,C14,C15:C17,C18,C19,C20,C21,C25,C26,C27,C28,C29)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R30C3CallableFixedRateBond,A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="3">
+        <f>_xll.qlBondNextCouponRate(B30)</f>
+        <v>0.4</v>
+      </c>
+      <c r="C31" s="3">
+        <f>_xll.qlBondNextCouponRate(C30)</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" s="3">
+        <f>_xll.qlBondPreviousCouponRate(B30)</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="3">
+        <f>_xll.qlBondPreviousCouponRate(C30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="2">
+        <f>_xll.qlBondNextCashFlowDate(B30)</f>
+        <v>46030</v>
+      </c>
+      <c r="C33" s="2">
+        <f>_xll.qlBondNextCashFlowDate(C30)</f>
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="2">
+        <f>_xll.qlBondPreviousCashFlowDate(B30)</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
+        <f>_xll.qlBondPreviousCashFlowDate(C30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="3">
+        <f>_xll.qlBondSettlementDays(B30)</f>
+        <v>2</v>
+      </c>
+      <c r="C35" s="3">
+        <f>_xll.qlBondSettlementDays(C30)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" s="2">
+        <f>_xll.qlBondSettlementDate(B30)</f>
+        <v>45667</v>
+      </c>
+      <c r="C36" s="2">
+        <f>_xll.qlBondSettlementDate(C30)</f>
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="3" t="b">
+        <f>_xll.qlBondIsTradable(B30)</f>
+        <v>1</v>
+      </c>
+      <c r="C37" s="3" t="b">
+        <f>_xll.qlBondIsTradable(C30)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" s="2">
+        <f>_xll.qlBondStartDate(B30)</f>
+        <v>45665</v>
+      </c>
+      <c r="C38" s="2">
+        <f>_xll.qlBondStartDate(C30)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" s="2">
+        <f>_xll.qlBondMaturityDate(B30)</f>
+        <v>49682</v>
+      </c>
+      <c r="C39" s="2">
+        <f>_xll.qlBondMaturityDate(C30)</f>
+        <v>49682</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="2">
+        <f>_xll.qlBondIssueDate(B30)</f>
+        <v>45665</v>
+      </c>
+      <c r="C40" s="2">
+        <f>_xll.qlBondIssueDate(C30)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B41" s="3" t="str">
+        <f>_xll.qlBondCashFlows(B30)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R41C2CashFlow,A</v>
+      </c>
+      <c r="C41" s="3" t="str">
+        <f>_xll.qlBondCashFlows(C30)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R41C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" s="3" t="str">
+        <f>_xll.qlBondRedemption(B30)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R42C2CashFlow,A</v>
+      </c>
+      <c r="C42" s="3" t="str">
+        <f>_xll.qlBondRedemption(C30)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R42C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" s="3" t="str">
+        <f>_xll.qlBondRedemptions(B30)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R43C2CashFlow,A</v>
+      </c>
+      <c r="C43" s="3" t="str">
+        <f>_xll.qlBondRedemptions(C30)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R43C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" s="3" t="str">
+        <f>_xll.qlBondCalendar(B30)</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C44" s="3" t="str">
+        <f>_xll.qlBondCalendar(C30)</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" s="3">
+        <f>_xll.qlBondNotional(B30)</f>
+        <v>100</v>
+      </c>
+      <c r="C45" s="3">
+        <f>_xll.qlBondNotional(C30)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="3">
+        <f>_xll.qlBondNotionals(B30)</f>
+        <v>100</v>
+      </c>
+      <c r="C46" s="3">
+        <f>_xll.qlBondNotionals(C30)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="B47" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="C47" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" s="3" t="str">
+        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R48C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C48" s="3" t="str">
+        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R48C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B49" s="3" t="e">
+        <f>_xll.qlBlackCallableFixedRateBondEngine(B30,B47,B48)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C49" s="3" t="e">
+        <f>_xll.qlBlackCallableFixedRateBondEngine(C30,C47,C48)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" s="9">
+        <f>_xll.qlBondCleanPrice(B30)</f>
+        <v>148.46385265411533</v>
+      </c>
+      <c r="C50" s="9">
+        <f>_xll.qlBondCleanPrice(C30)</f>
+        <v>150.59646745144829</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="9">
+        <v>0.28928264971926221</v>
+      </c>
+      <c r="C51" s="9">
+        <v>0.28928264971926221</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" s="9">
+        <f>_xll.qlBondCleanPrice2(B30,B51,"actual360","continuous")</f>
+        <v>148.46385071667095</v>
+      </c>
+      <c r="C52" s="9">
+        <f>_xll.qlBondCleanPrice2(C30,C51,"actual360","continuous")</f>
+        <v>150.59646548594415</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B53" s="9">
+        <f>_xll.qlBondDirtyPrice(B30)</f>
+        <v>148.68607487633753</v>
+      </c>
+      <c r="C53" s="9">
+        <f>_xll.qlBondDirtyPrice(C30)</f>
+        <v>150.81868967367049</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B54" s="9">
+        <f>_xll.qlBondDirtyPrice2(B30,B51,"actual360","CONTINUOUS","annual")</f>
+        <v>148.68607293889315</v>
+      </c>
+      <c r="C54" s="9">
+        <f>_xll.qlBondDirtyPrice2(C30,C51,"actual360","CONTINUOUS","annual")</f>
+        <v>150.81868770816635</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="9">
+        <f>_xll.qlBondYield(B30,"actual360","CONTINUOUS","annual")</f>
+        <v>0.28928264971926221</v>
+      </c>
+      <c r="C55" s="9">
+        <f>_xll.qlBondYield(C30,"actual360","CONTINUOUS","annual")</f>
+        <v>0.28928264971926221</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B56" s="9" t="str">
+        <f>_xll.qlBondPrice(B50,"clean")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R56C2BondPrice,A</v>
+      </c>
+      <c r="C56" s="9" t="str">
+        <f>_xll.qlBondPrice(C50,"clean")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R56C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="9">
+        <f>_xll.qlBondYield2(B30,B56,"actual360","CONTINUOUS","annual")</f>
+        <v>0.28967312533166412</v>
+      </c>
+      <c r="C57" s="9">
+        <f>_xll.qlBondYield2(C30,C56,"actual360","CONTINUOUS","annual")</f>
+        <v>0.28966754837324626</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B58" s="2">
+        <v>45667</v>
+      </c>
+      <c r="C58" s="2">
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B59" s="9">
+        <f>_xll.qlBondAccruedAmount(B30,B58)</f>
+        <v>0.22222222222221255</v>
+      </c>
+      <c r="C59" s="9">
+        <f>_xll.qlBondAccruedAmount(C30,C58)</f>
+        <v>0.22222222222221255</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="9">
+        <f>_xll.qlBondSettlementValue(B30)</f>
+        <v>148.68607487633753</v>
+      </c>
+      <c r="C60" s="9">
+        <f>_xll.qlBondSettlementValue(C30)</f>
+        <v>150.81868967367049</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="9">
+        <f>_xll.qlBondSettlementValue2(B30,B50)</f>
+        <v>148.68607487633753</v>
+      </c>
+      <c r="C61" s="9">
+        <f>_xll.qlBondSettlementValue2(C30,C50)</f>
+        <v>150.81868967367049</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" s="3" t="str">
+        <f>_xll.qlCallableBondCallability(B30)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R62C2Callability,A</v>
+      </c>
+      <c r="C62" s="3" t="str">
+        <f>_xll.qlCallableBondCallability(C30)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R62C3Callability,A</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="32" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="B64" s="3" t="str">
+        <f>_xll.qlCallableBondOAS(B30,43.82,B48,"Actual/360","Simple","Annual",,,1000)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations (last bracket attempt: f[-6.54557e+272,1.70185e+273] -&gt; [-104.405,-104.405])
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1118, in qlCallableBondOAS
+    return callable_bond.OAS(
+           ~~~~~~~~~~~~~~~~~^
+        clean_price,
+        ^^^^^^^^^^^^
+    ...&lt;7 lines&gt;...
+        guess,
+        ^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26304, in OAS
+    return _QuantLib.CallableBond_OAS(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: unable to bracket root in 1000 function evaluations (last bracket attempt: f[-6.54557e+272,1.70185e+273] -&gt; [-104.405,-104.405])
+</v>
+      </c>
+      <c r="C64" s="3" t="str">
+        <f>_xll.qlCallableBondOAS(C30,43.82,C48,"Actual/360","Simple","Annual",,,1000)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations (last bracket attempt: f[-6.54557e+272,1.70185e+273] -&gt; [-106.534,-106.534])
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1118, in qlCallableBondOAS
+    return callable_bond.OAS(
+           ~~~~~~~~~~~~~~~~~^
+        clean_price,
+        ^^^^^^^^^^^^
+    ...&lt;7 lines&gt;...
+        guess,
+        ^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26304, in OAS
+    return _QuantLib.CallableBond_OAS(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: unable to bracket root in 1000 function evaluations (last bracket attempt: f[-6.54557e+272,1.70185e+273] -&gt; [-106.534,-106.534])
+</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B65" s="3" t="str">
+        <f>_xll.qlCallableBondCleanPriceOAS(B30,0.3,B48,"actual/360","simple","annual")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: Boost assertion failed: px != 0
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1153, in qlCallableBondCleanPriceOAS
+    return callable_bond.cleanPriceOAS(
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~^
+        oas,
+        ^^^^
+    ...&lt;4 lines&gt;...
+        settlement_date,
+        ^^^^^^^^^^^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26308, in cleanPriceOAS
+    return _QuantLib.CallableBond_cleanPriceOAS(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Boost assertion failed: px != 0
+</v>
+      </c>
+      <c r="C65" s="3">
+        <f>_xll.qlCallableBondCleanPriceOAS(C30,0.3,C48,"actual/360","simple","annual")</f>
+        <v>150.35427750919169</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B66" s="3" t="str">
+        <f>_xll.qlCallableBondEffectiveDuration(B30,0.3,B48,"actual/360","simple","quarterly")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: Boost assertion failed: px != 0
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1185, in qlCallableBondEffectiveDuration
+    return callable_bond.effectiveDuration(
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^
+        oas,
+        ^^^^
+    ...&lt;4 lines&gt;...
+        bump,
+        ^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26312, in effectiveDuration
+    return _QuantLib.CallableBond_effectiveDuration(self, oas, engineTS, dayCounter, compounding, frequency, bump)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+RuntimeError: Boost assertion failed: px != 0
+</v>
+      </c>
+      <c r="C66" s="3">
+        <f>_xll.qlCallableBondEffectiveDuration(C30,0.3,C48,"actual/360","simple","quarterly")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B67" s="3" t="str">
+        <f>_xll.qlCallableBondEffectiveConvexity(B30,0.3,B48,"actual/360","simple","quarterly")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: Boost assertion failed: px != 0
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1217, in qlCallableBondEffectiveConvexity
+    return callable_bond.effectiveConvexity(
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^
+        oas,
+        ^^^^
+    ...&lt;4 lines&gt;...
+        bump,
+        ^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26316, in effectiveConvexity
+    return _QuantLib.CallableBond_effectiveConvexity(self, oas, engineTS, dayCounter, compounding, frequency, bump)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+RuntimeError: Boost assertion failed: px != 0
+</v>
+      </c>
+      <c r="C67" s="3">
+        <f>_xll.qlCallableBondEffectiveConvexity(C30,0.3,C48,"actual/360","simple","quarterly")</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:A17"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4EF9C2-FD4D-4E7F-8154-C8E782972C6B}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="44.140625" customWidth="1"/>
+    <col min="2" max="2" width="89.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="73.28515625" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2">
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="3" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C6" s="3" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2">
+        <v>49682</v>
+      </c>
+      <c r="C7" s="2">
+        <v>49682</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2">
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2" t="str">
+        <f>_xll.qlBondPrice(100,"CLEAN")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R12C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2">
+        <v>47664</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="3" t="str">
+        <f>_xll.qlCallability(C12,C13,C14)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R15C3Callability,A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" s="3" t="str">
+        <f>_xll.qlCallableZeroCouponBond(B4,B5,B6,B7,B8)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R16C2CallableZeroCouponBond,A</v>
+      </c>
+      <c r="C16" s="3" t="str">
+        <f>_xll.qlCallableZeroCouponBond(C4,C5,C6,C7,C8,C9,C10,C11,C15)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R16C3CallableZeroCouponBond,A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="3" t="str">
+        <f>_xll.qlBondNextCouponRate(B16)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 231, in qlBondNextCouponRate
+    return bond.nextCouponRate(date)
+           ~~~~~~~~~~~~~~~~~~~^^^^^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
+    return _QuantLib.Bond_nextCouponRate(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: no coupon paid at cashflow date January 8th, 2036
+</v>
+      </c>
+      <c r="C17" s="3" t="str">
+        <f>_xll.qlBondNextCouponRate(C16)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 231, in qlBondNextCouponRate
+    return bond.nextCouponRate(date)
+           ~~~~~~~~~~~~~~~~~~~^^^^^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
+    return _QuantLib.Bond_nextCouponRate(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: no coupon paid at cashflow date January 8th, 2036
+</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="3">
+        <f>_xll.qlBondPreviousCouponRate(B16)</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="3">
+        <f>_xll.qlBondPreviousCouponRate(C16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="2">
+        <f>_xll.qlBondNextCashFlowDate(B16)</f>
+        <v>49682</v>
+      </c>
+      <c r="C19" s="2">
+        <f>_xll.qlBondNextCashFlowDate(C16)</f>
+        <v>49682</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="2">
+        <f>_xll.qlBondPreviousCashFlowDate(B16)</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <f>_xll.qlBondPreviousCashFlowDate(C16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="3">
+        <f>_xll.qlBondSettlementDays(B16)</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="3">
+        <f>_xll.qlBondSettlementDays(C16)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="2">
+        <f>_xll.qlBondSettlementDate(B16)</f>
+        <v>45667</v>
+      </c>
+      <c r="C22" s="2">
+        <f>_xll.qlBondSettlementDate(C16)</f>
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <f>_xll.qlBondIsTradable(B16)</f>
+        <v>1</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <f>_xll.qlBondIsTradable(C16)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="2">
+        <f>_xll.qlBondStartDate(B16)</f>
+        <v>49682</v>
+      </c>
+      <c r="C24" s="2">
+        <f>_xll.qlBondStartDate(C16)</f>
+        <v>49682</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="2">
+        <f>_xll.qlBondMaturityDate(B16)</f>
+        <v>49682</v>
+      </c>
+      <c r="C25" s="2">
+        <f>_xll.qlBondMaturityDate(C16)</f>
+        <v>49682</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="2">
+        <f>_xll.qlBondIssueDate(B16)</f>
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
+        <f>_xll.qlBondIssueDate(C16)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="3" t="str">
+        <f>_xll.qlBondCashFlows(B16)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R27C2CashFlow,A</v>
+      </c>
+      <c r="C27" s="3" t="str">
+        <f>_xll.qlBondCashFlows(C16)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R27C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="3" t="str">
+        <f>_xll.qlBondRedemption(B16)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R28C2CashFlow,A</v>
+      </c>
+      <c r="C28" s="3" t="str">
+        <f>_xll.qlBondRedemption(C16)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R28C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="3" t="str">
+        <f>_xll.qlBondRedemptions(B16)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R29C2CashFlow,A</v>
+      </c>
+      <c r="C29" s="3" t="str">
+        <f>_xll.qlBondRedemptions(C16)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R29C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="3" t="str">
+        <f>_xll.qlBondCalendar(B16)</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C30" s="3" t="str">
+        <f>_xll.qlBondCalendar(C16)</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="3">
+        <f>_xll.qlBondNotional(B16)</f>
+        <v>100</v>
+      </c>
+      <c r="C31" s="3">
+        <f>_xll.qlBondNotional(C16)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="3">
+        <f>_xll.qlBondNotionals(B16)</f>
+        <v>100</v>
+      </c>
+      <c r="C32" s="3">
+        <f>_xll.qlBondNotionals(C16)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="B33" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="B34" s="3" t="str">
+        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R34C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C34" s="3" t="str">
+        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R34C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="3" t="e">
+        <f>_xll.qlBlackCallableFixedRateBondEngine(B16,B33,B34)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C35" s="3" t="e">
+        <f>_xll.qlBlackCallableFixedRateBondEngine(C16,C33,C34)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" s="9" t="str">
+        <f>_xll.qlBondCleanPrice(B16)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 422, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+</v>
+      </c>
+      <c r="C36" s="9" t="str">
+        <f>_xll.qlBondCleanPrice(C16)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 422, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="9">
+        <v>0.28928264971926221</v>
+      </c>
+      <c r="C37" s="9">
+        <v>0.28928264971926221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" s="9">
+        <f>_xll.qlBondCleanPrice2(B16,B37,"actual360","continuous")</f>
+        <v>3.9703929859425657</v>
+      </c>
+      <c r="C38" s="9">
+        <f>_xll.qlBondCleanPrice2(C16,C37,"actual360","continuous")</f>
+        <v>3.9703929859425661E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="9" t="str">
+        <f>_xll.qlBondDirtyPrice(B16)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 457, in qlBondDirtyPrice
+    return bond.dirtyPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
+    return _QuantLib.Bond_dirtyPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+</v>
+      </c>
+      <c r="C39" s="9" t="str">
+        <f>_xll.qlBondDirtyPrice(C16)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 457, in qlBondDirtyPrice
+    return bond.dirtyPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
+    return _QuantLib.Bond_dirtyPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="9">
+        <f>_xll.qlBondDirtyPrice2(B16,B37,"actual360","CONTINUOUS","annual")</f>
+        <v>3.9703929859425657</v>
+      </c>
+      <c r="C40" s="9">
+        <f>_xll.qlBondDirtyPrice2(C16,C37,"actual360","CONTINUOUS","annual")</f>
+        <v>3.9703929859425661E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="9" t="str">
+        <f>_xll.qlBondYield(B16,"actual360","CONTINUOUS","annual")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 505, in qlBondYield
+    return bond.bondYield(dc, compounding, freq, accuracy, max_evaluations)
+           ~~~~~~~~~~~~~~^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+</v>
+      </c>
+      <c r="C41" s="9" t="str">
+        <f>_xll.qlBondYield(C16,"actual360","CONTINUOUS","annual")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 505, in qlBondYield
+    return bond.bondYield(dc, compounding, freq, accuracy, max_evaluations)
+           ~~~~~~~~~~~~~~^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B42" s="9" t="str">
+        <f>_xll.qlBondPrice(B36,"clean")</f>
+        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 422, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+': Expected float</v>
+      </c>
+      <c r="C42" s="9" t="str">
+        <f>_xll.qlBondPrice(C36,"clean")</f>
+        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 422, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="9" t="str">
+        <f>_xll.qlBondYield2(B16,B42,"actual360","CONTINUOUS","annual")</f>
+        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 422, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+': Expected float': Expected cache string</v>
+      </c>
+      <c r="C43" s="9" t="str">
+        <f>_xll.qlBondYield2(C16,C42,"actual360","CONTINUOUS","annual")</f>
+        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 422, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float': Expected cache string</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="2">
+        <v>45667</v>
+      </c>
+      <c r="C44" s="2">
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="9">
+        <f>_xll.qlBondAccruedAmount(B16,B44)</f>
+        <v>0</v>
+      </c>
+      <c r="C45" s="9">
+        <f>_xll.qlBondAccruedAmount(C16,C44)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="9" t="str">
+        <f>_xll.qlBondSettlementValue(B16)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 562, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+</v>
+      </c>
+      <c r="C46" s="9" t="str">
+        <f>_xll.qlBondSettlementValue(C16)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 562, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="9" t="str">
+        <f>_xll.qlBondSettlementValue2(B16,B36)</f>
+        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 422, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+': Expected float</v>
+      </c>
+      <c r="C47" s="9" t="str">
+        <f>_xll.qlBondSettlementValue2(C16,C36)</f>
+        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 422, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+': Expected float</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B48" s="3">
+        <f>_xll.qlCallableBondCallability(B16)</f>
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="str">
+        <f>_xll.qlCallableBondCallability(C16)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R48C3Callability,A</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="B50" s="3" t="str">
+        <f>_xll.qlCallableBondOAS(B16,43.82,B34,"Actual/360","Simple","Annual")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1118, in qlCallableBondOAS
+    return callable_bond.OAS(
+           ~~~~~~~~~~~~~~~~~^
+        clean_price,
+        ^^^^^^^^^^^^
+    ...&lt;7 lines&gt;...
+        guess,
+        ^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26304, in OAS
+    return _QuantLib.CallableBond_OAS(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+</v>
+      </c>
+      <c r="C50" s="3" t="str">
+        <f>_xll.qlCallableBondOAS(C16,43.82,C34,"Actual/360","Simple","Annual")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: unable to bracket root in 100 function evaluations (last bracket attempt: f[-6.79107e+23,1.76568e+24] -&gt; [43.7804,43.7804])
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1118, in qlCallableBondOAS
+    return callable_bond.OAS(
+           ~~~~~~~~~~~~~~~~~^
+        clean_price,
+        ^^^^^^^^^^^^
+    ...&lt;7 lines&gt;...
+        guess,
+        ^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26304, in OAS
+    return _QuantLib.CallableBond_OAS(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: unable to bracket root in 100 function evaluations (last bracket attempt: f[-6.79107e+23,1.76568e+24] -&gt; [43.7804,43.7804])
+</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="B51" s="3" t="str">
+        <f>_xll.qlCallableBondCleanPriceOAS(B16,0.3,B34,"actual/360","simple","annual")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1153, in qlCallableBondCleanPriceOAS
+    return callable_bond.cleanPriceOAS(
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~^
+        oas,
+        ^^^^
+    ...&lt;4 lines&gt;...
+        settlement_date,
+        ^^^^^^^^^^^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26308, in cleanPriceOAS
+    return _QuantLib.CallableBond_cleanPriceOAS(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+</v>
+      </c>
+      <c r="C51" s="3">
+        <f>_xll.qlCallableBondCleanPriceOAS(C16,0.3,C34,"actual/360","simple","annual")</f>
+        <v>3.9640173399601616E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B52" s="3" t="str">
+        <f>_xll.qlCallableBondEffectiveDuration(B16,0.3,B34,"actual/360","simple","quarterly")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1185, in qlCallableBondEffectiveDuration
+    return callable_bond.effectiveDuration(
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^
+        oas,
+        ^^^^
+    ...&lt;4 lines&gt;...
+        bump,
+        ^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26312, in effectiveDuration
+    return _QuantLib.CallableBond_effectiveDuration(self, oas, engineTS, dayCounter, compounding, frequency, bump)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+</v>
+      </c>
+      <c r="C52" s="3">
+        <f>_xll.qlCallableBondEffectiveDuration(C16,0.3,C34,"actual/360","simple","quarterly")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B53" s="3" t="str">
+        <f>_xll.qlCallableBondEffectiveConvexity(B16,0.3,B34,"actual/360","simple","quarterly")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1217, in qlCallableBondEffectiveConvexity
+    return callable_bond.effectiveConvexity(
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^
+        oas,
+        ^^^^
+    ...&lt;4 lines&gt;...
+        bump,
+        ^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26316, in effectiveConvexity
+    return _QuantLib.CallableBond_effectiveConvexity(self, oas, engineTS, dayCounter, compounding, frequency, bump)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+</v>
+      </c>
+      <c r="C53" s="3">
+        <f>_xll.qlCallableBondEffectiveConvexity(C16,0.3,C34,"actual/360","simple","quarterly")</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2150,7 +3861,7 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B3" s="3">
         <v>100</v>
@@ -2158,15 +3869,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B5" s="3" t="str">
         <f>_xll.qlBondPrice(B3,B4)</f>
@@ -2175,7 +3886,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B6" s="3">
         <f>_xll.qlBondPriceAmount(B5)</f>
@@ -2184,7 +3895,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B7" s="3" t="str">
         <f>_xll.qlBondPriceType(B5)</f>
@@ -2193,7 +3904,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B8" s="3" t="b">
         <f>_xll.qlBondPriceIsValid(B5)</f>
@@ -2224,7 +3935,7 @@
       <c r="B1" s="2">
         <v>45665</v>
       </c>
-      <c r="E1" s="9"/>
+      <c r="E1" s="8"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -2242,7 +3953,7 @@
       <c r="A4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C4" s="6"/>
@@ -2251,7 +3962,7 @@
       <c r="A5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="11">
         <v>45665</v>
       </c>
       <c r="C5" s="6"/>
@@ -2260,9 +3971,9 @@
       <c r="A6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="7">
-        <f t="array" ref="B6">_xll.qlCalendarAdvance2(B4,B5,"2y","following")</f>
-        <v>46395</v>
+      <c r="B6" s="11">
+        <f>_xll.qlCalendarAdvance2(B4,B5,"10y","following")</f>
+        <v>49317</v>
       </c>
       <c r="C6" s="6"/>
     </row>
@@ -2270,8 +3981,8 @@
       <c r="A7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>53</v>
+      <c r="B7" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="C7" s="6"/>
     </row>
@@ -2279,8 +3990,8 @@
       <c r="A8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>54</v>
+      <c r="B8" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="C8" s="6"/>
     </row>
@@ -2288,16 +3999,16 @@
       <c r="A9" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>49</v>
+      <c r="B9" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="C9" s="6"/>
     </row>
     <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="5" t="str">
+        <v>49</v>
+      </c>
+      <c r="B10" s="6" t="str">
         <f>_xll.qlMakeSchedule(B5,B6, "12M","annual",B4,B8,B8,"Forward",0)</f>
         <v>欣[test_bonds.xlsx]Bond!R10C2Schedule,A</v>
       </c>
@@ -2305,26 +4016,26 @@
     </row>
     <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
-      <c r="B11" s="5">
+      <c r="B11" s="6">
         <v>100</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="6">
         <v>0.03</v>
       </c>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
-      <c r="B12" s="5">
+      <c r="B12" s="6">
         <f t="shared" ref="B12:B18" si="0">B11+1</f>
         <v>101</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="6">
         <v>0.02</v>
       </c>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
-      <c r="B13" s="5">
+      <c r="B13" s="6">
         <f t="shared" si="0"/>
         <v>102</v>
       </c>
@@ -2332,7 +4043,7 @@
     </row>
     <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
-      <c r="B14" s="5">
+      <c r="B14" s="6">
         <f t="shared" si="0"/>
         <v>103</v>
       </c>
@@ -2340,7 +4051,7 @@
     </row>
     <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="5">
+      <c r="B15" s="6">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
@@ -2348,7 +4059,7 @@
     </row>
     <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="5">
+      <c r="B16" s="6">
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
@@ -2356,7 +4067,7 @@
     </row>
     <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
-      <c r="B17" s="5">
+      <c r="B17" s="6">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
@@ -2364,7 +4075,7 @@
     </row>
     <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
-      <c r="B18" s="5">
+      <c r="B18" s="6">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
@@ -2418,7 +4129,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" s="3" t="str">
         <f>_xll.qlFixedRateLeg(B10,B9,B11:B18,C11:C12)</f>
@@ -2477,7 +4188,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B28" s="2">
@@ -2529,7 +4240,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B32" s="3" t="b">
@@ -2581,7 +4292,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="7" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="3" t="str">
@@ -2595,7 +4306,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B37" s="3" t="str">
         <f>_xll.qlBondRedemption(B25)</f>
@@ -2604,7 +4315,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B38" s="3" t="str">
         <f>_xll.qlBondRedemptions(B25)</f>
@@ -2625,7 +4336,7 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B40" s="3">
@@ -2638,8 +4349,8 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
-        <v>60</v>
+      <c r="A41" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="B41" s="3">
         <f>_xll.qlBondNotionals(B25)</f>
@@ -2651,8 +4362,8 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
-        <v>56</v>
+      <c r="A42" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="B42" s="3" t="str">
         <f>_xll.qlFlatForward(B1,0.3,"actual360","compounded","Annual")</f>
@@ -2664,8 +4375,8 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
-        <v>52</v>
+      <c r="A43" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="B43" s="3" t="str">
         <f>_xll.qlBondSetDiscountingEngine(B25,B42)</f>
@@ -2677,187 +4388,140 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B44" s="10" t="str">
+      <c r="B44" s="9">
         <f>_xll.qlBondCleanPrice(B25)</f>
+        <v>2.2859856860093175</v>
+      </c>
+      <c r="C44" s="9">
+        <f>_xll.qlBondCleanPrice(C25)</f>
+        <v>2.2859856860093175</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45" s="9">
+        <v>0.26236426550490211</v>
+      </c>
+      <c r="C45" s="9">
+        <v>0.26236426550490211</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" s="9">
+        <f>_xll.qlBondCleanPrice2(B25,B45,"actual360","continuous")</f>
+        <v>2.285985683600614</v>
+      </c>
+      <c r="C46" s="9">
+        <f>_xll.qlBondCleanPrice2(C25,C45,"actual360","continuous")</f>
+        <v>2.285985683600614</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" s="9">
+        <f>_xll.qlBondDirtyPrice(B25)</f>
+        <v>2.3026523526759823</v>
+      </c>
+      <c r="C47" s="9">
+        <f>_xll.qlBondDirtyPrice(C25)</f>
+        <v>2.3026523526759823</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48" s="9">
+        <f>_xll.qlBondDirtyPrice2(B25,B45,"actual360","CONTINUOUS","annual")</f>
+        <v>2.3026523502672789</v>
+      </c>
+      <c r="C48" s="9">
+        <f>_xll.qlBondDirtyPrice2(C25,C45,"actual360","CONTINUOUS","annual")</f>
+        <v>2.3026523502672789</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="9">
+        <f>_xll.qlBondYield(B25,"actual360","CONTINUOUS","annual")</f>
+        <v>0.26236426880388447</v>
+      </c>
+      <c r="C49" s="9">
+        <f>_xll.qlBondYield(C25,"actual360","CONTINUOUS","annual")</f>
+        <v>0.26236426880388447</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B50" s="9" t="str">
+        <f>_xll.qlBondPrice(B44,"clean")</f>
+        <v>欣[test_bonds.xlsx]Bond!R50C2BondPrice,A</v>
+      </c>
+      <c r="C50" s="9" t="str">
+        <f>_xll.qlBondPrice(C44,"clean")</f>
+        <v>欣[test_bonds.xlsx]Bond!R50C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="9">
+        <f>_xll.qlBondYield2(B25,B50,"actual360","CONTINUOUS","annual")</f>
+        <v>0.26956857911471388</v>
+      </c>
+      <c r="C51" s="9">
+        <f>_xll.qlBondYield2(C25,C50,"actual360","CONTINUOUS","annual")</f>
+        <v>0.26956857911471388</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="2">
+        <v>45667</v>
+      </c>
+      <c r="C52" s="2">
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="9">
+        <f>_xll.qlBondAccruedAmount(B25,B52)</f>
+        <v>1.6666666666664831E-2</v>
+      </c>
+      <c r="C53" s="9">
+        <f>_xll.qlBondAccruedAmount(C25,C52)</f>
+        <v>1.6666666666664831E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="9" t="str">
+        <f>_xll.qlBondSettlementValue(B25)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C44" s="10">
-        <f>_xll.qlBondCleanPrice(C25)</f>
-        <v>2.3179669686853783</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B45" s="10">
-        <v>0.26236426550490211</v>
-      </c>
-      <c r="C45" s="10">
-        <v>0.26236426550490211</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="10">
-        <f>_xll.qlBondCleanPrice2(B25,B45,"actual360","continuous")</f>
-        <v>2.3179669662432203</v>
-      </c>
-      <c r="C46" s="10">
-        <f>_xll.qlBondCleanPrice2(C25,C45,"actual360","continuous")</f>
-        <v>2.3179669662432203</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" s="10">
-        <f>_xll.qlBondDirtyPrice(B25)</f>
-        <v>2.3346336353520432</v>
-      </c>
-      <c r="C47" s="10">
-        <f>_xll.qlBondDirtyPrice(C25)</f>
-        <v>2.3346336353520432</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B48" s="10">
-        <f>_xll.qlBondDirtyPrice2(B25,B45,"actual360","CONTINUOUS","annual")</f>
-        <v>2.3346336329098851</v>
-      </c>
-      <c r="C48" s="10">
-        <f>_xll.qlBondDirtyPrice2(C25,C45,"actual360","CONTINUOUS","annual")</f>
-        <v>2.3346336329098851</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="10" t="str">
-        <f>_xll.qlBondYield(B25,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
-    return bond.bondYield(
-           ~~~~~~~~~~~~~~^
-        dc,
-        ^^^
-    ...&lt;3 lines&gt;...
-        max_evaluations
-        ^^^^^^^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C49" s="10">
-        <f>_xll.qlBondYield(C25,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426559332721</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B50" s="10" t="str">
-        <f>_xll.qlBondPrice(B44,"clean")</f>
-        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float</v>
-      </c>
-      <c r="C50" s="10" t="str">
-        <f>_xll.qlBondPrice(C44,"clean")</f>
-        <v>欣[test_bonds.xlsx]Bond!R50C3BondPrice,A</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="10" t="str">
-        <f>_xll.qlBondYield2(B25,B50,"actual360","CONTINUOUS","annual")</f>
-        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float': Expected cache string</v>
-      </c>
-      <c r="C51" s="10">
-        <f>_xll.qlBondYield2(C25,C50,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26946953931176648</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52" s="2">
-        <v>45667</v>
-      </c>
-      <c r="C52" s="2">
-        <v>45667</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="10">
-        <f>_xll.qlBondAccruedAmount(B25,B52)</f>
-        <v>1.6666666666664831E-2</v>
-      </c>
-      <c r="C53" s="10">
-        <f>_xll.qlBondAccruedAmount(C25,C52)</f>
-        <v>1.6666666666664831E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="10">
-        <f>_xll.qlBondSettlementValue(B25)</f>
-        <v>2.3346336353520432</v>
-      </c>
-      <c r="C54" s="10" t="str">
-        <f>_xll.qlBondSettlementValue(C25)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 635, in qlBondSettlementValue
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 562, in qlBondSettlementValue
     return bond.settlementValue()
            ~~~~~~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
@@ -2866,27 +4530,31 @@
 RuntimeError: null pricing engine
 </v>
       </c>
+      <c r="C54" s="9" t="str">
+        <f>_xll.qlBondSettlementValue(C25)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 562, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B55" s="10" t="str">
+      <c r="B55" s="9">
         <f>_xll.qlBondSettlementValue2(B25,B44)</f>
-        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float</v>
-      </c>
-      <c r="C55" s="10">
+        <v>2.3026523526759823</v>
+      </c>
+      <c r="C55" s="9">
         <f>_xll.qlBondSettlementValue2(C25,C44)</f>
-        <v>2.3346336353520432</v>
+        <v>2.3026523526759823</v>
       </c>
     </row>
   </sheetData>
@@ -2936,7 +4604,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B5" s="3" t="str">
         <f>_xll.qlCalendar("Target")</f>
@@ -2963,23 +4631,23 @@
         <v>16</v>
       </c>
       <c r="B7" s="2">
-        <v>46030</v>
+        <v>49682</v>
       </c>
       <c r="C7" s="2">
-        <v>46030</v>
+        <v>49682</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" s="3">
         <v>120</v>
@@ -2995,7 +4663,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B11" s="3" t="str">
         <f>_xll.qlZeroCouponBond(B4,B5,B6,B7)</f>
@@ -3012,28 +4680,28 @@
       </c>
       <c r="B12" s="3" t="str">
         <f>_xll.qlBondNextCouponRate(B11)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2026
+        <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 249, in qlBondNextCouponRate
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 231, in qlBondNextCouponRate
     return bond.nextCouponRate(date)
            ~~~~~~~~~~~~~~~~~~~^^^^^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
     return _QuantLib.Bond_nextCouponRate(self, *args)
            ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: no coupon paid at cashflow date January 8th, 2026
+RuntimeError: no coupon paid at cashflow date January 8th, 2036
 </v>
       </c>
       <c r="C12" s="3" t="str">
         <f>_xll.qlBondNextCouponRate(C11)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2026
+        <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 249, in qlBondNextCouponRate
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 231, in qlBondNextCouponRate
     return bond.nextCouponRate(date)
            ~~~~~~~~~~~~~~~~~~~^^^^^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
     return _QuantLib.Bond_nextCouponRate(self, *args)
            ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: no coupon paid at cashflow date January 8th, 2026
+RuntimeError: no coupon paid at cashflow date January 8th, 2036
 </v>
       </c>
     </row>
@@ -3051,16 +4719,16 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="2">
         <f>_xll.qlBondNextCashFlowDate(B11)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
       <c r="C14" s="2">
         <f>_xll.qlBondNextCashFlowDate(C11)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -3103,7 +4771,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="3" t="b">
@@ -3121,11 +4789,11 @@
       </c>
       <c r="B19" s="2">
         <f>_xll.qlBondStartDate(B11)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
       <c r="C19" s="2">
         <f>_xll.qlBondStartDate(C11)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -3134,11 +4802,11 @@
       </c>
       <c r="B20" s="2">
         <f>_xll.qlBondMaturityDate(B11)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
       <c r="C20" s="2">
         <f>_xll.qlBondMaturityDate(C11)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -3155,7 +4823,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>30</v>
       </c>
       <c r="B22" s="3" t="str">
@@ -3169,7 +4837,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" s="3" t="str">
         <f>_xll.qlBondRedemption(B11)</f>
@@ -3182,7 +4850,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24" s="3" t="str">
         <f>_xll.qlBondRedemptions(B11)</f>
@@ -3207,7 +4875,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B26" s="3">
@@ -3220,8 +4888,8 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>60</v>
+      <c r="A27" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="B27" s="3">
         <f>_xll.qlBondNotionals(B11)</f>
@@ -3233,8 +4901,8 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>56</v>
+      <c r="A28" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="B28" s="3" t="str">
         <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Annual")</f>
@@ -3246,8 +4914,8 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
-        <v>52</v>
+      <c r="A29" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="B29" s="3" t="str">
         <f>_xll.qlBondSetDiscountingEngine(B11,B28)</f>
@@ -3259,162 +4927,110 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="9">
         <f>_xll.qlBondCleanPrice(B11)</f>
-        <v>76.755078422532549</v>
-      </c>
-      <c r="C30" s="10" t="str">
+        <v>5.3606211124198397</v>
+      </c>
+      <c r="C30" s="9">
         <f>_xll.qlBondCleanPrice(C11)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>6.4327453349038084</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" s="10">
+      <c r="A31" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="9">
         <v>0.26236426550490211</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="9">
         <v>1.2623642655049001</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="9">
         <f>_xll.qlBondCleanPrice2(B11,B31,"actual360","continuous")</f>
-        <v>76.75507834224257</v>
-      </c>
-      <c r="C32" s="10">
+        <v>5.3606210503973868</v>
+      </c>
+      <c r="C32" s="9">
         <f>_xll.qlBondCleanPrice2(C11,C31,"actual360","continuous")</f>
-        <v>33.602745504170436</v>
+        <v>9.2216048105760734E-5</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="10" t="str">
+      <c r="B33" s="9">
         <f>_xll.qlBondDirtyPrice(B11)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 511, in qlBondDirtyPrice
-    return bond.dirtyPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
-    return _QuantLib.Bond_dirtyPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C33" s="10">
+        <v>5.3606211124198397</v>
+      </c>
+      <c r="C33" s="9">
         <f>_xll.qlBondDirtyPrice(C11)</f>
-        <v>92.106094107039056</v>
+        <v>6.4327453349038084</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="9">
         <f>_xll.qlBondDirtyPrice2(B11,B31,"actual360","CONTINUOUS","annual")</f>
-        <v>76.75507834224257</v>
-      </c>
-      <c r="C34" s="10">
+        <v>5.3606210503973868</v>
+      </c>
+      <c r="C34" s="9">
         <f>_xll.qlBondDirtyPrice2(C11,C31,"actual360","CONTINUOUS","annual")</f>
-        <v>33.602745504170436</v>
+        <v>9.2216048105760734E-5</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="10" t="str">
+      <c r="B35" s="9">
         <f>_xll.qlBondYield(B11,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
-    return bond.bondYield(
-           ~~~~~~~~~~~~~~^
-        dc,
-        ^^^
-    ...&lt;3 lines&gt;...
-        max_evaluations
-        ^^^^^^^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C35" s="10">
+        <v>0.26236426339626184</v>
+      </c>
+      <c r="C35" s="9">
         <f>_xll.qlBondYield(C11,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
+        <v>0.26236426471315105</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B36" s="10" t="str">
+      <c r="A36" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B36" s="9" t="str">
         <f>_xll.qlBondPrice(B30,"clean")</f>
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R36C2BondPrice,A</v>
       </c>
-      <c r="C36" s="10" t="str">
+      <c r="C36" s="9" t="str">
         <f>_xll.qlBondPrice(C30,"clean")</f>
-        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float</v>
+        <v>欣[test_bonds.xlsx]ZeroCouponBond!R36C3BondPrice,A</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="9">
         <f>_xll.qlBondYield2(B11,B36,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
-      </c>
-      <c r="C37" s="10" t="str">
+        <v>0.26236426339626184</v>
+      </c>
+      <c r="C37" s="9">
         <f>_xll.qlBondYield2(C11,C36,"actual360","CONTINUOUS","annual")</f>
-        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float': Expected cache string</v>
+        <v>0.26236426471315105</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
-        <v>55</v>
+      <c r="A38" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="B38" s="2">
         <v>45667</v>
@@ -3424,60 +5040,42 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="9">
         <f>_xll.qlBondAccruedAmount(B11,B38)</f>
         <v>0</v>
       </c>
-      <c r="C39" s="10">
+      <c r="C39" s="9">
         <f>_xll.qlBondAccruedAmount(C11,C38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="10" t="str">
+      <c r="B40" s="9">
         <f>_xll.qlBondSettlementValue(B11)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 635, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C40" s="10">
+        <v>5.3606211124198397</v>
+      </c>
+      <c r="C40" s="9">
         <f>_xll.qlBondSettlementValue(C11)</f>
-        <v>92.106094107039056</v>
+        <v>6.4327453349038075</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="9">
         <f>_xll.qlBondSettlementValue2(B11,B30)</f>
-        <v>76.755078422532549</v>
-      </c>
-      <c r="C41" s="10" t="str">
+        <v>5.3606211124198397</v>
+      </c>
+      <c r="C41" s="9">
         <f>_xll.qlBondSettlementValue2(C11,C30)</f>
-        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float</v>
+        <v>6.4327453349038084</v>
       </c>
     </row>
   </sheetData>
@@ -3492,7 +5090,7 @@
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
     <col min="2" max="2" width="59.140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="58" style="3" customWidth="1"/>
+    <col min="3" max="3" width="126.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3536,24 +5134,24 @@
     </row>
     <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="12">
+        <v>73</v>
+      </c>
+      <c r="B6" s="11">
         <v>45665</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <v>45665</v>
       </c>
     </row>
     <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="12">
-        <v>46030</v>
-      </c>
-      <c r="C7" s="12">
-        <v>46030</v>
+        <v>74</v>
+      </c>
+      <c r="B7" s="11">
+        <v>49682</v>
+      </c>
+      <c r="C7" s="11">
+        <v>49682</v>
       </c>
     </row>
     <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -3561,15 +5159,15 @@
         <v>46</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9" s="6" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
@@ -3585,37 +5183,37 @@
         <v>47</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B13" s="6">
         <v>0</v>
@@ -3626,7 +5224,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B14" s="3" t="str">
         <f>_xll.qlSchedule(B6,B7,B8,B9,B10,B11,B12,B13)</f>
@@ -3638,8 +5236,8 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
-        <v>67</v>
+      <c r="A15" s="35" t="s">
+        <v>66</v>
       </c>
       <c r="B15" s="3">
         <v>0.4</v>
@@ -3649,7 +5247,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="34"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="3">
         <v>0.5</v>
       </c>
@@ -3658,7 +5256,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="34"/>
+      <c r="A17" s="35"/>
       <c r="B17" s="3">
         <v>0.6</v>
       </c>
@@ -3668,26 +5266,26 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C20" s="3">
         <v>120</v>
@@ -3703,7 +5301,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C22" s="3" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
@@ -3712,15 +5310,15 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C24" s="3" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
@@ -3729,26 +5327,26 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="3">
-        <v>1</v>
+        <v>72</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B27" s="3" t="str">
-        <f>_xll.qlFixedRateBond(B4,B5,B14,B15:B17,B18)</f>
+        <f>_xll.qlFixedRateBond(B4,B5,B14,B15:B17,B18,,,,,,,,)</f>
         <v>欣[test_bonds.xlsx]FixedRateBond!R27C2FixedRateBond,A</v>
       </c>
       <c r="C27" s="3" t="str">
@@ -3783,16 +5381,16 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B30" s="2">
         <f>_xll.qlBondNextCashFlowDate(B27)</f>
-        <v>45755</v>
+        <v>46030</v>
       </c>
       <c r="C30" s="2">
         <f>_xll.qlBondNextCashFlowDate(C27)</f>
-        <v>45755</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -3835,7 +5433,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B34" s="3" t="b">
@@ -3866,11 +5464,11 @@
       </c>
       <c r="B36" s="2">
         <f>_xll.qlBondMaturityDate(B27)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
       <c r="C36" s="2">
         <f>_xll.qlBondMaturityDate(C27)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -3887,7 +5485,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="7" t="s">
         <v>30</v>
       </c>
       <c r="B38" s="3" t="str">
@@ -3901,7 +5499,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B39" s="3" t="str">
         <f>_xll.qlBondRedemption(B27)</f>
@@ -3914,7 +5512,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B40" s="3" t="str">
         <f>_xll.qlBondRedemptions(B27)</f>
@@ -3939,7 +5537,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B42" s="3">
@@ -3952,8 +5550,8 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
-        <v>60</v>
+      <c r="A43" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="B43" s="3">
         <f>_xll.qlBondNotionals(B27)</f>
@@ -3965,8 +5563,8 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
-        <v>56</v>
+      <c r="A44" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="B44" s="3" t="str">
         <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Annual")</f>
@@ -3978,8 +5576,8 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
-        <v>52</v>
+      <c r="A45" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="B45" s="3" t="str">
         <f>_xll.qlBondSetDiscountingEngine(B27,B44)</f>
@@ -3991,207 +5589,164 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="9">
         <f>_xll.qlBondCleanPrice(B27)</f>
-        <v>121.40429393805222</v>
-      </c>
-      <c r="C46" s="10" t="str">
+        <v>170.40963157834548</v>
+      </c>
+      <c r="C46" s="9">
         <f>_xll.qlBondCleanPrice(C27)</f>
+        <v>171.42647581938954</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" s="9">
+        <v>0.26236426550490211</v>
+      </c>
+      <c r="C47" s="9">
+        <v>0.26236426550490211</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B48" s="9">
+        <f>_xll.qlBondCleanPrice2(B27,B47,"actual360","continuous")</f>
+        <v>170.40963082810279</v>
+      </c>
+      <c r="C48" s="9">
+        <f>_xll.qlBondCleanPrice2(C27,C47,"actual360","continuous")</f>
+        <v>171.42647505679128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" s="9">
+        <f>_xll.qlBondDirtyPrice(B27)</f>
+        <v>170.40963157834548</v>
+      </c>
+      <c r="C49" s="9">
+        <f>_xll.qlBondDirtyPrice(C27)</f>
+        <v>171.42647581938954</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B50" s="9">
+        <f>_xll.qlBondDirtyPrice2(B27,B47,"actual360","CONTINUOUS","annual")</f>
+        <v>170.40963082810279</v>
+      </c>
+      <c r="C50" s="9">
+        <f>_xll.qlBondDirtyPrice2(C27,C47,"actual360","CONTINUOUS","annual")</f>
+        <v>171.42647505679128</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="9">
+        <f>_xll.qlBondYield(B27,"actual360","CONTINUOUS","annual")</f>
+        <v>0.26236426417183883</v>
+      </c>
+      <c r="C51" s="9">
+        <f>_xll.qlBondYield(C27,"actual360","CONTINUOUS","annual")</f>
+        <v>0.26236426417183883</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B52" s="9" t="str">
+        <f>_xll.qlBondPrice(B46,"clean")</f>
+        <v>欣[test_bonds.xlsx]FixedRateBond!R52C2BondPrice,A</v>
+      </c>
+      <c r="C52" s="9" t="str">
+        <f>_xll.qlBondPrice(C46,"clean")</f>
+        <v>欣[test_bonds.xlsx]FixedRateBond!R52C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="9">
+        <f>_xll.qlBondYield2(B27,B52,"actual360","CONTINUOUS","annual")</f>
+        <v>0.26236426417183883</v>
+      </c>
+      <c r="C53" s="9">
+        <f>_xll.qlBondYield2(C27,C52,"actual360","CONTINUOUS","annual")</f>
+        <v>0.26236426417183883</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="2">
+        <v>45667</v>
+      </c>
+      <c r="C54" s="2">
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="9">
+        <f>_xll.qlBondAccruedAmount(B27,B54)</f>
+        <v>0.22222222222221255</v>
+      </c>
+      <c r="C55" s="9">
+        <f>_xll.qlBondAccruedAmount(C27,C54)</f>
+        <v>0.22222222222221255</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="9" t="str">
+        <f>_xll.qlBondSettlementValue(B27)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 562, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
 RuntimeError: null pricing engine
 </v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="10">
-        <v>0.26236426550490211</v>
-      </c>
-      <c r="C47" s="10">
-        <v>0.26236426550490211</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B48" s="10">
-        <f>_xll.qlBondCleanPrice2(B27,B47,"actual360","continuous")</f>
-        <v>121.40429382698329</v>
-      </c>
-      <c r="C48" s="10">
-        <f>_xll.qlBondCleanPrice2(C27,C47,"actual360","continuous")</f>
-        <v>127.3678128928466</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B49" s="10">
-        <f>_xll.qlBondDirtyPrice(B27)</f>
-        <v>121.40429393805222</v>
-      </c>
-      <c r="C49" s="10">
-        <f>_xll.qlBondDirtyPrice(C27)</f>
-        <v>127.36781301760961</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B50" s="10">
-        <f>_xll.qlBondDirtyPrice2(B27,B47,"actual360","CONTINUOUS","annual")</f>
-        <v>121.40429382698329</v>
-      </c>
-      <c r="C50" s="10">
-        <f>_xll.qlBondDirtyPrice2(C27,C47,"actual360","CONTINUOUS","annual")</f>
-        <v>127.3678128928466</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="10">
-        <f>_xll.qlBondYield(B27,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
-      </c>
-      <c r="C51" s="10" t="str">
-        <f>_xll.qlBondYield(C27,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
-    return bond.bondYield(
-           ~~~~~~~~~~~~~~^
-        dc,
-        ^^^
-    ...&lt;3 lines&gt;...
-        max_evaluations
-        ^^^^^^^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B52" s="10" t="str">
-        <f>_xll.qlBondPrice(B46,"clean")</f>
-        <v>欣[test_bonds.xlsx]FixedRateBond!R52C2BondPrice,A</v>
-      </c>
-      <c r="C52" s="10" t="str">
-        <f>_xll.qlBondPrice(C46,"clean")</f>
-        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="10">
-        <f>_xll.qlBondYield2(B27,B52,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
-      </c>
-      <c r="C53" s="10" t="str">
-        <f>_xll.qlBondYield2(C27,C52,"actual360","CONTINUOUS","annual")</f>
-        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float': Expected cache string</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54" s="2">
-        <v>45667</v>
-      </c>
-      <c r="C54" s="2">
-        <v>45667</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="10">
-        <f>_xll.qlBondAccruedAmount(B27,B54)</f>
-        <v>0.22222222222221255</v>
-      </c>
-      <c r="C55" s="10">
-        <f>_xll.qlBondAccruedAmount(C27,C54)</f>
-        <v>-9.777777777777775</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="10">
-        <f>_xll.qlBondSettlementValue(B27)</f>
-        <v>121.40429393805221</v>
-      </c>
-      <c r="C56" s="10">
+      <c r="C56" s="9">
         <f>_xll.qlBondSettlementValue(C27)</f>
-        <v>127.36781301760961</v>
+        <v>171.42647581938951</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="9">
         <f>_xll.qlBondSettlementValue2(B27,B46)</f>
-        <v>121.40429393805221</v>
-      </c>
-      <c r="C57" s="10" t="str">
+        <v>170.40963157834548</v>
+      </c>
+      <c r="C57" s="9">
         <f>_xll.qlBondSettlementValue2(C27,C46)</f>
-        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float</v>
+        <v>171.42647581938954</v>
       </c>
     </row>
   </sheetData>
@@ -4241,8 +5796,8 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
-        <v>84</v>
+      <c r="A5" s="35" t="s">
+        <v>82</v>
       </c>
       <c r="B5" s="3">
         <v>150</v>
@@ -4252,7 +5807,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="34"/>
+      <c r="A6" s="35"/>
       <c r="B6" s="3">
         <v>125</v>
       </c>
@@ -4261,7 +5816,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="3">
         <v>100</v>
       </c>
@@ -4271,24 +5826,24 @@
     </row>
     <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="12">
+        <v>73</v>
+      </c>
+      <c r="B8" s="11">
         <v>45665</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <v>45665</v>
       </c>
     </row>
     <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="12">
-        <v>46030</v>
-      </c>
-      <c r="C9" s="12">
-        <v>46030</v>
+        <v>74</v>
+      </c>
+      <c r="B9" s="11">
+        <v>49682</v>
+      </c>
+      <c r="C9" s="11">
+        <v>49682</v>
       </c>
     </row>
     <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -4296,15 +5851,15 @@
         <v>46</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" s="6" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
@@ -4320,37 +5875,37 @@
         <v>47</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B15" s="6">
         <v>0</v>
@@ -4361,7 +5916,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" s="3" t="str">
         <f>_xll.qlSchedule(B8,B9,B10,B11,B12,B13,B14,B15)</f>
@@ -4373,8 +5928,8 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="34" t="s">
-        <v>67</v>
+      <c r="A17" s="35" t="s">
+        <v>66</v>
       </c>
       <c r="B17" s="3">
         <v>0.4</v>
@@ -4384,7 +5939,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="34"/>
+      <c r="A18" s="35"/>
       <c r="B18" s="3">
         <v>0.5</v>
       </c>
@@ -4393,7 +5948,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="34"/>
+      <c r="A19" s="35"/>
       <c r="B19" s="3">
         <v>0.6</v>
       </c>
@@ -4403,21 +5958,21 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -4430,15 +5985,15 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C24" s="3" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
@@ -4447,43 +6002,43 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C26" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="34" t="s">
-        <v>89</v>
+      <c r="A27" s="35" t="s">
+        <v>87</v>
       </c>
       <c r="C27" s="3">
         <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
+      <c r="A28" s="35"/>
       <c r="C28" s="3">
         <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
+      <c r="A29" s="35"/>
       <c r="C29" s="3">
         <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B30" s="3" t="str">
         <f>_xll.qlAmortizingFixedRateBond(B4,B5:B7,B16,B17:B19,B20)</f>
@@ -4521,16 +6076,16 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B33" s="2">
         <f>_xll.qlBondNextCashFlowDate(B30)</f>
-        <v>45755</v>
+        <v>46030</v>
       </c>
       <c r="C33" s="2">
         <f>_xll.qlBondNextCashFlowDate(C30)</f>
-        <v>45755</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -4573,7 +6128,7 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B37" s="3" t="b">
@@ -4604,11 +6159,11 @@
       </c>
       <c r="B39" s="2">
         <f>_xll.qlBondMaturityDate(B30)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
       <c r="C39" s="2">
         <f>_xll.qlBondMaturityDate(C30)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -4625,7 +6180,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="7" t="s">
         <v>30</v>
       </c>
       <c r="B41" s="3" t="str">
@@ -4639,13 +6194,13 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B42" s="3" t="str">
         <f>_xll.qlBondRedemption(B30)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 402, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 365, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -4658,7 +6213,7 @@
         <f>_xll.qlBondRedemption(C30)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 402, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 365, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -4670,7 +6225,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B43" s="3" t="str">
         <f>_xll.qlBondRedemptions(B30)</f>
@@ -4695,7 +6250,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B45" s="3">
@@ -4708,8 +6263,8 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="8" t="s">
-        <v>60</v>
+      <c r="A46" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="B46" s="3">
         <f>_xll.qlBondNotionals(B30)</f>
@@ -4721,8 +6276,8 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
-        <v>56</v>
+      <c r="A47" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="B47" s="3" t="str">
         <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Annual")</f>
@@ -4734,8 +6289,8 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
-        <v>52</v>
+      <c r="A48" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="B48" s="3" t="str">
         <f>_xll.qlBondSetDiscountingEngine(B30,B47)</f>
@@ -4747,126 +6302,119 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="9">
         <f>_xll.qlBondCleanPrice(B30)</f>
-        <v>116.06677073244725</v>
-      </c>
-      <c r="C49" s="10">
+        <v>151.24747199666061</v>
+      </c>
+      <c r="C49" s="9">
         <f>_xll.qlBondCleanPrice(C30)</f>
-        <v>124.83094006125697</v>
+        <v>153.90042276113556</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="10">
+      <c r="A50" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="9">
         <v>0.26236426550490211</v>
       </c>
-      <c r="C50" s="10">
+      <c r="C50" s="9">
         <v>0.26236426550490211</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="9">
         <f>_xll.qlBondCleanPrice2(B30,B50,"actual360","continuous")</f>
-        <v>116.06677064550468</v>
-      </c>
-      <c r="C51" s="10">
+        <v>151.24747144150959</v>
+      </c>
+      <c r="C51" s="9">
         <f>_xll.qlBondCleanPrice2(C30,C50,"actual360","continuous")</f>
-        <v>124.83093997018912</v>
+        <v>153.90042219843011</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="9" t="str">
         <f>_xll.qlBondDirtyPrice(B30)</f>
-        <v>116.28899295466947</v>
-      </c>
-      <c r="C52" s="10">
+        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 457, in qlBondDirtyPrice
+    return bond.dirtyPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
+    return _QuantLib.Bond_dirtyPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: null pricing engine
+</v>
+      </c>
+      <c r="C52" s="9">
         <f>_xll.qlBondDirtyPrice(C30)</f>
-        <v>115.0531622834792</v>
+        <v>154.12264498335776</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="9">
         <f>_xll.qlBondDirtyPrice2(B30,B50,"actual360","CONTINUOUS","annual")</f>
-        <v>116.28899286772689</v>
-      </c>
-      <c r="C53" s="10">
+        <v>151.46969366373179</v>
+      </c>
+      <c r="C53" s="9">
         <f>_xll.qlBondDirtyPrice2(C30,C50,"actual360","CONTINUOUS","annual")</f>
-        <v>115.05316219241135</v>
+        <v>154.12264442065231</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="9">
         <f>_xll.qlBondYield(B30,"actual360","CONTINUOUS","annual")</f>
         <v>0.26236426417183883</v>
       </c>
-      <c r="C54" s="10" t="str">
+      <c r="C54" s="9">
         <f>_xll.qlBondYield(C30,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
-    return bond.bondYield(
-           ~~~~~~~~~~~~~~^
-        dc,
-        ^^^
-    ...&lt;3 lines&gt;...
-        max_evaluations
-        ^^^^^^^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>0.26236426417183883</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B55" s="10" t="str">
+      <c r="A55" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" s="9" t="str">
         <f>_xll.qlBondPrice(B49,"clean")</f>
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R55C2BondPrice,A</v>
       </c>
-      <c r="C55" s="10" t="str">
+      <c r="C55" s="9" t="str">
         <f>_xll.qlBondPrice(C49,"clean")</f>
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R55C3BondPrice,A</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="9">
         <f>_xll.qlBondYield2(B30,B55,"actual360","CONTINUOUS","annual")</f>
-        <v>0.2650188827598095</v>
-      </c>
-      <c r="C56" s="10">
+        <v>0.2627800233576299</v>
+      </c>
+      <c r="C56" s="9">
         <f>_xll.qlBondYield2(C30,C55,"actual360","CONTINUOUS","annual")</f>
-        <v>0.1561166555979252</v>
+        <v>0.26277443958973895</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
-        <v>55</v>
+      <c r="A57" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="B57" s="2">
         <v>45667</v>
@@ -4876,42 +6424,42 @@
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="9">
         <f>_xll.qlBondAccruedAmount(B30,B57)</f>
         <v>0.22222222222221252</v>
       </c>
-      <c r="C58" s="10">
+      <c r="C58" s="9">
         <f>_xll.qlBondAccruedAmount(C30,C57)</f>
-        <v>-9.7777777777777732</v>
+        <v>0.22222222222221252</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="9">
         <f>_xll.qlBondSettlementValue(B30)</f>
-        <v>174.43348943200422</v>
-      </c>
-      <c r="C59" s="10">
+        <v>227.20454132832424</v>
+      </c>
+      <c r="C59" s="9">
         <f>_xll.qlBondSettlementValue(C30)</f>
-        <v>172.57974342521879</v>
+        <v>231.18396747503664</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="9">
         <f>_xll.qlBondSettlementValue2(B30,B49)</f>
-        <v>174.43348943200419</v>
-      </c>
-      <c r="C60" s="10">
+        <v>227.20454132832421</v>
+      </c>
+      <c r="C60" s="9">
         <f>_xll.qlBondSettlementValue2(C30,C49)</f>
-        <v>172.57974342521879</v>
+        <v>231.18396747503661</v>
       </c>
     </row>
   </sheetData>
@@ -4963,8 +6511,8 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
-        <v>90</v>
+      <c r="A5" s="35" t="s">
+        <v>88</v>
       </c>
       <c r="B5" s="3">
         <v>150</v>
@@ -4974,7 +6522,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="34"/>
+      <c r="A6" s="35"/>
       <c r="B6" s="3">
         <v>125</v>
       </c>
@@ -4983,7 +6531,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="3">
         <v>100</v>
       </c>
@@ -4993,24 +6541,24 @@
     </row>
     <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="12">
+        <v>73</v>
+      </c>
+      <c r="B8" s="11">
         <v>45665</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <v>45665</v>
       </c>
     </row>
     <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="12">
-        <v>46030</v>
-      </c>
-      <c r="C9" s="12">
-        <v>46030</v>
+        <v>74</v>
+      </c>
+      <c r="B9" s="11">
+        <v>49682</v>
+      </c>
+      <c r="C9" s="11">
+        <v>49682</v>
       </c>
     </row>
     <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -5018,15 +6566,15 @@
         <v>46</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" s="6" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
@@ -5042,37 +6590,37 @@
         <v>47</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B15" s="6">
         <v>0</v>
@@ -5083,7 +6631,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" s="3" t="str">
         <f>_xll.qlSchedule(B8,B9,B10,B11,B12,B13,B14,B15)</f>
@@ -5095,21 +6643,21 @@
       </c>
     </row>
     <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="15" t="str">
+      <c r="A17" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="14" t="str">
         <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R17C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C17" s="15" t="str">
+      <c r="C17" s="14" t="str">
         <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R17C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B18" s="3" t="str">
         <f>_xll.qlEuribor("3M",B17)</f>
@@ -5122,26 +6670,26 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C21" s="3">
         <v>0</v>
@@ -5149,7 +6697,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -5157,33 +6705,33 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="1"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>97</v>
-      </c>
       <c r="C26" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C27" s="2">
@@ -5192,15 +6740,15 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C29" s="3" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
@@ -5209,15 +6757,15 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C31" s="3">
         <v>0</v>
@@ -5225,7 +6773,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C32" s="3">
         <v>100</v>
@@ -5233,7 +6781,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C33" s="3">
         <v>0</v>
@@ -5241,7 +6789,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B34" s="3" t="str">
         <f>_xll.qlAmortizingFloatingRateBond(B4,B5:B7,B16,B18,B19)</f>
@@ -5258,11 +6806,11 @@
       </c>
       <c r="B35" s="3">
         <f>_xll.qlBondNextCouponRate(B34)</f>
-        <v>0.29999999999999982</v>
+        <v>0.33645996454499488</v>
       </c>
       <c r="C35" s="3">
         <f>_xll.qlBondNextCouponRate(C34)</f>
-        <v>0.29999999999999982</v>
+        <v>0.33645996454499488</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -5279,16 +6827,16 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B37" s="2">
         <f>_xll.qlBondNextCashFlowDate(B34)</f>
-        <v>45755</v>
+        <v>46030</v>
       </c>
       <c r="C37" s="2">
         <f>_xll.qlBondNextCashFlowDate(C34)</f>
-        <v>45755</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -5331,7 +6879,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B41" s="3" t="b">
@@ -5362,11 +6910,11 @@
       </c>
       <c r="B43" s="2">
         <f>_xll.qlBondMaturityDate(B34)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
       <c r="C43" s="2">
         <f>_xll.qlBondMaturityDate(C34)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -5383,7 +6931,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="7" t="s">
         <v>30</v>
       </c>
       <c r="B45" s="3" t="str">
@@ -5397,13 +6945,13 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B46" s="3" t="str">
         <f>_xll.qlBondRedemption(B34)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 402, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 365, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -5416,7 +6964,7 @@
         <f>_xll.qlBondRedemption(C34)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 402, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 365, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -5428,7 +6976,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B47" s="3" t="str">
         <f>_xll.qlBondRedemptions(B34)</f>
@@ -5453,7 +7001,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B49" s="3">
@@ -5466,8 +7014,8 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
-        <v>60</v>
+      <c r="A50" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="B50" s="3">
         <f>_xll.qlBondNotionals(B34)</f>
@@ -5479,8 +7027,8 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
-        <v>56</v>
+      <c r="A51" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="B51" s="3" t="str">
         <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
@@ -5492,8 +7040,8 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
-        <v>52</v>
+      <c r="A52" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="B52" s="3" t="str">
         <f>_xll.qlBondSetDiscountingEngine(B34,B51)</f>
@@ -5505,178 +7053,110 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B53" s="10" t="str">
+      <c r="B53" s="9">
         <f>_xll.qlBondCleanPrice(B34)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C53" s="10">
+        <v>98.911948723893104</v>
+      </c>
+      <c r="C53" s="9">
         <f>_xll.qlBondCleanPrice(C34)</f>
-        <v>100.50931941462544</v>
+        <v>98.911948723893104</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B54" s="10">
+      <c r="A54" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="9">
         <v>0.28928264971926221</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C54" s="9">
         <v>0.28928264971926221</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="9">
         <f>_xll.qlBondCleanPrice2(B34,B54,"actual360","continuous")</f>
-        <v>99.997284874328287</v>
-      </c>
-      <c r="C55" s="10">
+        <v>98.911947709487364</v>
+      </c>
+      <c r="C55" s="9">
         <f>_xll.qlBondCleanPrice2(C34,C54,"actual360","continuous")</f>
-        <v>100.50931917363729</v>
+        <v>98.911947709487364</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B56" s="10" t="str">
+      <c r="B56" s="9">
         <f>_xll.qlBondDirtyPrice(B34)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 511, in qlBondDirtyPrice
-    return bond.dirtyPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
-    return _QuantLib.Bond_dirtyPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C56" s="10">
+        <v>99.098870926418101</v>
+      </c>
+      <c r="C56" s="9">
         <f>_xll.qlBondDirtyPrice(C34)</f>
-        <v>93.175986081292109</v>
+        <v>99.098870926418101</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="9">
         <f>_xll.qlBondDirtyPrice2(B34,B54,"actual360","CONTINUOUS","annual")</f>
-        <v>100.16395154099496</v>
-      </c>
-      <c r="C57" s="10">
+        <v>99.098869912012361</v>
+      </c>
+      <c r="C57" s="9">
         <f>_xll.qlBondDirtyPrice2(C34,C54,"actual360","CONTINUOUS","annual")</f>
-        <v>93.175985840303966</v>
+        <v>99.098869912012361</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B58" s="10" t="str">
+      <c r="B58" s="9">
         <f>_xll.qlBondYield(B34,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
-    return bond.bondYield(
-           ~~~~~~~~~~~~~~^
-        dc,
-        ^^^
-    ...&lt;3 lines&gt;...
-        max_evaluations
-        ^^^^^^^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C58" s="10" t="str">
+        <v>0.28928264971926221</v>
+      </c>
+      <c r="C58" s="9">
         <f>_xll.qlBondYield(C34,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
-    return bond.bondYield(
-           ~~~~~~~~~~~~~~^
-        dc,
-        ^^^
-    ...&lt;3 lines&gt;...
-        max_evaluations
-        ^^^^^^^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>0.28928264971926221</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B59" s="10" t="str">
+      <c r="A59" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B59" s="9" t="str">
         <f>_xll.qlBondPrice(B53,"clean")</f>
-        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float</v>
-      </c>
-      <c r="C59" s="10" t="str">
+        <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R59C2BondPrice,A</v>
+      </c>
+      <c r="C59" s="9" t="str">
         <f>_xll.qlBondPrice(C53,"clean")</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R59C3BondPrice,A</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B60" s="10" t="str">
+      <c r="B60" s="9">
         <f>_xll.qlBondYield2(B34,B59,"actual360","CONTINUOUS","annual")</f>
-        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float': Expected cache string</v>
-      </c>
-      <c r="C60" s="10">
+        <v>0.28991034966766843</v>
+      </c>
+      <c r="C60" s="9">
         <f>_xll.qlBondYield2(C34,C59,"actual360","CONTINUOUS","annual")</f>
-        <v>0.19027274083304402</v>
+        <v>0.28991034966766843</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="11" t="s">
-        <v>55</v>
+      <c r="A61" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="B61" s="2">
         <v>45667</v>
@@ -5686,60 +7166,42 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B62" s="9">
         <f>_xll.qlBondAccruedAmount(B34,B61)</f>
-        <v>0.16666666666666657</v>
-      </c>
-      <c r="C62" s="10">
+        <v>0.18692220252499714</v>
+      </c>
+      <c r="C62" s="9">
         <f>_xll.qlBondAccruedAmount(C34,C61)</f>
-        <v>-7.3333333333333286</v>
+        <v>0.18692220252499714</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B63" s="10" t="str">
+      <c r="B63" s="9">
         <f>_xll.qlBondSettlementValue(B34)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 635, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C63" s="10">
+        <v>148.64830638962715</v>
+      </c>
+      <c r="C63" s="9">
         <f>_xll.qlBondSettlementValue(C34)</f>
-        <v>139.76397912193815</v>
+        <v>148.64830638962715</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B64" s="10" t="str">
+      <c r="B64" s="9">
         <f>_xll.qlBondSettlementValue2(B34,B53)</f>
-        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float</v>
-      </c>
-      <c r="C64" s="10">
+        <v>148.64830638962715</v>
+      </c>
+      <c r="C64" s="9">
         <f>_xll.qlBondSettlementValue2(C34,C53)</f>
-        <v>139.76397912193815</v>
+        <v>148.64830638962715</v>
       </c>
     </row>
   </sheetData>
@@ -5802,24 +7264,24 @@
     </row>
     <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="12">
+        <v>73</v>
+      </c>
+      <c r="B6" s="11">
         <v>45665</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <v>45665</v>
       </c>
     </row>
     <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="12">
-        <v>46030</v>
-      </c>
-      <c r="C7" s="12">
-        <v>46030</v>
+        <v>74</v>
+      </c>
+      <c r="B7" s="11">
+        <v>49682</v>
+      </c>
+      <c r="C7" s="11">
+        <v>49682</v>
       </c>
     </row>
     <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -5827,15 +7289,15 @@
         <v>46</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9" s="6" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
@@ -5851,37 +7313,37 @@
         <v>47</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B13" s="6">
         <v>0</v>
@@ -5892,7 +7354,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B14" s="3" t="str">
         <f>_xll.qlSchedule(B6,B7,B8,B9,B10,B11,B12,B13)</f>
@@ -5904,21 +7366,21 @@
       </c>
     </row>
     <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="15" t="str">
+      <c r="A15" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="14" t="str">
         <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R15C2YieldTermStructureHandle,A</v>
       </c>
-      <c r="C15" s="15" t="str">
+      <c r="C15" s="14" t="str">
         <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R15C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B16" s="3" t="str">
         <f>_xll.qlEuribor("3M",B15)</f>
@@ -5931,26 +7393,26 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C19" s="3">
         <v>0</v>
@@ -5958,7 +7420,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -5966,25 +7428,25 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
         <v>94</v>
-      </c>
-      <c r="C21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C24" s="3">
         <v>0</v>
@@ -5992,7 +7454,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C25" s="3">
         <v>100</v>
@@ -6008,15 +7470,15 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28" s="3" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
@@ -6025,15 +7487,15 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -6041,7 +7503,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B31" s="3" t="str">
         <f>_xll.qlFloatingRateBond(B4,B5,B14,B16,B17)</f>
@@ -6058,11 +7520,11 @@
       </c>
       <c r="B32" s="3">
         <f>_xll.qlBondNextCouponRate(B31)</f>
-        <v>0.29999999999999982</v>
+        <v>0.33645996454499488</v>
       </c>
       <c r="C32" s="3">
         <f>_xll.qlBondNextCouponRate(C31)</f>
-        <v>0.29999999999999982</v>
+        <v>0.33645996454499488</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -6079,16 +7541,16 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B34" s="2">
         <f>_xll.qlBondNextCashFlowDate(B31)</f>
-        <v>45755</v>
+        <v>46030</v>
       </c>
       <c r="C34" s="2">
         <f>_xll.qlBondNextCashFlowDate(C31)</f>
-        <v>45755</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -6131,7 +7593,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B38" s="3" t="b">
@@ -6162,11 +7624,11 @@
       </c>
       <c r="B40" s="2">
         <f>_xll.qlBondMaturityDate(B31)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
       <c r="C40" s="2">
         <f>_xll.qlBondMaturityDate(C31)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -6183,7 +7645,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="7" t="s">
         <v>30</v>
       </c>
       <c r="B42" s="3" t="str">
@@ -6197,7 +7659,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B43" s="3" t="str">
         <f>_xll.qlBondRedemption(B31)</f>
@@ -6210,7 +7672,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B44" s="3" t="str">
         <f>_xll.qlBondRedemptions(B31)</f>
@@ -6235,7 +7697,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B46" s="3">
@@ -6248,8 +7710,8 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
-        <v>60</v>
+      <c r="A47" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="B47" s="3">
         <f>_xll.qlBondNotionals(B31)</f>
@@ -6261,8 +7723,8 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
-        <v>56</v>
+      <c r="A48" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="B48" s="3" t="str">
         <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
@@ -6274,8 +7736,8 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
-        <v>52</v>
+      <c r="A49" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="B49" s="3" t="str">
         <f>_xll.qlBondSetDiscountingEngine(B31,B48)</f>
@@ -6287,151 +7749,110 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="9">
         <f>_xll.qlBondCleanPrice(B31)</f>
-        <v>99.998840118437755</v>
-      </c>
-      <c r="C50" s="10">
+        <v>98.609796527032515</v>
+      </c>
+      <c r="C50" s="9">
         <f>_xll.qlBondCleanPrice(C31)</f>
-        <v>100.51087441193772</v>
+        <v>98.609796527032515</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="10">
+      <c r="A51" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="9">
         <v>0.28928264971926221</v>
       </c>
-      <c r="C51" s="10">
+      <c r="C51" s="9">
         <v>0.28928264971926221</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="9">
         <f>_xll.qlBondCleanPrice2(B31,B51,"actual360","continuous")</f>
-        <v>99.998839809897291</v>
-      </c>
-      <c r="C52" s="10">
+        <v>98.60979524053667</v>
+      </c>
+      <c r="C52" s="9">
         <f>_xll.qlBondCleanPrice2(C31,C51,"actual360","continuous")</f>
-        <v>100.51087410920631</v>
+        <v>98.60979524053667</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B53" s="10" t="str">
+      <c r="B53" s="9">
         <f>_xll.qlBondDirtyPrice(B31)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 511, in qlBondDirtyPrice
-    return bond.dirtyPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
-    return _QuantLib.Bond_dirtyPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C53" s="10">
+        <v>98.796718729557512</v>
+      </c>
+      <c r="C53" s="9">
         <f>_xll.qlBondDirtyPrice(C31)</f>
-        <v>93.177541078604392</v>
+        <v>98.796718729557512</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="9">
         <f>_xll.qlBondDirtyPrice2(B31,B51,"actual360","CONTINUOUS","annual")</f>
-        <v>100.16550647656396</v>
-      </c>
-      <c r="C54" s="10">
+        <v>98.796717443061667</v>
+      </c>
+      <c r="C54" s="9">
         <f>_xll.qlBondDirtyPrice2(C31,C51,"actual360","CONTINUOUS","annual")</f>
-        <v>93.177540775872984</v>
+        <v>98.796717443061667</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B55" s="10" t="str">
+      <c r="B55" s="9">
         <f>_xll.qlBondYield(B31,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
-    return bond.bondYield(
-           ~~~~~~~~~~~~~~^
-        dc,
-        ^^^
-    ...&lt;3 lines&gt;...
-        max_evaluations
-        ^^^^^^^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C55" s="10" t="str">
+        <v>0.28928264971926221</v>
+      </c>
+      <c r="C55" s="9">
         <f>_xll.qlBondYield(C31,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
-    return bond.bondYield(
-           ~~~~~~~~~~~~~~^
-        dc,
-        ^^^
-    ...&lt;3 lines&gt;...
-        max_evaluations
-        ^^^^^^^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>0.28928264971926221</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B56" s="10" t="str">
+      <c r="A56" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B56" s="9" t="str">
         <f>_xll.qlBondPrice(B50,"clean")</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R56C2BondPrice,A</v>
       </c>
-      <c r="C56" s="10" t="str">
+      <c r="C56" s="9" t="str">
         <f>_xll.qlBondPrice(C50,"clean")</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R56C3BondPrice,A</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="9">
         <f>_xll.qlBondYield2(B31,B56,"actual360","CONTINUOUS","annual")</f>
-        <v>0.29112129323880687</v>
-      </c>
-      <c r="C57" s="10">
+        <v>0.28977749412491322</v>
+      </c>
+      <c r="C57" s="9">
         <f>_xll.qlBondYield2(C31,C56,"actual360","CONTINUOUS","annual")</f>
-        <v>0.21004909842705732</v>
+        <v>0.28977749412491322</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="11" t="s">
-        <v>55</v>
+      <c r="A58" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="B58" s="2">
         <v>45667</v>
@@ -6441,60 +7862,42 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="9">
         <f>_xll.qlBondAccruedAmount(B31,B58)</f>
-        <v>0.16666666666666657</v>
-      </c>
-      <c r="C59" s="10">
+        <v>0.18692220252499717</v>
+      </c>
+      <c r="C59" s="9">
         <f>_xll.qlBondAccruedAmount(C31,C58)</f>
-        <v>-7.3333333333333277</v>
+        <v>0.18692220252499717</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B60" s="10" t="str">
+      <c r="B60" s="9">
         <f>_xll.qlBondSettlementValue(B31)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 635, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C60" s="10" t="str">
+        <v>98.796718729557512</v>
+      </c>
+      <c r="C60" s="9">
         <f>_xll.qlBondSettlementValue(C31)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 635, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>98.796718729557512</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B61" s="9">
         <f>_xll.qlBondSettlementValue2(B31,B50)</f>
-        <v>100.16550678510443</v>
-      </c>
-      <c r="C61" s="10">
+        <v>98.796718729557512</v>
+      </c>
+      <c r="C61" s="9">
         <f>_xll.qlBondSettlementValue2(C31,C50)</f>
-        <v>93.177541078604392</v>
+        <v>98.796718729557512</v>
       </c>
     </row>
   </sheetData>
@@ -6553,24 +7956,24 @@
     </row>
     <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="12">
+        <v>73</v>
+      </c>
+      <c r="B6" s="11">
         <v>45665</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <v>45665</v>
       </c>
     </row>
     <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="12">
-        <v>46030</v>
-      </c>
-      <c r="C7" s="12">
-        <v>46030</v>
+        <v>74</v>
+      </c>
+      <c r="B7" s="11">
+        <v>49682</v>
+      </c>
+      <c r="C7" s="11">
+        <v>49682</v>
       </c>
     </row>
     <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -6578,15 +7981,15 @@
         <v>46</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9" s="6" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
@@ -6602,37 +8005,37 @@
         <v>47</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B13" s="6">
         <v>0</v>
@@ -6643,7 +8046,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B14" s="3" t="str">
         <f>_xll.qlSchedule(B6,B7,B8,B9,B10,B11,B12,B13)</f>
@@ -6655,29 +8058,29 @@
       </c>
     </row>
     <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>103</v>
+      <c r="A15" s="13" t="s">
+        <v>101</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="13" t="s">
         <v>46</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="13" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="6">
@@ -6688,19 +8091,19 @@
       </c>
     </row>
     <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>105</v>
+      <c r="A18" s="13" t="s">
+        <v>103</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>61</v>
+      <c r="A19" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="B19" s="6" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
@@ -6712,41 +8115,41 @@
       </c>
     </row>
     <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="B22" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="C22" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>111</v>
       </c>
       <c r="B23" s="6" t="str">
         <f>_xll.qlEuribor("3M")</f>
@@ -6758,8 +8161,8 @@
       </c>
     </row>
     <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>112</v>
+      <c r="A24" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="B24" s="6" t="str">
         <f>_xll.qlFlatForward(#REF!,0.03,"Actual360","Compounded","Quarterly")</f>
@@ -6772,7 +8175,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B25" s="3" t="str">
         <f>_xll.qlSwapIndex(B15,B16,B17,B18,B19,B20,B21,B22,B23,B24)</f>
@@ -6785,29 +8188,29 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B28" s="3">
         <v>2</v>
@@ -6817,8 +8220,8 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>93</v>
+      <c r="A29" s="12" t="s">
+        <v>91</v>
       </c>
       <c r="B29" s="3">
         <v>0</v>
@@ -6829,7 +8232,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B30" s="3">
         <v>3.0000000000000001E-3</v>
@@ -6839,8 +8242,8 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
-        <v>95</v>
+      <c r="A31" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="B31" s="3">
         <v>1</v>
@@ -6850,8 +8253,8 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
-        <v>96</v>
+      <c r="A32" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="B32" s="3">
         <v>1</v>
@@ -6862,7 +8265,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C33" s="3">
         <v>1</v>
@@ -6870,7 +8273,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C34" s="3">
         <v>120</v>
@@ -6886,7 +8289,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B36" s="3" t="str">
         <f>_xll.qlCmsRateBond(B4,B5,B14,B25,B26,B27,B28,B29,B30,B31,B32)</f>
@@ -6924,16 +8327,16 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B39" s="2">
         <f>_xll.qlBondNextCashFlowDate(B36)</f>
-        <v>45755</v>
+        <v>46030</v>
       </c>
       <c r="C39" s="2">
         <f>_xll.qlBondNextCashFlowDate(C36)</f>
-        <v>45755</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -6976,7 +8379,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B43" s="3" t="b">
@@ -7007,11 +8410,11 @@
       </c>
       <c r="B45" s="2">
         <f>_xll.qlBondMaturityDate(B36)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
       <c r="C45" s="2">
         <f>_xll.qlBondMaturityDate(C36)</f>
-        <v>46030</v>
+        <v>49682</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -7028,7 +8431,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="7" t="s">
         <v>30</v>
       </c>
       <c r="B47" s="3" t="str">
@@ -7042,7 +8445,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B48" s="3" t="str">
         <f>_xll.qlBondRedemption(B36)</f>
@@ -7055,7 +8458,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B49" s="3" t="str">
         <f>_xll.qlBondRedemptions(B36)</f>
@@ -7080,7 +8483,7 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B51" s="3">
@@ -7093,8 +8496,8 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
-        <v>60</v>
+      <c r="A52" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="B52" s="3">
         <f>_xll.qlBondNotionals(B36)</f>
@@ -7106,8 +8509,8 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
-        <v>56</v>
+      <c r="A53" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="B53" s="3" t="str">
         <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
@@ -7119,8 +8522,8 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
-        <v>52</v>
+      <c r="A54" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="B54" s="3" t="str">
         <f>_xll.qlBondSetDiscountingEngine(B36,B53)</f>
@@ -7132,178 +8535,110 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B55" s="10" t="str">
+      <c r="B55" s="9">
         <f>_xll.qlBondCleanPrice(B36)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C55" s="10">
+        <v>285.41003697223789</v>
+      </c>
+      <c r="C55" s="9">
         <f>_xll.qlBondCleanPrice(C36)</f>
-        <v>89.639709460333037</v>
+        <v>4.7644717638374612</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B56" s="10">
+      <c r="A56" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56" s="9">
         <v>0.28928264971926221</v>
       </c>
-      <c r="C56" s="10">
+      <c r="C56" s="9">
         <v>0.28928264971926221</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="9">
         <f>_xll.qlBondCleanPrice2(B36,B56,"actual360","continuous")</f>
-        <v>158.97331939573809</v>
-      </c>
-      <c r="C57" s="10">
+        <v>285.4100334433362</v>
+      </c>
+      <c r="C57" s="9">
         <f>_xll.qlBondCleanPrice2(C36,C56,"actual360","continuous")</f>
-        <v>89.639709152949933</v>
+        <v>4.7644715831310851</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B58" s="10" t="str">
+      <c r="B58" s="9">
         <f>_xll.qlBondDirtyPrice(B36)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 511, in qlBondDirtyPrice
-    return bond.dirtyPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
-    return _QuantLib.Bond_dirtyPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C58" s="10">
+        <v>285.96559252779343</v>
+      </c>
+      <c r="C58" s="9">
         <f>_xll.qlBondDirtyPrice(C36)</f>
-        <v>89.639709460333037</v>
+        <v>4.7644717638374612</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="9">
         <f>_xll.qlBondDirtyPrice2(B36,B56,"actual360","CONTINUOUS","annual")</f>
-        <v>159.52887495129363</v>
-      </c>
-      <c r="C59" s="10">
+        <v>285.96558899889175</v>
+      </c>
+      <c r="C59" s="9">
         <f>_xll.qlBondDirtyPrice2(C36,C56,"actual360","CONTINUOUS","annual")</f>
-        <v>89.639709152949933</v>
+        <v>4.7644715831310851</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B60" s="10" t="str">
+      <c r="B60" s="9">
         <f>_xll.qlBondYield(B36,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
-    return bond.bondYield(
-           ~~~~~~~~~~~~~~^
-        dc,
-        ^^^
-    ...&lt;3 lines&gt;...
-        max_evaluations
-        ^^^^^^^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C60" s="10" t="str">
+        <v>0.28928264971926221</v>
+      </c>
+      <c r="C60" s="9">
         <f>_xll.qlBondYield(C36,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 563, in qlBondYield
-    return bond.bondYield(
-           ~~~~~~~~~~~~~~^
-        dc,
-        ^^^
-    ...&lt;3 lines&gt;...
-        max_evaluations
-        ^^^^^^^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>0.28928264788123847</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B61" s="10" t="str">
+      <c r="A61" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B61" s="9" t="str">
         <f>_xll.qlBondPrice(B55,"clean")</f>
-        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float</v>
-      </c>
-      <c r="C61" s="10" t="str">
+        <v>欣[test_bonds.xlsx]CmsRateBond!R61C2BondPrice,A</v>
+      </c>
+      <c r="C61" s="9" t="str">
         <f>_xll.qlBondPrice(C55,"clean")</f>
         <v>欣[test_bonds.xlsx]CmsRateBond!R61C3BondPrice,A</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="10" t="str">
+      <c r="B62" s="9">
         <f>_xll.qlBondYield2(B36,B61,"actual360","CONTINUOUS","annual")</f>
-        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float': Expected cache string</v>
-      </c>
-      <c r="C62" s="10">
+        <v>0.28981883443572526</v>
+      </c>
+      <c r="C62" s="9">
         <f>_xll.qlBondYield2(C36,C61,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928265005463161</v>
+        <v>0.28928264788123847</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="11" t="s">
-        <v>55</v>
+      <c r="A63" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="B63" s="2">
         <v>45667</v>
@@ -7313,69 +8648,42 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B64" s="9">
         <f>_xll.qlBondAccruedAmount(B36,B63)</f>
         <v>0.55555555555555358</v>
       </c>
-      <c r="C64" s="10">
+      <c r="C64" s="9">
         <f>_xll.qlBondAccruedAmount(C36,C63)</f>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B65" s="10" t="str">
+      <c r="B65" s="9">
         <f>_xll.qlBondSettlementValue(B36)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 635, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C65" s="10" t="str">
+        <v>285.96559252779343</v>
+      </c>
+      <c r="C65" s="9">
         <f>_xll.qlBondSettlementValue(C36)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 635, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>4.7644717638374612</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B66" s="10" t="str">
+      <c r="B66" s="9">
         <f>_xll.qlBondSettlementValue2(B36,B55)</f>
-        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 470, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float</v>
-      </c>
-      <c r="C66" s="10">
+        <v>285.96559252779343</v>
+      </c>
+      <c r="C66" s="9">
         <f>_xll.qlBondSettlementValue2(C36,C55)</f>
-        <v>89.639709460333037</v>
+        <v>4.7644717638374612</v>
       </c>
     </row>
   </sheetData>

--- a/tests/workbooks/test_bonds.xlsx
+++ b/tests/workbooks/test_bonds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD11E35-3656-452B-BDAE-A27D463BD4B8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED47D65-5269-434E-B33E-8578ED008772}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="32370" windowHeight="9360" xr2:uid="{A8952777-E146-413E-A9B0-D4A573A66C27}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="154">
   <si>
     <t>Bond</t>
   </si>
@@ -491,6 +491,15 @@
   </si>
   <si>
     <t>30/360</t>
+  </si>
+  <si>
+    <t>qlInstrumentSetPricingEngine</t>
+  </si>
+  <si>
+    <t>qlBondDiscountingEngine</t>
+  </si>
+  <si>
+    <t>qlInstrumentPricingEngine</t>
   </si>
 </sst>
 </file>
@@ -680,7 +689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -734,6 +743,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1072,11 +1084,11 @@
       <c r="B2" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="33"/>
-      <c r="E2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
     </row>
     <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="17"/>
@@ -1225,7 +1237,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28ABD84F-1436-4AE1-BC17-091C65B56114}">
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.5703125" customWidth="1"/>
@@ -1265,7 +1277,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="36" t="s">
         <v>82</v>
       </c>
       <c r="B5" s="3">
@@ -1276,7 +1288,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="35"/>
+      <c r="A6" s="36"/>
       <c r="B6" s="3">
         <v>102</v>
       </c>
@@ -1285,7 +1297,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="35"/>
+      <c r="A7" s="36"/>
       <c r="B7" s="3">
         <v>101</v>
       </c>
@@ -1772,7 +1784,7 @@
         <f>_xll.qlBondRedemption(B37)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 365, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 350, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -1785,7 +1797,7 @@
         <f>_xll.qlBondRedemption(C37)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 365, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 350, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -1852,177 +1864,190 @@
         <v>55</v>
       </c>
       <c r="B54" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R54C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C54" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R54C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="B55" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(B37,B54)</f>
+        <f>_xll.qlDiscountingBondEngine(B54)</f>
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R55C2DiscountingBondEngine,A</v>
       </c>
       <c r="C55" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(C37,C54)</f>
+        <f>_xll.qlDiscountingBondEngine(C54)</f>
         <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R55C3DiscountingBondEngine,A</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B56" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(B37,B55)</f>
+        <v>1</v>
+      </c>
+      <c r="C56" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(C37,C55)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B56" s="9">
+      <c r="B57" s="9">
         <f>_xll.qlBondCleanPrice(B37)</f>
-        <v>5.159421325147961</v>
-      </c>
-      <c r="C56" s="9">
+        <v>72.117682106498307</v>
+      </c>
+      <c r="C57" s="9">
         <f>_xll.qlBondCleanPrice(C37)</f>
-        <v>5.9932874425424671</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="10" t="s">
+        <v>74.834890455035776</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="9">
-        <v>0.28928264971926221</v>
-      </c>
-      <c r="C57" s="9">
-        <v>0.28928264971926221</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="B58" s="9">
-        <f>_xll.qlBondCleanPrice2(B37,B57,"actual360","continuous")</f>
-        <v>5.1594211712767493</v>
+        <v>2.9888064241409308E-2</v>
       </c>
       <c r="C58" s="9">
-        <f>_xll.qlBondCleanPrice2(C37,C57,"actual360","continuous")</f>
-        <v>5.9932872787070313</v>
+        <v>2.9888064241409308E-2</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B59" s="9">
-        <f>_xll.qlBondDirtyPrice(B37)</f>
-        <v>5.159421325147961</v>
+        <f>_xll.qlBondCleanPrice2(B37,B58,"actual360","continuous")</f>
+        <v>72.117678263617449</v>
       </c>
       <c r="C59" s="9">
-        <f>_xll.qlBondDirtyPrice(C37)</f>
-        <v>5.9949541092091447</v>
+        <f>_xll.qlBondCleanPrice2(C37,C58,"actual360","continuous")</f>
+        <v>74.834886535610039</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B60" s="9">
-        <f>_xll.qlBondDirtyPrice2(B37,B57,"actual360","CONTINUOUS","annual")</f>
-        <v>5.1594211712767493</v>
+        <f>_xll.qlBondDirtyPrice(B37)</f>
+        <v>72.117682106498307</v>
       </c>
       <c r="C60" s="9">
-        <f>_xll.qlBondDirtyPrice2(C37,C57,"actual360","CONTINUOUS","annual")</f>
-        <v>5.9949539453737088</v>
+        <f>_xll.qlBondDirtyPrice(C37)</f>
+        <v>74.836557121702455</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" s="9">
+        <f>_xll.qlBondDirtyPrice2(B37,B58,"actual360","CONTINUOUS","annual")</f>
+        <v>72.117678263617449</v>
+      </c>
+      <c r="C61" s="9">
+        <f>_xll.qlBondDirtyPrice2(C37,C58,"actual360","CONTINUOUS","annual")</f>
+        <v>74.836553202276718</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B61" s="9">
+      <c r="B62" s="9">
         <f>_xll.qlBondYield(B37,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264139762888</v>
-      </c>
-      <c r="C61" s="9">
+        <v>2.9888064241409308E-2</v>
+      </c>
+      <c r="C62" s="9">
         <f>_xll.qlBondYield(C37,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264388044844</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="10" t="s">
+        <v>2.9888064241409308E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B62" s="9" t="str">
-        <f>_xll.qlBondPrice(B56,"clean")</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R62C2BondPrice,A</v>
-      </c>
-      <c r="C62" s="9" t="str">
-        <f>_xll.qlBondPrice(C56,"clean")</f>
-        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R62C3BondPrice,A</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
+      <c r="B63" s="9" t="str">
+        <f>_xll.qlBondPrice(B57,"clean")</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R63C2BondPrice,A</v>
+      </c>
+      <c r="C63" s="9" t="str">
+        <f>_xll.qlBondPrice(C57,"clean")</f>
+        <v>欣[test_bonds.xlsx]AmortizingCmsRateBond!R63C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B63" s="9">
-        <f>_xll.qlBondYield2(B37,B62,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264139762888</v>
-      </c>
-      <c r="C63" s="9">
-        <f>_xll.qlBondYield2(C37,C62,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28931725029223304</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="10" t="s">
+      <c r="B64" s="9">
+        <f>_xll.qlBondYield2(B37,B63,"actual360","CONTINUOUS","annual")</f>
+        <v>2.9888064241409308E-2</v>
+      </c>
+      <c r="C64" s="9">
+        <f>_xll.qlBondYield2(C37,C63,"actual360","CONTINUOUS","annual")</f>
+        <v>2.9890143346786503E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B65" s="2">
         <v>45667</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C65" s="2">
         <v>45667</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="9">
-        <f>_xll.qlBondAccruedAmount(B37,B64)</f>
-        <v>0</v>
-      </c>
-      <c r="C65" s="9">
-        <f>_xll.qlBondAccruedAmount(C37,C64)</f>
-        <v>1.6666666666775853E-3</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B66" s="9">
-        <f>_xll.qlBondSettlementValue(B37)</f>
-        <v>5.3142039649023998</v>
+        <f>_xll.qlBondAccruedAmount(B37,B65)</f>
+        <v>0</v>
       </c>
       <c r="C66" s="9">
-        <f>_xll.qlBondSettlementValue(C37)</f>
-        <v>6.1748027324854196</v>
+        <f>_xll.qlBondAccruedAmount(C37,C65)</f>
+        <v>1.6666666666775853E-3</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B67" s="9">
+        <f>_xll.qlBondSettlementValue(B37)</f>
+        <v>74.281212569693253</v>
+      </c>
+      <c r="C67" s="9">
+        <f>_xll.qlBondSettlementValue(C37)</f>
+        <v>77.081653835353535</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B67" s="9">
-        <f>_xll.qlBondSettlementValue2(B37,B56)</f>
-        <v>5.3142039649023998</v>
-      </c>
-      <c r="C67" s="9">
-        <f>_xll.qlBondSettlementValue2(C37,C56)</f>
-        <v>6.1748027324854187</v>
+      <c r="B68" s="9">
+        <f>_xll.qlBondSettlementValue2(B37,B57)</f>
+        <v>74.281212569693253</v>
+      </c>
+      <c r="C68" s="9">
+        <f>_xll.qlBondSettlementValue2(C37,C57)</f>
+        <v>77.081653835353521</v>
       </c>
     </row>
   </sheetData>
@@ -2114,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F0A1FE9-B1FE-4762-AEA9-E4B3F6C519F7}">
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.7109375" customWidth="1"/>
@@ -2144,7 +2169,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3">
         <v>2</v>
@@ -2265,32 +2290,32 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="36" t="s">
         <v>66</v>
       </c>
       <c r="B15" s="3">
-        <v>0.4</v>
+        <v>0.03</v>
       </c>
       <c r="C15" s="3">
-        <v>0.4</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
+      <c r="A16" s="36"/>
       <c r="B16" s="3">
-        <v>0.5</v>
+        <v>0.03</v>
       </c>
       <c r="C16" s="3">
-        <v>0.5</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="35"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="3">
-        <v>0.6</v>
+        <v>0.03</v>
       </c>
       <c r="C17" s="3">
-        <v>0.6</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2320,10 +2345,10 @@
         <v>63</v>
       </c>
       <c r="B20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2389,6 +2414,9 @@
       <c r="A26" t="s">
         <v>69</v>
       </c>
+      <c r="B26" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="C26" s="3" t="s">
         <v>76</v>
       </c>
@@ -2397,6 +2425,10 @@
       <c r="A27" t="s">
         <v>70</v>
       </c>
+      <c r="B27" s="3" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
       <c r="C27" s="3" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
         <v>TARGET</v>
@@ -2437,11 +2469,11 @@
       </c>
       <c r="B31" s="3">
         <f>_xll.qlBondNextCouponRate(B30)</f>
-        <v>0.4</v>
+        <v>0.03</v>
       </c>
       <c r="C31" s="3">
         <f>_xll.qlBondNextCouponRate(C30)</f>
-        <v>0.4</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2489,7 +2521,7 @@
       </c>
       <c r="B35" s="3">
         <f>_xll.qlBondSettlementDays(B30)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35" s="3">
         <f>_xll.qlBondSettlementDays(C30)</f>
@@ -2502,7 +2534,7 @@
       </c>
       <c r="B36" s="2">
         <f>_xll.qlBondSettlementDate(B30)</f>
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="C36" s="2">
         <f>_xll.qlBondSettlementDate(C30)</f>
@@ -2644,10 +2676,10 @@
         <v>139</v>
       </c>
       <c r="B47" s="3">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="C47" s="3">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -2655,11 +2687,11 @@
         <v>110</v>
       </c>
       <c r="B48" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(#REF!,0.025,"actual360")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R48C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C48" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(#REF!,0.025,"actual360")</f>
         <v>欣[test_bonds.xlsx]CallableFixedRateBond!R48C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2667,194 +2699,220 @@
       <c r="A49" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B49" s="3" t="e">
-        <f>_xll.qlBlackCallableFixedRateBondEngine(B30,B47,B48)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C49" s="3" t="e">
-        <f>_xll.qlBlackCallableFixedRateBondEngine(C30,C47,C48)</f>
-        <v>#N/A</v>
+      <c r="B49" s="3" t="str">
+        <f>_xll.qlBlackCallableFixedRateBondEngine(B47,B48)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R49C2BlackCallableFixedRateBondEngine,A</v>
+      </c>
+      <c r="C49" s="3" t="str">
+        <f>_xll.qlBlackCallableFixedRateBondEngine(C47,C48)</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R49C3BlackCallableFixedRateBondEngine,A</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="B50" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(B30,B49)</f>
+        <v>1</v>
+      </c>
+      <c r="C50" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(C30,C49)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B51" s="33">
         <f>_xll.qlBondCleanPrice(B30)</f>
-        <v>148.46385265411533</v>
-      </c>
-      <c r="C50" s="9">
+        <v>104.08408808408915</v>
+      </c>
+      <c r="C51" s="9">
         <f>_xll.qlBondCleanPrice(C30)</f>
-        <v>150.59646745144829</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="10" t="s">
+        <v>104.49668091130677</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B52" s="9">
+        <v>2.8928264971926201E-2</v>
+      </c>
+      <c r="C52" s="9">
         <v>0.28928264971926221</v>
-      </c>
-      <c r="C51" s="9">
-        <v>0.28928264971926221</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B52" s="9">
-        <f>_xll.qlBondCleanPrice2(B30,B51,"actual360","continuous")</f>
-        <v>148.46385071667095</v>
-      </c>
-      <c r="C52" s="9">
-        <f>_xll.qlBondCleanPrice2(C30,C51,"actual360","continuous")</f>
-        <v>150.59646548594415</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B53" s="9">
-        <f>_xll.qlBondDirtyPrice(B30)</f>
-        <v>148.68607487633753</v>
+        <f>_xll.qlBondCleanPrice2(B30,B52,"actual360","continuous")</f>
+        <v>100.20194238732337</v>
       </c>
       <c r="C53" s="9">
-        <f>_xll.qlBondDirtyPrice(C30)</f>
-        <v>150.81868967367049</v>
+        <f>_xll.qlBondCleanPrice2(C30,C52,"actual360","continuous")</f>
+        <v>12.534456719148118</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B54" s="9">
-        <f>_xll.qlBondDirtyPrice2(B30,B51,"actual360","CONTINUOUS","annual")</f>
-        <v>148.68607293889315</v>
+        <f>_xll.qlBondDirtyPrice(B30)</f>
+        <v>104.12575475075582</v>
       </c>
       <c r="C54" s="9">
-        <f>_xll.qlBondDirtyPrice2(C30,C51,"actual360","CONTINUOUS","annual")</f>
-        <v>150.81868770816635</v>
+        <f>_xll.qlBondDirtyPrice(C30)</f>
+        <v>104.51334757797343</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" s="9">
+        <f>_xll.qlBondDirtyPrice2(B30,B52,"actual360","CONTINUOUS","annual")</f>
+        <v>100.24360905399004</v>
+      </c>
+      <c r="C55" s="9">
+        <f>_xll.qlBondDirtyPrice2(C30,C52,"actual360","CONTINUOUS","annual")</f>
+        <v>12.551123385814783</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B56" s="9">
         <f>_xll.qlBondYield(B30,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
-      </c>
-      <c r="C55" s="9">
+        <v>2.5000006914138798E-2</v>
+      </c>
+      <c r="C56" s="9">
         <f>_xll.qlBondYield(C30,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="10" t="s">
+        <v>2.5000006914138798E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B56" s="9" t="str">
-        <f>_xll.qlBondPrice(B50,"clean")</f>
-        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R56C2BondPrice,A</v>
-      </c>
-      <c r="C56" s="9" t="str">
-        <f>_xll.qlBondPrice(C50,"clean")</f>
-        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R56C3BondPrice,A</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
+      <c r="B57" s="9" t="str">
+        <f>_xll.qlBondPrice(B51,"clean")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R57C2BondPrice,A</v>
+      </c>
+      <c r="C57" s="9" t="str">
+        <f>_xll.qlBondPrice(C51,"clean")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R57C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B57" s="9">
-        <f>_xll.qlBondYield2(B30,B56,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28967312533166412</v>
-      </c>
-      <c r="C57" s="9">
-        <f>_xll.qlBondYield2(C30,C56,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28966754837324626</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="10" t="s">
+      <c r="B58" s="9">
+        <f>_xll.qlBondYield2(B30,B57,"actual360","CONTINUOUS","annual")</f>
+        <v>2.5041315031051642E-2</v>
+      </c>
+      <c r="C58" s="9">
+        <f>_xll.qlBondYield2(C30,C57,"actual360","CONTINUOUS","annual")</f>
+        <v>2.5016478586196905E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B59" s="2">
         <v>45667</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C59" s="2">
         <v>45667</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="9">
-        <f>_xll.qlBondAccruedAmount(B30,B58)</f>
-        <v>0.22222222222221255</v>
-      </c>
-      <c r="C59" s="9">
-        <f>_xll.qlBondAccruedAmount(C30,C58)</f>
-        <v>0.22222222222221255</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B60" s="9">
-        <f>_xll.qlBondSettlementValue(B30)</f>
-        <v>148.68607487633753</v>
+        <f>_xll.qlBondAccruedAmount(B30,B59)</f>
+        <v>1.6666666666664831E-2</v>
       </c>
       <c r="C60" s="9">
-        <f>_xll.qlBondSettlementValue(C30)</f>
-        <v>150.81868967367049</v>
+        <f>_xll.qlBondAccruedAmount(C30,C59)</f>
+        <v>1.6666666666664831E-2</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B61" s="9">
-        <f>_xll.qlBondSettlementValue2(B30,B50)</f>
-        <v>148.68607487633753</v>
+        <f>_xll.qlBondSettlementValue(B30)</f>
+        <v>104.12575475075583</v>
       </c>
       <c r="C61" s="9">
-        <f>_xll.qlBondSettlementValue2(C30,C50)</f>
-        <v>150.81868967367049</v>
+        <f>_xll.qlBondSettlementValue(C30)</f>
+        <v>104.51334757797343</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="9">
+        <f>_xll.qlBondSettlementValue2(B30,B51)</f>
+        <v>104.12575475075583</v>
+      </c>
+      <c r="C62" s="9">
+        <f>_xll.qlBondSettlementValue2(C30,C51)</f>
+        <v>104.51334757797343</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B62" s="3" t="str">
+      <c r="B63" s="3" t="str">
         <f>_xll.qlCallableBondCallability(B30)</f>
-        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R62C2Callability,A</v>
-      </c>
-      <c r="C62" s="3" t="str">
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R63C2Callability,A</v>
+      </c>
+      <c r="C63" s="3" t="str">
         <f>_xll.qlCallableBondCallability(C30)</f>
-        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R62C3Callability,A</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="32" t="s">
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R63C3Callability,A</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B64" s="3" t="str">
+        <f>_xll.qlBondPrice(B51,"Clean")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R64C2BondPrice,A</v>
+      </c>
+      <c r="C64" s="3" t="str">
+        <f>_xll.qlBondPrice(C51,"Clean")</f>
+        <v>欣[test_bonds.xlsx]CallableFixedRateBond!R64C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="32" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="32" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="B64" s="3" t="str">
+      <c r="B66" s="3" t="str">
         <f>_xll.qlCallableBondOAS(B30,43.82,B48,"Actual/360","Simple","Annual",,,1000)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations (last bracket attempt: f[-6.54557e+272,1.70185e+273] -&gt; [-104.405,-104.405])
+        <v xml:space="preserve">RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations (last bracket attempt: f[-6.54557e+272,1.70185e+273] -&gt; [-60.2279,-60.2279])
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1118, in qlCallableBondOAS
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1105, in qlCallableBondOAS
     return callable_bond.OAS(
            ~~~~~~~~~~~~~~~~~^
         clean_price,
@@ -2867,14 +2925,14 @@
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26304, in OAS
     return _QuantLib.CallableBond_OAS(self, *args)
            ~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: unable to bracket root in 1000 function evaluations (last bracket attempt: f[-6.54557e+272,1.70185e+273] -&gt; [-104.405,-104.405])
+RuntimeError: unable to bracket root in 1000 function evaluations (last bracket attempt: f[-6.54557e+272,1.70185e+273] -&gt; [-60.2279,-60.2279])
 </v>
       </c>
-      <c r="C64" s="3" t="str">
+      <c r="C66" s="3" t="str">
         <f>_xll.qlCallableBondOAS(C30,43.82,C48,"Actual/360","Simple","Annual",,,1000)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations (last bracket attempt: f[-6.54557e+272,1.70185e+273] -&gt; [-106.534,-106.534])
+        <v xml:space="preserve">RuntimeError: RuntimeError: unable to bracket root in 1000 function evaluations (last bracket attempt: f[-6.54557e+272,1.70185e+273] -&gt; [-60.6622,-60.6622])
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1118, in qlCallableBondOAS
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1105, in qlCallableBondOAS
     return callable_bond.OAS(
            ~~~~~~~~~~~~~~~~~^
         clean_price,
@@ -2887,19 +2945,779 @@
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26304, in OAS
     return _QuantLib.CallableBond_OAS(self, *args)
            ~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: unable to bracket root in 1000 function evaluations (last bracket attempt: f[-6.54557e+272,1.70185e+273] -&gt; [-106.534,-106.534])
+RuntimeError: unable to bracket root in 1000 function evaluations (last bracket attempt: f[-6.54557e+272,1.70185e+273] -&gt; [-60.6622,-60.6622])
 </v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B65" s="3" t="str">
+      <c r="B67" s="3">
         <f>_xll.qlCallableBondCleanPriceOAS(B30,0.3,B48,"actual/360","simple","annual")</f>
+        <v>104.04793958427845</v>
+      </c>
+      <c r="C67" s="3">
+        <f>_xll.qlCallableBondCleanPriceOAS(C30,0.3,C48,"actual/360","simple","annual")</f>
+        <v>104.48216617657867</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B68" s="3">
+        <f>_xll.qlCallableBondEffectiveDuration(B30,0.3,B48,"actual/360","compounded","annual")</f>
+        <v>0</v>
+      </c>
+      <c r="C68" s="3">
+        <f>_xll.qlCallableBondEffectiveDuration(C30,0.3,C48,"actual/360","compounded","annual")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" s="3">
+        <f>_xll.qlCallableBondEffectiveConvexity(B30,0.3,B48,"actual/360","compounded","annual")</f>
+        <v>0</v>
+      </c>
+      <c r="C69" s="3">
+        <f>_xll.qlCallableBondEffectiveConvexity(C30,0.3,C48,"actual/360","compounded","annual")</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:A17"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4EF9C2-FD4D-4E7F-8154-C8E782972C6B}">
+  <dimension ref="A1:C54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="44.140625" customWidth="1"/>
+    <col min="2" max="2" width="89.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="73.28515625" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2">
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="3" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C6" s="3" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2">
+        <v>49682</v>
+      </c>
+      <c r="C7" s="2">
+        <v>49682</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2">
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2" t="str">
+        <f>_xll.qlBondPrice(100,"CLEAN")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R12C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2">
+        <v>47664</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="3" t="str">
+        <f>_xll.qlCallability(C12,C13,C14)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R15C3Callability,A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" s="3" t="str">
+        <f>_xll.qlCallableZeroCouponBond(B4,B5,B6,B7,B8)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R16C2CallableZeroCouponBond,A</v>
+      </c>
+      <c r="C16" s="3" t="str">
+        <f>_xll.qlCallableZeroCouponBond(C4,C5,C6,C7,C8,C9,C10,C11,C15)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R16C3CallableZeroCouponBond,A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="3" t="str">
+        <f>_xll.qlBondNextCouponRate(B16)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 216, in qlBondNextCouponRate
+    return bond.nextCouponRate(date)
+           ~~~~~~~~~~~~~~~~~~~^^^^^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
+    return _QuantLib.Bond_nextCouponRate(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: no coupon paid at cashflow date January 8th, 2036
+</v>
+      </c>
+      <c r="C17" s="3" t="str">
+        <f>_xll.qlBondNextCouponRate(C16)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 216, in qlBondNextCouponRate
+    return bond.nextCouponRate(date)
+           ~~~~~~~~~~~~~~~~~~~^^^^^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
+    return _QuantLib.Bond_nextCouponRate(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: no coupon paid at cashflow date January 8th, 2036
+</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="3">
+        <f>_xll.qlBondPreviousCouponRate(B16)</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="3">
+        <f>_xll.qlBondPreviousCouponRate(C16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="2">
+        <f>_xll.qlBondNextCashFlowDate(B16)</f>
+        <v>49682</v>
+      </c>
+      <c r="C19" s="2">
+        <f>_xll.qlBondNextCashFlowDate(C16)</f>
+        <v>49682</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="2">
+        <f>_xll.qlBondPreviousCashFlowDate(B16)</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <f>_xll.qlBondPreviousCashFlowDate(C16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="3">
+        <f>_xll.qlBondSettlementDays(B16)</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="3">
+        <f>_xll.qlBondSettlementDays(C16)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="2">
+        <f>_xll.qlBondSettlementDate(B16)</f>
+        <v>45667</v>
+      </c>
+      <c r="C22" s="2">
+        <f>_xll.qlBondSettlementDate(C16)</f>
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <f>_xll.qlBondIsTradable(B16)</f>
+        <v>1</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <f>_xll.qlBondIsTradable(C16)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="2">
+        <f>_xll.qlBondStartDate(B16)</f>
+        <v>49682</v>
+      </c>
+      <c r="C24" s="2">
+        <f>_xll.qlBondStartDate(C16)</f>
+        <v>49682</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="2">
+        <f>_xll.qlBondMaturityDate(B16)</f>
+        <v>49682</v>
+      </c>
+      <c r="C25" s="2">
+        <f>_xll.qlBondMaturityDate(C16)</f>
+        <v>49682</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="2">
+        <f>_xll.qlBondIssueDate(B16)</f>
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
+        <f>_xll.qlBondIssueDate(C16)</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="3" t="str">
+        <f>_xll.qlBondCashFlows(B16)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R27C2CashFlow,A</v>
+      </c>
+      <c r="C27" s="3" t="str">
+        <f>_xll.qlBondCashFlows(C16)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R27C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="3" t="str">
+        <f>_xll.qlBondRedemption(B16)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R28C2CashFlow,A</v>
+      </c>
+      <c r="C28" s="3" t="str">
+        <f>_xll.qlBondRedemption(C16)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R28C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="3" t="str">
+        <f>_xll.qlBondRedemptions(B16)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R29C2CashFlow,A</v>
+      </c>
+      <c r="C29" s="3" t="str">
+        <f>_xll.qlBondRedemptions(C16)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R29C3CashFlow,A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="3" t="str">
+        <f>_xll.qlBondCalendar(B16)</f>
+        <v>TARGET</v>
+      </c>
+      <c r="C30" s="3" t="str">
+        <f>_xll.qlBondCalendar(C16)</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="3">
+        <f>_xll.qlBondNotional(B16)</f>
+        <v>100</v>
+      </c>
+      <c r="C31" s="3">
+        <f>_xll.qlBondNotional(C16)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="3">
+        <f>_xll.qlBondNotionals(B16)</f>
+        <v>100</v>
+      </c>
+      <c r="C32" s="3">
+        <f>_xll.qlBondNotionals(C16)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="B33" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="B34" s="3" t="str">
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R34C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C34" s="3" t="str">
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R34C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="3" t="str">
+        <f>_xll.qlBlackCallableFixedRateBondEngine(B33,B34)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R35C2BlackCallableFixedRateBondEngine,A</v>
+      </c>
+      <c r="C35" s="3" t="str">
+        <f>_xll.qlBlackCallableFixedRateBondEngine(C33,C34)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R35C3BlackCallableFixedRateBondEngine,A</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(B16,B35)</f>
+        <v>1</v>
+      </c>
+      <c r="C36" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(C16,C35)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" s="9" t="str">
+        <f>_xll.qlBondCleanPrice(B16)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 407, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+</v>
+      </c>
+      <c r="C37" s="9">
+        <f>_xll.qlBondCleanPrice(C16)</f>
+        <v>71.653019933502407</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="9">
+        <v>2.9888064241409308E-2</v>
+      </c>
+      <c r="C38" s="9">
+        <v>2.9888064241409308E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="9">
+        <f>_xll.qlBondCleanPrice2(B16,B38,"actual360","continuous")</f>
+        <v>71.65301602846877</v>
+      </c>
+      <c r="C39" s="9">
+        <f>_xll.qlBondCleanPrice2(C16,C38,"actual360","continuous")</f>
+        <v>71.65301602846877</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="9" t="str">
+        <f>_xll.qlBondDirtyPrice(B16)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 442, in qlBondDirtyPrice
+    return bond.dirtyPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
+    return _QuantLib.Bond_dirtyPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+</v>
+      </c>
+      <c r="C40" s="9">
+        <f>_xll.qlBondDirtyPrice(C16)</f>
+        <v>71.653019933502407</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="9">
+        <f>_xll.qlBondDirtyPrice2(B16,B38,"actual360","CONTINUOUS","annual")</f>
+        <v>71.65301602846877</v>
+      </c>
+      <c r="C41" s="9">
+        <f>_xll.qlBondDirtyPrice2(C16,C38,"actual360","CONTINUOUS","annual")</f>
+        <v>71.65301602846877</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="9" t="str">
+        <f>_xll.qlBondYield(B16,"actual360","CONTINUOUS","annual")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 490, in qlBondYield
+    return bond.bondYield(dc, compounding, freq, accuracy, max_evaluations)
+           ~~~~~~~~~~~~~~^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
+    return _QuantLib.Bond_bondYield(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+</v>
+      </c>
+      <c r="C42" s="9">
+        <f>_xll.qlBondYield(C16,"actual360","CONTINUOUS","annual")</f>
+        <v>2.9888064241409308E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B43" s="9" t="str">
+        <f>_xll.qlBondPrice(B37,"clean")</f>
+        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 407, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+': Expected float</v>
+      </c>
+      <c r="C43" s="9" t="str">
+        <f>_xll.qlBondPrice(C37,"clean")</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R43C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="9" t="str">
+        <f>_xll.qlBondYield2(B16,B43,"actual360","CONTINUOUS","annual")</f>
+        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 407, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+': Expected float': Expected cache string</v>
+      </c>
+      <c r="C44" s="9">
+        <f>_xll.qlBondYield2(C16,C43,"actual360","CONTINUOUS","annual")</f>
+        <v>2.9888064241409308E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" s="2">
+        <v>45667</v>
+      </c>
+      <c r="C45" s="2">
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="9">
+        <f>_xll.qlBondAccruedAmount(B16,B45)</f>
+        <v>0</v>
+      </c>
+      <c r="C46" s="9">
+        <f>_xll.qlBondAccruedAmount(C16,C45)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="9" t="str">
+        <f>_xll.qlBondSettlementValue(B16)</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 547, in qlBondSettlementValue
+    return bond.settlementValue()
+           ~~~~~~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
+    return _QuantLib.Bond_settlementValue(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+</v>
+      </c>
+      <c r="C47" s="9">
+        <f>_xll.qlBondSettlementValue(C16)</f>
+        <v>71.653019933502407</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="9" t="str">
+        <f>_xll.qlBondSettlementValue2(B16,B37)</f>
+        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 407, in qlBondCleanPrice
+    return bond.cleanPrice()
+           ~~~~~~~~~~~~~~~^^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
+    return _QuantLib.Bond_cleanPrice(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+': Expected float</v>
+      </c>
+      <c r="C48" s="9">
+        <f>_xll.qlBondSettlementValue2(C16,C37)</f>
+        <v>71.653019933502407</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B49" s="3">
+        <f>_xll.qlCallableBondCallability(B16)</f>
+        <v>0</v>
+      </c>
+      <c r="C49" s="3" t="str">
+        <f>_xll.qlCallableBondCallability(C16)</f>
+        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R49C3Callability,A</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="B51" s="3" t="str">
+        <f>_xll.qlCallableBondOAS(B16,43.82,B34,"Actual/360","Simple","Annual")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1105, in qlCallableBondOAS
+    return callable_bond.OAS(
+           ~~~~~~~~~~~~~~~~~^
+        clean_price,
+        ^^^^^^^^^^^^
+    ...&lt;7 lines&gt;...
+        guess,
+        ^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26304, in OAS
+    return _QuantLib.CallableBond_OAS(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: Must have exactly one call/put date to use Black Engine
+</v>
+      </c>
+      <c r="C51" s="3" t="str">
+        <f>_xll.qlCallableBondOAS(C16,43.82,C34,"Actual/360","Simple","Annual")</f>
+        <v xml:space="preserve">RuntimeError: RuntimeError: unable to bracket root in 100 function evaluations (last bracket attempt: f[-6.79107e+23,1.76568e+24] -&gt; [-27.8211,-27.8211])
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1105, in qlCallableBondOAS
+    return callable_bond.OAS(
+           ~~~~~~~~~~~~~~~~~^
+        clean_price,
+        ^^^^^^^^^^^^
+    ...&lt;7 lines&gt;...
+        guess,
+        ^^^^^^
+    )
+    ^
+  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26304, in OAS
+    return _QuantLib.CallableBond_OAS(self, *args)
+           ~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
+RuntimeError: unable to bracket root in 100 function evaluations (last bracket attempt: f[-6.79107e+23,1.76568e+24] -&gt; [-27.8211,-27.8211])
+</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="B52" s="3" t="str">
+        <f>_xll.qlCallableBondCleanPriceOAS(B16,0.3,B34,"actual/360","simple","annual")</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: Boost assertion failed: px != 0
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1153, in qlCallableBondCleanPriceOAS
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1140, in qlCallableBondCleanPriceOAS
     return callable_bond.cleanPriceOAS(
            ~~~~~~~~~~~~~~~~~~~~~~~~~~~^
         oas,
@@ -2915,20 +3733,20 @@
 RuntimeError: Boost assertion failed: px != 0
 </v>
       </c>
-      <c r="C65" s="3">
-        <f>_xll.qlCallableBondCleanPriceOAS(C30,0.3,C48,"actual/360","simple","annual")</f>
-        <v>150.35427750919169</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
+      <c r="C52" s="3">
+        <f>_xll.qlCallableBondCleanPriceOAS(C16,0.3,C34,"actual/360","simple","annual")</f>
+        <v>71.641123311700554</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B66" s="3" t="str">
-        <f>_xll.qlCallableBondEffectiveDuration(B30,0.3,B48,"actual/360","simple","quarterly")</f>
+      <c r="B53" s="3" t="str">
+        <f>_xll.qlCallableBondEffectiveDuration(B16,0.3,B34,"actual/360","simple","quarterly")</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: Boost assertion failed: px != 0
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1185, in qlCallableBondEffectiveDuration
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1172, in qlCallableBondEffectiveDuration
     return callable_bond.effectiveDuration(
            ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^
         oas,
@@ -2944,878 +3762,20 @@
 RuntimeError: Boost assertion failed: px != 0
 </v>
       </c>
-      <c r="C66" s="3">
-        <f>_xll.qlCallableBondEffectiveDuration(C30,0.3,C48,"actual/360","simple","quarterly")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
+      <c r="C53" s="3">
+        <f>_xll.qlCallableBondEffectiveDuration(C16,0.3,C34,"actual/360","simple","quarterly")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="B67" s="3" t="str">
-        <f>_xll.qlCallableBondEffectiveConvexity(B30,0.3,B48,"actual/360","simple","quarterly")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: Boost assertion failed: px != 0
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1217, in qlCallableBondEffectiveConvexity
-    return callable_bond.effectiveConvexity(
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^
-        oas,
-        ^^^^
-    ...&lt;4 lines&gt;...
-        bump,
-        ^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26316, in effectiveConvexity
-    return _QuantLib.CallableBond_effectiveConvexity(self, oas, engineTS, dayCounter, compounding, frequency, bump)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-RuntimeError: Boost assertion failed: px != 0
-</v>
-      </c>
-      <c r="C67" s="3">
-        <f>_xll.qlCallableBondEffectiveConvexity(C30,0.3,C48,"actual/360","simple","quarterly")</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A15:A17"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4EF9C2-FD4D-4E7F-8154-C8E782972C6B}">
-  <dimension ref="A1:C53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="44.140625" customWidth="1"/>
-    <col min="2" max="2" width="89.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="73.28515625" style="3" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="2">
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="2">
-        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="3">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="3">
-        <v>100</v>
-      </c>
-      <c r="C5" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="3" t="str">
-        <f>_xll.qlCalendar("TARGET")</f>
-        <v>TARGET</v>
-      </c>
-      <c r="C6" s="3" t="str">
-        <f>_xll.qlCalendar("TARGET")</f>
-        <v>TARGET</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="2">
-        <v>49682</v>
-      </c>
-      <c r="C7" s="2">
-        <v>49682</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>146</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="2">
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2" t="str">
-        <f>_xll.qlBondPrice(100,"CLEAN")</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R12C3BondPrice,A</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2">
-        <v>47664</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="3" t="str">
-        <f>_xll.qlCallability(C12,C13,C14)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R15C3Callability,A</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B16" s="3" t="str">
-        <f>_xll.qlCallableZeroCouponBond(B4,B5,B6,B7,B8)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R16C2CallableZeroCouponBond,A</v>
-      </c>
-      <c r="C16" s="3" t="str">
-        <f>_xll.qlCallableZeroCouponBond(C4,C5,C6,C7,C8,C9,C10,C11,C15)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R16C3CallableZeroCouponBond,A</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="3" t="str">
-        <f>_xll.qlBondNextCouponRate(B16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 231, in qlBondNextCouponRate
-    return bond.nextCouponRate(date)
-           ~~~~~~~~~~~~~~~~~~~^^^^^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
-    return _QuantLib.Bond_nextCouponRate(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: no coupon paid at cashflow date January 8th, 2036
-</v>
-      </c>
-      <c r="C17" s="3" t="str">
-        <f>_xll.qlBondNextCouponRate(C16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 231, in qlBondNextCouponRate
-    return bond.nextCouponRate(date)
-           ~~~~~~~~~~~~~~~~~~~^^^^^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
-    return _QuantLib.Bond_nextCouponRate(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: no coupon paid at cashflow date January 8th, 2036
-</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="3">
-        <f>_xll.qlBondPreviousCouponRate(B16)</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="3">
-        <f>_xll.qlBondPreviousCouponRate(C16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="2">
-        <f>_xll.qlBondNextCashFlowDate(B16)</f>
-        <v>49682</v>
-      </c>
-      <c r="C19" s="2">
-        <f>_xll.qlBondNextCashFlowDate(C16)</f>
-        <v>49682</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="2">
-        <f>_xll.qlBondPreviousCashFlowDate(B16)</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="2">
-        <f>_xll.qlBondPreviousCashFlowDate(C16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="3">
-        <f>_xll.qlBondSettlementDays(B16)</f>
-        <v>2</v>
-      </c>
-      <c r="C21" s="3">
-        <f>_xll.qlBondSettlementDays(C16)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="2">
-        <f>_xll.qlBondSettlementDate(B16)</f>
-        <v>45667</v>
-      </c>
-      <c r="C22" s="2">
-        <f>_xll.qlBondSettlementDate(C16)</f>
-        <v>45667</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="3" t="b">
-        <f>_xll.qlBondIsTradable(B16)</f>
-        <v>1</v>
-      </c>
-      <c r="C23" s="3" t="b">
-        <f>_xll.qlBondIsTradable(C16)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="2">
-        <f>_xll.qlBondStartDate(B16)</f>
-        <v>49682</v>
-      </c>
-      <c r="C24" s="2">
-        <f>_xll.qlBondStartDate(C16)</f>
-        <v>49682</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="2">
-        <f>_xll.qlBondMaturityDate(B16)</f>
-        <v>49682</v>
-      </c>
-      <c r="C25" s="2">
-        <f>_xll.qlBondMaturityDate(C16)</f>
-        <v>49682</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="2">
-        <f>_xll.qlBondIssueDate(B16)</f>
-        <v>0</v>
-      </c>
-      <c r="C26" s="2">
-        <f>_xll.qlBondIssueDate(C16)</f>
-        <v>45665</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="3" t="str">
-        <f>_xll.qlBondCashFlows(B16)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R27C2CashFlow,A</v>
-      </c>
-      <c r="C27" s="3" t="str">
-        <f>_xll.qlBondCashFlows(C16)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R27C3CashFlow,A</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" s="3" t="str">
-        <f>_xll.qlBondRedemption(B16)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R28C2CashFlow,A</v>
-      </c>
-      <c r="C28" s="3" t="str">
-        <f>_xll.qlBondRedemption(C16)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R28C3CashFlow,A</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="3" t="str">
-        <f>_xll.qlBondRedemptions(B16)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R29C2CashFlow,A</v>
-      </c>
-      <c r="C29" s="3" t="str">
-        <f>_xll.qlBondRedemptions(C16)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R29C3CashFlow,A</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="3" t="str">
-        <f>_xll.qlBondCalendar(B16)</f>
-        <v>TARGET</v>
-      </c>
-      <c r="C30" s="3" t="str">
-        <f>_xll.qlBondCalendar(C16)</f>
-        <v>TARGET</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="3">
-        <f>_xll.qlBondNotional(B16)</f>
-        <v>100</v>
-      </c>
-      <c r="C31" s="3">
-        <f>_xll.qlBondNotional(C16)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="3">
-        <f>_xll.qlBondNotionals(B16)</f>
-        <v>100</v>
-      </c>
-      <c r="C32" s="3">
-        <f>_xll.qlBondNotionals(C16)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="B33" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="C33" s="3">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="B34" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R34C2YieldTermStructureHandle,A</v>
-      </c>
-      <c r="C34" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R34C3YieldTermStructureHandle,A</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B35" s="3" t="e">
-        <f>_xll.qlBlackCallableFixedRateBondEngine(B16,B33,B34)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C35" s="3" t="e">
-        <f>_xll.qlBlackCallableFixedRateBondEngine(C16,C33,C34)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B36" s="9" t="str">
-        <f>_xll.qlBondCleanPrice(B16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 422, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-</v>
-      </c>
-      <c r="C36" s="9" t="str">
-        <f>_xll.qlBondCleanPrice(C16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 422, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="9">
-        <v>0.28928264971926221</v>
-      </c>
-      <c r="C37" s="9">
-        <v>0.28928264971926221</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38" s="9">
-        <f>_xll.qlBondCleanPrice2(B16,B37,"actual360","continuous")</f>
-        <v>3.9703929859425657</v>
-      </c>
-      <c r="C38" s="9">
-        <f>_xll.qlBondCleanPrice2(C16,C37,"actual360","continuous")</f>
-        <v>3.9703929859425661E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" s="9" t="str">
-        <f>_xll.qlBondDirtyPrice(B16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 457, in qlBondDirtyPrice
-    return bond.dirtyPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
-    return _QuantLib.Bond_dirtyPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-</v>
-      </c>
-      <c r="C39" s="9" t="str">
-        <f>_xll.qlBondDirtyPrice(C16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 457, in qlBondDirtyPrice
-    return bond.dirtyPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
-    return _QuantLib.Bond_dirtyPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40" s="9">
-        <f>_xll.qlBondDirtyPrice2(B16,B37,"actual360","CONTINUOUS","annual")</f>
-        <v>3.9703929859425657</v>
-      </c>
-      <c r="C40" s="9">
-        <f>_xll.qlBondDirtyPrice2(C16,C37,"actual360","CONTINUOUS","annual")</f>
-        <v>3.9703929859425661E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="9" t="str">
-        <f>_xll.qlBondYield(B16,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 505, in qlBondYield
-    return bond.bondYield(dc, compounding, freq, accuracy, max_evaluations)
-           ~~~~~~~~~~~~~~^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-</v>
-      </c>
-      <c r="C41" s="9" t="str">
-        <f>_xll.qlBondYield(C16,"actual360","CONTINUOUS","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 505, in qlBondYield
-    return bond.bondYield(dc, compounding, freq, accuracy, max_evaluations)
-           ~~~~~~~~~~~~~~^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25922, in bondYield
-    return _QuantLib.Bond_bondYield(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B42" s="9" t="str">
-        <f>_xll.qlBondPrice(B36,"clean")</f>
-        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 422, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-': Expected float</v>
-      </c>
-      <c r="C42" s="9" t="str">
-        <f>_xll.qlBondPrice(C36,"clean")</f>
-        <v>Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 422, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="9" t="str">
-        <f>_xll.qlBondYield2(B16,B42,"actual360","CONTINUOUS","annual")</f>
-        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 422, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-': Expected float': Expected cache string</v>
-      </c>
-      <c r="C43" s="9" t="str">
-        <f>_xll.qlBondYield2(C16,C42,"actual360","CONTINUOUS","annual")</f>
-        <v>Error in arg 2 'price': Cannot convert 'Error in arg 1 'amount': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 422, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float': Expected cache string</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B44" s="2">
-        <v>45667</v>
-      </c>
-      <c r="C44" s="2">
-        <v>45667</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="9">
-        <f>_xll.qlBondAccruedAmount(B16,B44)</f>
-        <v>0</v>
-      </c>
-      <c r="C45" s="9">
-        <f>_xll.qlBondAccruedAmount(C16,C44)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="9" t="str">
-        <f>_xll.qlBondSettlementValue(B16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 562, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-</v>
-      </c>
-      <c r="C46" s="9" t="str">
-        <f>_xll.qlBondSettlementValue(C16)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 562, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="9" t="str">
-        <f>_xll.qlBondSettlementValue2(B16,B36)</f>
-        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 422, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-': Expected float</v>
-      </c>
-      <c r="C47" s="9" t="str">
-        <f>_xll.qlBondSettlementValue2(C16,C36)</f>
-        <v>Error in arg 2 'clean_price': Cannot convert 'RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 422, in qlBondCleanPrice
-    return bond.cleanPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25908, in cleanPrice
-    return _QuantLib.Bond_cleanPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-': Expected float</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="B48" s="3">
-        <f>_xll.qlCallableBondCallability(B16)</f>
-        <v>0</v>
-      </c>
-      <c r="C48" s="3" t="str">
-        <f>_xll.qlCallableBondCallability(C16)</f>
-        <v>欣[test_bonds.xlsx]CallableZeroCouponBond!R48C3Callability,A</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="32" t="s">
-        <v>142</v>
-      </c>
-      <c r="B50" s="3" t="str">
-        <f>_xll.qlCallableBondOAS(B16,43.82,B34,"Actual/360","Simple","Annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1118, in qlCallableBondOAS
-    return callable_bond.OAS(
-           ~~~~~~~~~~~~~~~~~^
-        clean_price,
-        ^^^^^^^^^^^^
-    ...&lt;7 lines&gt;...
-        guess,
-        ^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26304, in OAS
-    return _QuantLib.CallableBond_OAS(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-</v>
-      </c>
-      <c r="C50" s="3" t="str">
-        <f>_xll.qlCallableBondOAS(C16,43.82,C34,"Actual/360","Simple","Annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: unable to bracket root in 100 function evaluations (last bracket attempt: f[-6.79107e+23,1.76568e+24] -&gt; [43.7804,43.7804])
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1118, in qlCallableBondOAS
-    return callable_bond.OAS(
-           ~~~~~~~~~~~~~~~~~^
-        clean_price,
-        ^^^^^^^^^^^^
-    ...&lt;7 lines&gt;...
-        guess,
-        ^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26304, in OAS
-    return _QuantLib.CallableBond_OAS(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: unable to bracket root in 100 function evaluations (last bracket attempt: f[-6.79107e+23,1.76568e+24] -&gt; [43.7804,43.7804])
-</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="B51" s="3" t="str">
-        <f>_xll.qlCallableBondCleanPriceOAS(B16,0.3,B34,"actual/360","simple","annual")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1153, in qlCallableBondCleanPriceOAS
-    return callable_bond.cleanPriceOAS(
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~^
-        oas,
-        ^^^^
-    ...&lt;4 lines&gt;...
-        settlement_date,
-        ^^^^^^^^^^^^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26308, in cleanPriceOAS
-    return _QuantLib.CallableBond_cleanPriceOAS(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-</v>
-      </c>
-      <c r="C51" s="3">
-        <f>_xll.qlCallableBondCleanPriceOAS(C16,0.3,C34,"actual/360","simple","annual")</f>
-        <v>3.9640173399601616E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B52" s="3" t="str">
-        <f>_xll.qlCallableBondEffectiveDuration(B16,0.3,B34,"actual/360","simple","quarterly")</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1185, in qlCallableBondEffectiveDuration
-    return callable_bond.effectiveDuration(
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^
-        oas,
-        ^^^^
-    ...&lt;4 lines&gt;...
-        bump,
-        ^^^^^
-    )
-    ^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 26312, in effectiveDuration
-    return _QuantLib.CallableBond_effectiveDuration(self, oas, engineTS, dayCounter, compounding, frequency, bump)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
-RuntimeError: Must have exactly one call/put date to use Black Engine
-</v>
-      </c>
-      <c r="C52" s="3">
-        <f>_xll.qlCallableBondEffectiveDuration(C16,0.3,C34,"actual/360","simple","quarterly")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B53" s="3" t="str">
+      <c r="B54" s="3" t="str">
         <f>_xll.qlCallableBondEffectiveConvexity(B16,0.3,B34,"actual/360","simple","quarterly")</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: Must have exactly one call/put date to use Black Engine
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1217, in qlCallableBondEffectiveConvexity
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 1204, in qlCallableBondEffectiveConvexity
     return callable_bond.effectiveConvexity(
            ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^
         oas,
@@ -3831,13 +3791,14 @@
 RuntimeError: Must have exactly one call/put date to use Black Engine
 </v>
       </c>
-      <c r="C53" s="3">
+      <c r="C54" s="3">
         <f>_xll.qlCallableBondEffectiveConvexity(C16,0.3,C34,"actual/360","simple","quarterly")</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3919,7 +3880,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8683113-FD1C-4D88-8D42-F7763B404E4F}">
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -4017,7 +3978,7 @@
     <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="6">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C11" s="6">
         <v>0.03</v>
@@ -4026,8 +3987,7 @@
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="6">
-        <f t="shared" ref="B12:B18" si="0">B11+1</f>
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C12" s="6">
         <v>0.02</v>
@@ -4036,15 +3996,13 @@
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="6">
-        <f t="shared" si="0"/>
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C13" s="6"/>
     </row>
     <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="6">
-        <f t="shared" si="0"/>
         <v>103</v>
       </c>
       <c r="C14" s="6"/>
@@ -4052,32 +4010,28 @@
     <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="6">
-        <f t="shared" si="0"/>
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C15" s="6"/>
     </row>
     <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="6">
-        <f t="shared" si="0"/>
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C16" s="6"/>
     </row>
     <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="6">
-        <f t="shared" si="0"/>
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C17" s="6"/>
     </row>
     <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="6">
-        <f t="shared" si="0"/>
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C18" s="6"/>
     </row>
@@ -4243,9 +4197,9 @@
       <c r="A32" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="3" t="b">
-        <f>_xll.qlBondIsTradable(B25)</f>
-        <v>1</v>
+      <c r="B32" s="3" t="e">
+        <f ca="1">qlBondIsTradable(B25)</f>
+        <v>#NAME?</v>
       </c>
       <c r="C32" s="3" t="b">
         <f>_xll.qlBondIsTradable(C25)</f>
@@ -4312,6 +4266,10 @@
         <f>_xll.qlBondRedemption(B25)</f>
         <v>欣[test_bonds.xlsx]Bond!R37C2CashFlow,A</v>
       </c>
+      <c r="C37" s="3" t="str">
+        <f>_xll.qlBondRedemption(C25)</f>
+        <v>欣[test_bonds.xlsx]Bond!R37C3CashFlow,A</v>
+      </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
@@ -4321,6 +4279,10 @@
         <f>_xll.qlBondRedemptions(B25)</f>
         <v>欣[test_bonds.xlsx]Bond!R38C2CashFlow,A</v>
       </c>
+      <c r="C38" s="3" t="str">
+        <f>_xll.qlBondRedemptions(C25)</f>
+        <v>欣[test_bonds.xlsx]Bond!R38C3CashFlow,A</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
@@ -4366,195 +4328,190 @@
         <v>55</v>
       </c>
       <c r="B42" s="3" t="str">
-        <f>_xll.qlFlatForward(B1,0.3,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(B1,0.03,"actual360","compounded","Annual")</f>
         <v>欣[test_bonds.xlsx]Bond!R42C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C42" s="3" t="str">
-        <f>_xll.qlFlatForward(B1,0.3,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(B1,0.03,"actual360","compounded","Annual")</f>
         <v>欣[test_bonds.xlsx]Bond!R42C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="B43" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(B25,B42)</f>
+        <f>_xll.qlDiscountingBondEngine(B42)</f>
         <v>欣[test_bonds.xlsx]Bond!R43C2DiscountingBondEngine,A</v>
       </c>
       <c r="C43" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(C25,C42)</f>
+        <f>_xll.qlDiscountingBondEngine(C42)</f>
         <v>欣[test_bonds.xlsx]Bond!R43C3DiscountingBondEngine,A</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B44" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(B25,B43)</f>
+        <v>1</v>
+      </c>
+      <c r="C44" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(C25,C43)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B44" s="9">
+      <c r="B45" s="9">
         <f>_xll.qlBondCleanPrice(B25)</f>
-        <v>2.2859856860093175</v>
-      </c>
-      <c r="C44" s="9">
+        <v>2.9820944542826178</v>
+      </c>
+      <c r="C45" s="9">
         <f>_xll.qlBondCleanPrice(C25)</f>
-        <v>2.2859856860093175</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+        <v>2.9820944542826178</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B45" s="9">
-        <v>0.26236426550490211</v>
-      </c>
-      <c r="C45" s="9">
-        <v>0.26236426550490211</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="B46" s="9">
-        <f>_xll.qlBondCleanPrice2(B25,B45,"actual360","continuous")</f>
-        <v>2.285985683600614</v>
+        <v>2.9558800538580478E-2</v>
       </c>
       <c r="C46" s="9">
-        <f>_xll.qlBondCleanPrice2(C25,C45,"actual360","continuous")</f>
-        <v>2.285985683600614</v>
+        <v>2.9558800538580478E-2</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B47" s="9">
-        <f>_xll.qlBondDirtyPrice(B25)</f>
-        <v>2.3026523526759823</v>
+        <f>_xll.qlBondCleanPrice2(B25,B46,"actual360","continuous")</f>
+        <v>2.9820944594328145</v>
       </c>
       <c r="C47" s="9">
-        <f>_xll.qlBondDirtyPrice(C25)</f>
-        <v>2.3026523526759823</v>
+        <f>_xll.qlBondCleanPrice2(C25,C46,"actual360","continuous")</f>
+        <v>2.9820944594328145</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B48" s="9">
-        <f>_xll.qlBondDirtyPrice2(B25,B45,"actual360","CONTINUOUS","annual")</f>
-        <v>2.3026523502672789</v>
+        <f>_xll.qlBondDirtyPrice(B25)</f>
+        <v>2.9992611209492823</v>
       </c>
       <c r="C48" s="9">
-        <f>_xll.qlBondDirtyPrice2(C25,C45,"actual360","CONTINUOUS","annual")</f>
-        <v>2.3026523502672789</v>
+        <f>_xll.qlBondDirtyPrice(C25)</f>
+        <v>2.9992611209492823</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49" s="9">
+        <f>_xll.qlBondDirtyPrice2(B25,B46,"actual360","CONTINUOUS","annual")</f>
+        <v>2.999261126099479</v>
+      </c>
+      <c r="C49" s="9">
+        <f>_xll.qlBondDirtyPrice2(C25,C46,"actual360","CONTINUOUS","annual")</f>
+        <v>2.999261126099479</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="9">
+      <c r="B50" s="9">
         <f>_xll.qlBondYield(B25,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426880388447</v>
-      </c>
-      <c r="C49" s="9">
+        <v>2.9558799446356546E-2</v>
+      </c>
+      <c r="C50" s="9">
         <f>_xll.qlBondYield(C25,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426880388447</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="10" t="s">
+        <v>2.9558799446356546E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B50" s="9" t="str">
-        <f>_xll.qlBondPrice(B44,"clean")</f>
-        <v>欣[test_bonds.xlsx]Bond!R50C2BondPrice,A</v>
-      </c>
-      <c r="C50" s="9" t="str">
-        <f>_xll.qlBondPrice(C44,"clean")</f>
-        <v>欣[test_bonds.xlsx]Bond!R50C3BondPrice,A</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
+      <c r="B51" s="9" t="str">
+        <f>_xll.qlBondPrice(B45,"clean")</f>
+        <v>欣[test_bonds.xlsx]Bond!R51C2BondPrice,A</v>
+      </c>
+      <c r="C51" s="9" t="str">
+        <f>_xll.qlBondPrice(C45,"clean")</f>
+        <v>欣[test_bonds.xlsx]Bond!R51C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B51" s="9">
-        <f>_xll.qlBondYield2(B25,B50,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26956857911471388</v>
-      </c>
-      <c r="C51" s="9">
-        <f>_xll.qlBondYield2(C25,C50,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26956857911471388</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="10" t="s">
+      <c r="B52" s="9">
+        <f>_xll.qlBondYield2(B25,B51,"actual360","CONTINUOUS","annual")</f>
+        <v>3.5251441098982664E-2</v>
+      </c>
+      <c r="C52" s="9">
+        <f>_xll.qlBondYield2(C25,C51,"actual360","CONTINUOUS","annual")</f>
+        <v>3.5251441098982664E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B53" s="2">
         <v>45667</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C53" s="2">
         <v>45667</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="9">
-        <f>_xll.qlBondAccruedAmount(B25,B52)</f>
-        <v>1.6666666666664831E-2</v>
-      </c>
-      <c r="C53" s="9">
-        <f>_xll.qlBondAccruedAmount(C25,C52)</f>
-        <v>1.6666666666664831E-2</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="9" t="str">
-        <f>_xll.qlBondSettlementValue(B25)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 562, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
-      </c>
-      <c r="C54" s="9" t="str">
-        <f>_xll.qlBondSettlementValue(C25)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 562, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>39</v>
+      </c>
+      <c r="B54" s="9">
+        <f>_xll.qlBondAccruedAmount(B25,B53)</f>
+        <v>1.7166666666664776E-2</v>
+      </c>
+      <c r="C54" s="9">
+        <f>_xll.qlBondAccruedAmount(C25,C53)</f>
+        <v>1.7166666666664776E-2</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="9">
+        <f>_xll.qlBondSettlementValue(B25)</f>
+        <v>2.9992611209492819</v>
+      </c>
+      <c r="C55" s="9">
+        <f>_xll.qlBondSettlementValue(C25)</f>
+        <v>2.9992611209492819</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B55" s="9">
-        <f>_xll.qlBondSettlementValue2(B25,B44)</f>
-        <v>2.3026523526759823</v>
-      </c>
-      <c r="C55" s="9">
-        <f>_xll.qlBondSettlementValue2(C25,C44)</f>
-        <v>2.3026523526759823</v>
+      <c r="B56" s="9">
+        <f>_xll.qlBondSettlementValue2(B25,B45)</f>
+        <v>2.9992611209492823</v>
+      </c>
+      <c r="C56" s="9">
+        <f>_xll.qlBondSettlementValue2(C25,C45)</f>
+        <v>2.9992611209492823</v>
       </c>
     </row>
   </sheetData>
@@ -4565,7 +4522,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA0BDDB4-6035-4089-86B1-6246F3228CBC}">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
@@ -4682,7 +4639,7 @@
         <f>_xll.qlBondNextCouponRate(B11)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 231, in qlBondNextCouponRate
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 216, in qlBondNextCouponRate
     return bond.nextCouponRate(date)
            ~~~~~~~~~~~~~~~~~~~^^^^^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
@@ -4695,7 +4652,7 @@
         <f>_xll.qlBondNextCouponRate(C11)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: no coupon paid at cashflow date January 8th, 2036
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 231, in qlBondNextCouponRate
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 216, in qlBondNextCouponRate
     return bond.nextCouponRate(date)
            ~~~~~~~~~~~~~~~~~~~^^^^^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25841, in nextCouponRate
@@ -4905,177 +4862,190 @@
         <v>55</v>
       </c>
       <c r="B28" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Annual")</f>
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R28C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C28" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Annual")</f>
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R28C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="B29" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(B11,B28)</f>
+        <f>_xll.qlDiscountingBondEngine(B28)</f>
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R29C2DiscountingBondEngine,A</v>
       </c>
       <c r="C29" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(C11,C28)</f>
+        <f>_xll.qlDiscountingBondEngine(C28)</f>
         <v>欣[test_bonds.xlsx]ZeroCouponBond!R29C3DiscountingBondEngine,A</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B30" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(B11,B29)</f>
+        <v>1</v>
+      </c>
+      <c r="C30" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(C11,C29)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B31" s="9">
         <f>_xll.qlBondCleanPrice(B11)</f>
-        <v>5.3606211124198397</v>
-      </c>
-      <c r="C30" s="9">
+        <v>71.916622935265281</v>
+      </c>
+      <c r="C31" s="9">
         <f>_xll.qlBondCleanPrice(C11)</f>
-        <v>6.4327453349038084</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
+        <v>86.29994752231832</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="9">
-        <v>0.26236426550490211</v>
-      </c>
-      <c r="C31" s="9">
-        <v>1.2623642655049001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="B32" s="9">
-        <f>_xll.qlBondCleanPrice2(B11,B31,"actual360","continuous")</f>
-        <v>5.3606210503973868</v>
+        <v>2.9558808088302614E-2</v>
       </c>
       <c r="C32" s="9">
-        <f>_xll.qlBondCleanPrice2(C11,C31,"actual360","continuous")</f>
-        <v>9.2216048105760734E-5</v>
+        <v>2.9558808088302614E-2</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B33" s="9">
-        <f>_xll.qlBondDirtyPrice(B11)</f>
-        <v>5.3606211124198397</v>
+        <f>_xll.qlBondCleanPrice2(B11,B32,"actual360","continuous")</f>
+        <v>71.916618245755444</v>
       </c>
       <c r="C33" s="9">
-        <f>_xll.qlBondDirtyPrice(C11)</f>
-        <v>6.4327453349038084</v>
+        <f>_xll.qlBondCleanPrice2(C11,C32,"actual360","continuous")</f>
+        <v>86.299941894906539</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B34" s="9">
-        <f>_xll.qlBondDirtyPrice2(B11,B31,"actual360","CONTINUOUS","annual")</f>
-        <v>5.3606210503973868</v>
+        <f>_xll.qlBondDirtyPrice(B11)</f>
+        <v>71.916622935265281</v>
       </c>
       <c r="C34" s="9">
-        <f>_xll.qlBondDirtyPrice2(C11,C31,"actual360","CONTINUOUS","annual")</f>
-        <v>9.2216048105760734E-5</v>
+        <f>_xll.qlBondDirtyPrice(C11)</f>
+        <v>86.29994752231832</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="9">
+        <f>_xll.qlBondDirtyPrice2(B11,B32,"actual360","CONTINUOUS","annual")</f>
+        <v>71.916618245755444</v>
+      </c>
+      <c r="C35" s="9">
+        <f>_xll.qlBondDirtyPrice2(C11,C32,"actual360","CONTINUOUS","annual")</f>
+        <v>86.299941894906539</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B36" s="9">
         <f>_xll.qlBondYield(B11,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426339626184</v>
-      </c>
-      <c r="C35" s="9">
+        <v>2.9558808088302614E-2</v>
+      </c>
+      <c r="C36" s="9">
         <f>_xll.qlBondYield(C11,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426471315105</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
+        <v>2.9558808088302614E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B36" s="9" t="str">
-        <f>_xll.qlBondPrice(B30,"clean")</f>
-        <v>欣[test_bonds.xlsx]ZeroCouponBond!R36C2BondPrice,A</v>
-      </c>
-      <c r="C36" s="9" t="str">
-        <f>_xll.qlBondPrice(C30,"clean")</f>
-        <v>欣[test_bonds.xlsx]ZeroCouponBond!R36C3BondPrice,A</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+      <c r="B37" s="9" t="str">
+        <f>_xll.qlBondPrice(B31,"clean")</f>
+        <v>欣[test_bonds.xlsx]ZeroCouponBond!R37C2BondPrice,A</v>
+      </c>
+      <c r="C37" s="9" t="str">
+        <f>_xll.qlBondPrice(C31,"clean")</f>
+        <v>欣[test_bonds.xlsx]ZeroCouponBond!R37C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="9">
-        <f>_xll.qlBondYield2(B11,B36,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426339626184</v>
-      </c>
-      <c r="C37" s="9">
-        <f>_xll.qlBondYield2(C11,C36,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426471315105</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+      <c r="B38" s="9">
+        <f>_xll.qlBondYield2(B11,B37,"actual360","CONTINUOUS","annual")</f>
+        <v>2.9558808088302614E-2</v>
+      </c>
+      <c r="C38" s="9">
+        <f>_xll.qlBondYield2(C11,C37,"actual360","CONTINUOUS","annual")</f>
+        <v>2.9558808088302614E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B39" s="2">
         <v>45667</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C39" s="2">
         <v>45667</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="9">
-        <f>_xll.qlBondAccruedAmount(B11,B38)</f>
-        <v>0</v>
-      </c>
-      <c r="C39" s="9">
-        <f>_xll.qlBondAccruedAmount(C11,C38)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="9">
-        <f>_xll.qlBondSettlementValue(B11)</f>
-        <v>5.3606211124198397</v>
+        <f>_xll.qlBondAccruedAmount(B11,B39)</f>
+        <v>0</v>
       </c>
       <c r="C40" s="9">
-        <f>_xll.qlBondSettlementValue(C11)</f>
-        <v>6.4327453349038075</v>
+        <f>_xll.qlBondAccruedAmount(C11,C39)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="9">
+        <f>_xll.qlBondSettlementValue(B11)</f>
+        <v>71.916622935265281</v>
+      </c>
+      <c r="C41" s="9">
+        <f>_xll.qlBondSettlementValue(C11)</f>
+        <v>86.299947522318334</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="9">
-        <f>_xll.qlBondSettlementValue2(B11,B30)</f>
-        <v>5.3606211124198397</v>
-      </c>
-      <c r="C41" s="9">
-        <f>_xll.qlBondSettlementValue2(C11,C30)</f>
-        <v>6.4327453349038084</v>
+      <c r="B42" s="9">
+        <f>_xll.qlBondSettlementValue2(B11,B31)</f>
+        <v>71.916622935265281</v>
+      </c>
+      <c r="C42" s="9">
+        <f>_xll.qlBondSettlementValue2(C11,C31)</f>
+        <v>86.29994752231832</v>
       </c>
     </row>
   </sheetData>
@@ -5085,7 +5055,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00EB77E5-949B-439C-BFA2-575F2A710E3C}">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
@@ -5236,32 +5206,32 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="36" t="s">
         <v>66</v>
       </c>
       <c r="B15" s="3">
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="C15" s="3">
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
+      <c r="A16" s="36"/>
       <c r="B16" s="3">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="C16" s="3">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="35"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="3">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
       <c r="C17" s="3">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -5288,7 +5258,7 @@
         <v>63</v>
       </c>
       <c r="C20" s="3">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5360,11 +5330,11 @@
       </c>
       <c r="B28" s="3">
         <f>_xll.qlBondNextCouponRate(B27)</f>
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="C28" s="3">
         <f>_xll.qlBondNextCouponRate(C27)</f>
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -5567,186 +5537,190 @@
         <v>55</v>
       </c>
       <c r="B44" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Annual")</f>
         <v>欣[test_bonds.xlsx]FixedRateBond!R44C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C44" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Annual")</f>
         <v>欣[test_bonds.xlsx]FixedRateBond!R44C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="B45" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(B27,B44)</f>
+        <f>_xll.qlDiscountingBondEngine(B44)</f>
         <v>欣[test_bonds.xlsx]FixedRateBond!R45C2DiscountingBondEngine,A</v>
       </c>
       <c r="C45" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(C27,C44)</f>
+        <f>_xll.qlDiscountingBondEngine(C44)</f>
         <v>欣[test_bonds.xlsx]FixedRateBond!R45C3DiscountingBondEngine,A</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B46" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(B27,B45)</f>
+        <v>1</v>
+      </c>
+      <c r="C46" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(C27,C45)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B47" s="9">
         <f>_xll.qlBondCleanPrice(B27)</f>
-        <v>170.40963157834548</v>
-      </c>
-      <c r="C46" s="9">
+        <v>124.40332304252406</v>
+      </c>
+      <c r="C47" s="9">
         <f>_xll.qlBondCleanPrice(C27)</f>
-        <v>171.42647581938954</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="10" t="s">
+        <v>124.40127138186649</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B47" s="9">
-        <v>0.26236426550490211</v>
-      </c>
-      <c r="C47" s="9">
-        <v>0.26236426550490211</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="B48" s="9">
-        <f>_xll.qlBondCleanPrice2(B27,B47,"actual360","continuous")</f>
-        <v>170.40963082810279</v>
+        <v>2.9558808088302614E-2</v>
       </c>
       <c r="C48" s="9">
-        <f>_xll.qlBondCleanPrice2(C27,C47,"actual360","continuous")</f>
-        <v>171.42647505679128</v>
+        <v>2.9558808088302614E-2</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B49" s="9">
-        <f>_xll.qlBondDirtyPrice(B27)</f>
-        <v>170.40963157834548</v>
+        <f>_xll.qlBondCleanPrice2(B27,B48,"actual360","continuous")</f>
+        <v>124.40331650168764</v>
       </c>
       <c r="C49" s="9">
-        <f>_xll.qlBondDirtyPrice(C27)</f>
-        <v>171.42647581938954</v>
+        <f>_xll.qlBondCleanPrice2(C27,C48,"actual360","continuous")</f>
+        <v>124.40126484069721</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B50" s="9">
-        <f>_xll.qlBondDirtyPrice2(B27,B47,"actual360","CONTINUOUS","annual")</f>
-        <v>170.40963082810279</v>
+        <f>_xll.qlBondDirtyPrice(B27)</f>
+        <v>124.40332304252406</v>
       </c>
       <c r="C50" s="9">
-        <f>_xll.qlBondDirtyPrice2(C27,C47,"actual360","CONTINUOUS","annual")</f>
-        <v>171.42647505679128</v>
+        <f>_xll.qlBondDirtyPrice(C27)</f>
+        <v>124.40127138186649</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" s="9">
+        <f>_xll.qlBondDirtyPrice2(B27,B48,"actual360","CONTINUOUS","annual")</f>
+        <v>124.40331650168764</v>
+      </c>
+      <c r="C51" s="9">
+        <f>_xll.qlBondDirtyPrice2(C27,C48,"actual360","CONTINUOUS","annual")</f>
+        <v>124.40126484069721</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B52" s="9">
         <f>_xll.qlBondYield(B27,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
-      </c>
-      <c r="C51" s="9">
+        <v>2.9558808088302614E-2</v>
+      </c>
+      <c r="C52" s="9">
         <f>_xll.qlBondYield(C27,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="10" t="s">
+        <v>2.9558808088302614E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B52" s="9" t="str">
-        <f>_xll.qlBondPrice(B46,"clean")</f>
-        <v>欣[test_bonds.xlsx]FixedRateBond!R52C2BondPrice,A</v>
-      </c>
-      <c r="C52" s="9" t="str">
-        <f>_xll.qlBondPrice(C46,"clean")</f>
-        <v>欣[test_bonds.xlsx]FixedRateBond!R52C3BondPrice,A</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
+      <c r="B53" s="9" t="str">
+        <f>_xll.qlBondPrice(B47,"clean")</f>
+        <v>欣[test_bonds.xlsx]FixedRateBond!R53C2BondPrice,A</v>
+      </c>
+      <c r="C53" s="9" t="str">
+        <f>_xll.qlBondPrice(C47,"clean")</f>
+        <v>欣[test_bonds.xlsx]FixedRateBond!R53C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B53" s="9">
-        <f>_xll.qlBondYield2(B27,B52,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
-      </c>
-      <c r="C53" s="9">
-        <f>_xll.qlBondYield2(C27,C52,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
+      <c r="B54" s="9">
+        <f>_xll.qlBondYield2(B27,B53,"actual360","CONTINUOUS","annual")</f>
+        <v>2.9558808088302614E-2</v>
+      </c>
+      <c r="C54" s="9">
+        <f>_xll.qlBondYield2(C27,C53,"actual360","CONTINUOUS","annual")</f>
+        <v>2.9558808088302614E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B55" s="2">
         <v>45667</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C55" s="2">
         <v>45667</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="9">
-        <f>_xll.qlBondAccruedAmount(B27,B54)</f>
-        <v>0.22222222222221255</v>
-      </c>
-      <c r="C55" s="9">
-        <f>_xll.qlBondAccruedAmount(C27,C54)</f>
-        <v>0.22222222222221255</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="9" t="str">
-        <f>_xll.qlBondSettlementValue(B27)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 562, in qlBondSettlementValue
-    return bond.settlementValue()
-           ~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25933, in settlementValue
-    return _QuantLib.Bond_settlementValue(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>39</v>
+      </c>
+      <c r="B56" s="9">
+        <f>_xll.qlBondAccruedAmount(B27,B55)</f>
+        <v>2.2222222222212373E-2</v>
       </c>
       <c r="C56" s="9">
-        <f>_xll.qlBondSettlementValue(C27)</f>
-        <v>171.42647581938951</v>
+        <f>_xll.qlBondAccruedAmount(C27,C55)</f>
+        <v>2.2222222222212373E-2</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="9">
+        <f>_xll.qlBondSettlementValue(B27)</f>
+        <v>124.40332304252406</v>
+      </c>
+      <c r="C57" s="9">
+        <f>_xll.qlBondSettlementValue(C27)</f>
+        <v>124.40127138186649</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B57" s="9">
-        <f>_xll.qlBondSettlementValue2(B27,B46)</f>
-        <v>170.40963157834548</v>
-      </c>
-      <c r="C57" s="9">
-        <f>_xll.qlBondSettlementValue2(C27,C46)</f>
-        <v>171.42647581938954</v>
+      <c r="B58" s="9">
+        <f>_xll.qlBondSettlementValue2(B27,B47)</f>
+        <v>124.40332304252406</v>
+      </c>
+      <c r="C58" s="9">
+        <f>_xll.qlBondSettlementValue2(C27,C47)</f>
+        <v>124.40127138186649</v>
       </c>
     </row>
   </sheetData>
@@ -5759,7 +5733,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303A5445-988F-4FD7-9234-8C10A40DEB2F}">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.42578125" customWidth="1"/>
@@ -5796,7 +5770,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="36" t="s">
         <v>82</v>
       </c>
       <c r="B5" s="3">
@@ -5807,7 +5781,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="35"/>
+      <c r="A6" s="36"/>
       <c r="B6" s="3">
         <v>125</v>
       </c>
@@ -5816,7 +5790,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="35"/>
+      <c r="A7" s="36"/>
       <c r="B7" s="3">
         <v>100</v>
       </c>
@@ -5928,32 +5902,32 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="35" t="s">
+      <c r="A17" s="36" t="s">
         <v>66</v>
       </c>
       <c r="B17" s="3">
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="C17" s="3">
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="35"/>
+      <c r="A18" s="36"/>
       <c r="B18" s="3">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="C18" s="3">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="35"/>
+      <c r="A19" s="36"/>
       <c r="B19" s="3">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
       <c r="C19" s="3">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -6017,7 +5991,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="35" t="s">
+      <c r="A27" s="36" t="s">
         <v>87</v>
       </c>
       <c r="C27" s="3">
@@ -6025,13 +5999,13 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="35"/>
+      <c r="A28" s="36"/>
       <c r="C28" s="3">
         <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="35"/>
+      <c r="A29" s="36"/>
       <c r="C29" s="3">
         <v>110</v>
       </c>
@@ -6055,11 +6029,11 @@
       </c>
       <c r="B31" s="3">
         <f>_xll.qlBondNextCouponRate(B30)</f>
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="C31" s="3">
         <f>_xll.qlBondNextCouponRate(C30)</f>
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -6174,7 +6148,7 @@
         <f>_xll.qlBondIssueDate(B30)</f>
         <v>0</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="2">
         <f>_xll.qlBondIssueDate(C30)</f>
         <v>45663</v>
       </c>
@@ -6200,7 +6174,7 @@
         <f>_xll.qlBondRedemption(B30)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 365, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 350, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -6213,7 +6187,7 @@
         <f>_xll.qlBondRedemption(C30)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 365, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 350, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -6280,186 +6254,190 @@
         <v>55</v>
       </c>
       <c r="B47" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Annual")</f>
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R47C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C47" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Annual")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Annual")</f>
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R47C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="B48" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(B30,B47)</f>
+        <f>_xll.qlDiscountingBondEngine(B47)</f>
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R48C2DiscountingBondEngine,A</v>
       </c>
       <c r="C48" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(C30,C47)</f>
+        <f>_xll.qlDiscountingBondEngine(C47)</f>
         <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R48C3DiscountingBondEngine,A</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B49" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(B30,B48)</f>
+        <v>1</v>
+      </c>
+      <c r="C49" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(C30,C48)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B49" s="9">
+      <c r="B50" s="9">
         <f>_xll.qlBondCleanPrice(B30)</f>
-        <v>151.24747199666061</v>
-      </c>
-      <c r="C49" s="9">
+        <v>116.88159964957646</v>
+      </c>
+      <c r="C50" s="9">
         <f>_xll.qlBondCleanPrice(C30)</f>
-        <v>153.90042276113556</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="10" t="s">
+        <v>124.8650952165318</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B50" s="9">
-        <v>0.26236426550490211</v>
-      </c>
-      <c r="C50" s="9">
-        <v>0.26236426550490211</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="B51" s="9">
-        <f>_xll.qlBondCleanPrice2(B30,B50,"actual360","continuous")</f>
-        <v>151.24747144150959</v>
+        <v>2.9586706781387334E-2</v>
       </c>
       <c r="C51" s="9">
-        <f>_xll.qlBondCleanPrice2(C30,C50,"actual360","continuous")</f>
-        <v>153.90042219843011</v>
+        <v>2.9586706781387334E-2</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B52" s="9" t="str">
-        <f>_xll.qlBondDirtyPrice(B30)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: null pricing engine
-Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 457, in qlBondDirtyPrice
-    return bond.dirtyPrice()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25915, in dirtyPrice
-    return _QuantLib.Bond_dirtyPrice(self, *args)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-RuntimeError: null pricing engine
-</v>
+        <v>34</v>
+      </c>
+      <c r="B52" s="9">
+        <f>_xll.qlBondCleanPrice2(B30,B51,"actual360","continuous")</f>
+        <v>116.85937778132163</v>
       </c>
       <c r="C52" s="9">
-        <f>_xll.qlBondDirtyPrice(C30)</f>
-        <v>154.12264498335776</v>
+        <f>_xll.qlBondCleanPrice2(C30,C51,"actual360","continuous")</f>
+        <v>124.84124844017744</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B53" s="9">
-        <f>_xll.qlBondDirtyPrice2(B30,B50,"actual360","CONTINUOUS","annual")</f>
-        <v>151.46969366373179</v>
+        <f>_xll.qlBondDirtyPrice(B30)</f>
+        <v>116.90382187179867</v>
       </c>
       <c r="C53" s="9">
-        <f>_xll.qlBondDirtyPrice2(C30,C50,"actual360","CONTINUOUS","annual")</f>
-        <v>154.12264442065231</v>
+        <f>_xll.qlBondDirtyPrice(C30)</f>
+        <v>124.88731743875401</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B54" s="9">
+        <f>_xll.qlBondDirtyPrice2(B30,B51,"actual360","CONTINUOUS","annual")</f>
+        <v>116.88160000354384</v>
+      </c>
+      <c r="C54" s="9">
+        <f>_xll.qlBondDirtyPrice2(C30,C51,"actual360","CONTINUOUS","annual")</f>
+        <v>124.86347066239965</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B54" s="9">
+      <c r="B55" s="9">
         <f>_xll.qlBondYield(B30,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
-      </c>
-      <c r="C54" s="9">
+        <v>2.9558808088302614E-2</v>
+      </c>
+      <c r="C55" s="9">
         <f>_xll.qlBondYield(C30,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26236426417183883</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="10" t="s">
+        <v>2.9558808088302614E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B55" s="9" t="str">
-        <f>_xll.qlBondPrice(B49,"clean")</f>
-        <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R55C2BondPrice,A</v>
-      </c>
-      <c r="C55" s="9" t="str">
-        <f>_xll.qlBondPrice(C49,"clean")</f>
-        <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R55C3BondPrice,A</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
+      <c r="B56" s="9" t="str">
+        <f>_xll.qlBondPrice(B50,"clean")</f>
+        <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R56C2BondPrice,A</v>
+      </c>
+      <c r="C56" s="9" t="str">
+        <f>_xll.qlBondPrice(C50,"clean")</f>
+        <v>欣[test_bonds.xlsx]AmortizingFixedRateBond!R56C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B56" s="9">
-        <f>_xll.qlBondYield2(B30,B55,"actual360","CONTINUOUS","annual")</f>
-        <v>0.2627800233576299</v>
-      </c>
-      <c r="C56" s="9">
-        <f>_xll.qlBondYield2(C30,C55,"actual360","CONTINUOUS","annual")</f>
-        <v>0.26277443958973895</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="10" t="s">
+      <c r="B57" s="9">
+        <f>_xll.qlBondYield2(B30,B56,"actual360","CONTINUOUS","annual")</f>
+        <v>2.9586706781387334E-2</v>
+      </c>
+      <c r="C57" s="9">
+        <f>_xll.qlBondYield2(C30,C56,"actual360","CONTINUOUS","annual")</f>
+        <v>2.9584804964065556E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B58" s="2">
         <v>45667</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C58" s="2">
         <v>45667</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="9">
-        <f>_xll.qlBondAccruedAmount(B30,B57)</f>
-        <v>0.22222222222221252</v>
-      </c>
-      <c r="C58" s="9">
-        <f>_xll.qlBondAccruedAmount(C30,C57)</f>
-        <v>0.22222222222221252</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B59" s="9">
-        <f>_xll.qlBondSettlementValue(B30)</f>
-        <v>227.20454132832424</v>
+        <f>_xll.qlBondAccruedAmount(B30,B58)</f>
+        <v>2.2222222222212373E-2</v>
       </c>
       <c r="C59" s="9">
-        <f>_xll.qlBondSettlementValue(C30)</f>
-        <v>231.18396747503664</v>
+        <f>_xll.qlBondAccruedAmount(C30,C58)</f>
+        <v>2.2222222222212373E-2</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="9">
+        <f>_xll.qlBondSettlementValue(B30)</f>
+        <v>175.35573280769802</v>
+      </c>
+      <c r="C60" s="9">
+        <f>_xll.qlBondSettlementValue(C30)</f>
+        <v>187.33097615813102</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B60" s="9">
-        <f>_xll.qlBondSettlementValue2(B30,B49)</f>
-        <v>227.20454132832421</v>
-      </c>
-      <c r="C60" s="9">
-        <f>_xll.qlBondSettlementValue2(C30,C49)</f>
-        <v>231.18396747503661</v>
+      <c r="B61" s="9">
+        <f>_xll.qlBondSettlementValue2(B30,B50)</f>
+        <v>175.35573280769799</v>
+      </c>
+      <c r="C61" s="9">
+        <f>_xll.qlBondSettlementValue2(C30,C50)</f>
+        <v>187.33097615813102</v>
       </c>
     </row>
   </sheetData>
@@ -6474,7 +6452,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F76F30CA-2F79-453E-B116-2A48310E361D}">
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.42578125" customWidth="1"/>
@@ -6511,7 +6489,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="36" t="s">
         <v>88</v>
       </c>
       <c r="B5" s="3">
@@ -6522,7 +6500,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="35"/>
+      <c r="A6" s="36"/>
       <c r="B6" s="3">
         <v>125</v>
       </c>
@@ -6531,7 +6509,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="35"/>
+      <c r="A7" s="36"/>
       <c r="B7" s="3">
         <v>100</v>
       </c>
@@ -6647,11 +6625,11 @@
         <v>55</v>
       </c>
       <c r="B17" s="14" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R17C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C17" s="14" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R17C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -6806,11 +6784,11 @@
       </c>
       <c r="B35" s="3">
         <f>_xll.qlBondNextCouponRate(B34)</f>
-        <v>0.33645996454499488</v>
+        <v>3.0348052211435581E-2</v>
       </c>
       <c r="C35" s="3">
         <f>_xll.qlBondNextCouponRate(C34)</f>
-        <v>0.33645996454499488</v>
+        <v>3.0348052211435581E-2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -6951,7 +6929,7 @@
         <f>_xll.qlBondRedemption(B34)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 365, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 350, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -6964,7 +6942,7 @@
         <f>_xll.qlBondRedemption(C34)</f>
         <v xml:space="preserve">RuntimeError: RuntimeError: multiple redemption cash flows given
 Traceback (most recent call last):
-  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 365, in qlBondRedemption
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\bonds.py", line 350, in qlBondRedemption
     return bond.redemption()
            ~~~~~~~~~~~~~~~^^
   File "C:\Users\kerst\AppData\Roaming\Python\Python314\site-packages\QuantLib\QuantLib.py", line 25889, in redemption
@@ -7031,177 +7009,190 @@
         <v>55</v>
       </c>
       <c r="B51" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R51C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C51" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R51C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="B52" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(B34,B51)</f>
+        <f>_xll.qlDiscountingBondEngine(B51)</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R52C2DiscountingBondEngine,A</v>
       </c>
       <c r="C52" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(C34,C51)</f>
+        <f>_xll.qlDiscountingBondEngine(C51)</f>
         <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R52C3DiscountingBondEngine,A</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B53" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(B34,B52)</f>
+        <v>1</v>
+      </c>
+      <c r="C53" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(C34,C52)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B53" s="9">
+      <c r="B54" s="9">
         <f>_xll.qlBondCleanPrice(B34)</f>
-        <v>98.911948723893104</v>
-      </c>
-      <c r="C53" s="9">
+        <v>99.710822698691373</v>
+      </c>
+      <c r="C54" s="9">
         <f>_xll.qlBondCleanPrice(C34)</f>
-        <v>98.911948723893104</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
+        <v>99.710822698691373</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="9">
-        <v>0.28928264971926221</v>
-      </c>
-      <c r="C54" s="9">
-        <v>0.28928264971926221</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="B55" s="9">
-        <f>_xll.qlBondCleanPrice2(B34,B54,"actual360","continuous")</f>
-        <v>98.911947709487364</v>
+        <v>2.9888064241409308E-2</v>
       </c>
       <c r="C55" s="9">
-        <f>_xll.qlBondCleanPrice2(C34,C54,"actual360","continuous")</f>
-        <v>98.911947709487364</v>
+        <v>2.9888064241409308E-2</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B56" s="9">
-        <f>_xll.qlBondDirtyPrice(B34)</f>
-        <v>99.098870926418101</v>
+        <f>_xll.qlBondCleanPrice2(B34,B55,"actual360","continuous")</f>
+        <v>99.710819325044909</v>
       </c>
       <c r="C56" s="9">
-        <f>_xll.qlBondDirtyPrice(C34)</f>
-        <v>99.098870926418101</v>
+        <f>_xll.qlBondCleanPrice2(C34,C55,"actual360","continuous")</f>
+        <v>99.710819325044909</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B57" s="9">
-        <f>_xll.qlBondDirtyPrice2(B34,B54,"actual360","CONTINUOUS","annual")</f>
-        <v>99.098869912012361</v>
+        <f>_xll.qlBondDirtyPrice(B34)</f>
+        <v>99.727682727697726</v>
       </c>
       <c r="C57" s="9">
-        <f>_xll.qlBondDirtyPrice2(C34,C54,"actual360","CONTINUOUS","annual")</f>
-        <v>99.098869912012361</v>
+        <f>_xll.qlBondDirtyPrice(C34)</f>
+        <v>99.727682727697726</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" s="9">
+        <f>_xll.qlBondDirtyPrice2(B34,B55,"actual360","CONTINUOUS","annual")</f>
+        <v>99.727679354051261</v>
+      </c>
+      <c r="C58" s="9">
+        <f>_xll.qlBondDirtyPrice2(C34,C55,"actual360","CONTINUOUS","annual")</f>
+        <v>99.727679354051261</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B59" s="9">
         <f>_xll.qlBondYield(B34,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
-      </c>
-      <c r="C58" s="9">
+        <v>2.9888064241409308E-2</v>
+      </c>
+      <c r="C59" s="9">
         <f>_xll.qlBondYield(C34,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="10" t="s">
+        <v>2.9888064241409308E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B59" s="9" t="str">
-        <f>_xll.qlBondPrice(B53,"clean")</f>
-        <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R59C2BondPrice,A</v>
-      </c>
-      <c r="C59" s="9" t="str">
-        <f>_xll.qlBondPrice(C53,"clean")</f>
-        <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R59C3BondPrice,A</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
+      <c r="B60" s="9" t="str">
+        <f>_xll.qlBondPrice(B54,"clean")</f>
+        <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R60C2BondPrice,A</v>
+      </c>
+      <c r="C60" s="9" t="str">
+        <f>_xll.qlBondPrice(C54,"clean")</f>
+        <v>欣[test_bonds.xlsx]AmortizingFloatingRateBond!R60C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B60" s="9">
-        <f>_xll.qlBondYield2(B34,B59,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28991034966766843</v>
-      </c>
-      <c r="C60" s="9">
-        <f>_xll.qlBondYield2(C34,C59,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28991034966766843</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="10" t="s">
+      <c r="B61" s="9">
+        <f>_xll.qlBondYield2(B34,B60,"actual360","CONTINUOUS","annual")</f>
+        <v>2.991248164176942E-2</v>
+      </c>
+      <c r="C61" s="9">
+        <f>_xll.qlBondYield2(C34,C60,"actual360","CONTINUOUS","annual")</f>
+        <v>2.991248164176942E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B62" s="2">
         <v>45667</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C62" s="2">
         <v>45667</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="9">
-        <f>_xll.qlBondAccruedAmount(B34,B61)</f>
-        <v>0.18692220252499714</v>
-      </c>
-      <c r="C62" s="9">
-        <f>_xll.qlBondAccruedAmount(C34,C61)</f>
-        <v>0.18692220252499714</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B63" s="9">
-        <f>_xll.qlBondSettlementValue(B34)</f>
-        <v>148.64830638962715</v>
+        <f>_xll.qlBondAccruedAmount(B34,B62)</f>
+        <v>1.6860029006353104E-2</v>
       </c>
       <c r="C63" s="9">
-        <f>_xll.qlBondSettlementValue(C34)</f>
-        <v>148.64830638962715</v>
+        <f>_xll.qlBondAccruedAmount(C34,C62)</f>
+        <v>1.6860029006353104E-2</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B64" s="9">
+        <f>_xll.qlBondSettlementValue(B34)</f>
+        <v>149.59152409154657</v>
+      </c>
+      <c r="C64" s="9">
+        <f>_xll.qlBondSettlementValue(C34)</f>
+        <v>149.59152409154657</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B64" s="9">
-        <f>_xll.qlBondSettlementValue2(B34,B53)</f>
-        <v>148.64830638962715</v>
-      </c>
-      <c r="C64" s="9">
-        <f>_xll.qlBondSettlementValue2(C34,C53)</f>
-        <v>148.64830638962715</v>
+      <c r="B65" s="9">
+        <f>_xll.qlBondSettlementValue2(B34,B54)</f>
+        <v>149.5915240915466</v>
+      </c>
+      <c r="C65" s="9">
+        <f>_xll.qlBondSettlementValue2(C34,C54)</f>
+        <v>149.5915240915466</v>
       </c>
     </row>
   </sheetData>
@@ -7215,7 +7206,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05025377-E5EA-48F0-BE68-1C47A2C5C8E6}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.28515625" customWidth="1"/>
@@ -7370,11 +7361,11 @@
         <v>55</v>
       </c>
       <c r="B15" s="14" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R15C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C15" s="14" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R15C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -7520,11 +7511,11 @@
       </c>
       <c r="B32" s="3">
         <f>_xll.qlBondNextCouponRate(B31)</f>
-        <v>0.33645996454499488</v>
+        <v>3.0348052211435581E-2</v>
       </c>
       <c r="C32" s="3">
         <f>_xll.qlBondNextCouponRate(C31)</f>
-        <v>0.33645996454499488</v>
+        <v>3.0348052211435581E-2</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -7727,177 +7718,190 @@
         <v>55</v>
       </c>
       <c r="B48" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R48C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C48" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R48C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="B49" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(B31,B48)</f>
+        <f>_xll.qlDiscountingBondEngine(B48)</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R49C2DiscountingBondEngine,A</v>
       </c>
       <c r="C49" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(C31,C48)</f>
+        <f>_xll.qlDiscountingBondEngine(C48)</f>
         <v>欣[test_bonds.xlsx]FloatingRateBond!R49C3DiscountingBondEngine,A</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B50" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(B31,B49)</f>
+        <v>1</v>
+      </c>
+      <c r="C50" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(C31,C49)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B51" s="9">
         <f>_xll.qlBondCleanPrice(B31)</f>
-        <v>98.609796527032515</v>
-      </c>
-      <c r="C50" s="9">
+        <v>99.596604611054204</v>
+      </c>
+      <c r="C51" s="9">
         <f>_xll.qlBondCleanPrice(C31)</f>
-        <v>98.609796527032515</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="10" t="s">
+        <v>99.596604611054204</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B51" s="9">
-        <v>0.28928264971926221</v>
-      </c>
-      <c r="C51" s="9">
-        <v>0.28928264971926221</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="B52" s="9">
-        <f>_xll.qlBondCleanPrice2(B31,B51,"actual360","continuous")</f>
-        <v>98.60979524053667</v>
+        <v>2.9888064241409308E-2</v>
       </c>
       <c r="C52" s="9">
-        <f>_xll.qlBondCleanPrice2(C31,C51,"actual360","continuous")</f>
-        <v>98.60979524053667</v>
+        <v>2.9888064241409308E-2</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B53" s="9">
-        <f>_xll.qlBondDirtyPrice(B31)</f>
-        <v>98.796718729557512</v>
+        <f>_xll.qlBondCleanPrice2(B31,B52,"actual360","continuous")</f>
+        <v>99.596599916978278</v>
       </c>
       <c r="C53" s="9">
-        <f>_xll.qlBondDirtyPrice(C31)</f>
-        <v>98.796718729557512</v>
+        <f>_xll.qlBondCleanPrice2(C31,C52,"actual360","continuous")</f>
+        <v>99.596599916978278</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B54" s="9">
-        <f>_xll.qlBondDirtyPrice2(B31,B51,"actual360","CONTINUOUS","annual")</f>
-        <v>98.796717443061667</v>
+        <f>_xll.qlBondDirtyPrice(B31)</f>
+        <v>99.613464640060556</v>
       </c>
       <c r="C54" s="9">
-        <f>_xll.qlBondDirtyPrice2(C31,C51,"actual360","CONTINUOUS","annual")</f>
-        <v>98.796717443061667</v>
+        <f>_xll.qlBondDirtyPrice(C31)</f>
+        <v>99.613464640060556</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" s="9">
+        <f>_xll.qlBondDirtyPrice2(B31,B52,"actual360","CONTINUOUS","annual")</f>
+        <v>99.61345994598463</v>
+      </c>
+      <c r="C55" s="9">
+        <f>_xll.qlBondDirtyPrice2(C31,C52,"actual360","CONTINUOUS","annual")</f>
+        <v>99.61345994598463</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B56" s="9">
         <f>_xll.qlBondYield(B31,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
-      </c>
-      <c r="C55" s="9">
+        <v>2.9888064241409308E-2</v>
+      </c>
+      <c r="C56" s="9">
         <f>_xll.qlBondYield(C31,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="10" t="s">
+        <v>2.9888064241409308E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B56" s="9" t="str">
-        <f>_xll.qlBondPrice(B50,"clean")</f>
-        <v>欣[test_bonds.xlsx]FloatingRateBond!R56C2BondPrice,A</v>
-      </c>
-      <c r="C56" s="9" t="str">
-        <f>_xll.qlBondPrice(C50,"clean")</f>
-        <v>欣[test_bonds.xlsx]FloatingRateBond!R56C3BondPrice,A</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
+      <c r="B57" s="9" t="str">
+        <f>_xll.qlBondPrice(B51,"clean")</f>
+        <v>欣[test_bonds.xlsx]FloatingRateBond!R57C2BondPrice,A</v>
+      </c>
+      <c r="C57" s="9" t="str">
+        <f>_xll.qlBondPrice(C51,"clean")</f>
+        <v>欣[test_bonds.xlsx]FloatingRateBond!R57C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B57" s="9">
-        <f>_xll.qlBondYield2(B31,B56,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28977749412491322</v>
-      </c>
-      <c r="C57" s="9">
-        <f>_xll.qlBondYield2(C31,C56,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28977749412491322</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="10" t="s">
+      <c r="B58" s="9">
+        <f>_xll.qlBondYield2(B31,B57,"actual360","CONTINUOUS","annual")</f>
+        <v>2.990561575889588E-2</v>
+      </c>
+      <c r="C58" s="9">
+        <f>_xll.qlBondYield2(C31,C57,"actual360","CONTINUOUS","annual")</f>
+        <v>2.990561575889588E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B59" s="2">
         <v>45667</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C59" s="2">
         <v>45667</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="9">
-        <f>_xll.qlBondAccruedAmount(B31,B58)</f>
-        <v>0.18692220252499717</v>
-      </c>
-      <c r="C59" s="9">
-        <f>_xll.qlBondAccruedAmount(C31,C58)</f>
-        <v>0.18692220252499717</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B60" s="9">
-        <f>_xll.qlBondSettlementValue(B31)</f>
-        <v>98.796718729557512</v>
+        <f>_xll.qlBondAccruedAmount(B31,B59)</f>
+        <v>1.6860029006353101E-2</v>
       </c>
       <c r="C60" s="9">
-        <f>_xll.qlBondSettlementValue(C31)</f>
-        <v>98.796718729557512</v>
+        <f>_xll.qlBondAccruedAmount(C31,C59)</f>
+        <v>1.6860029006353101E-2</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" s="9">
+        <f>_xll.qlBondSettlementValue(B31)</f>
+        <v>99.613464640060556</v>
+      </c>
+      <c r="C61" s="9">
+        <f>_xll.qlBondSettlementValue(C31)</f>
+        <v>99.613464640060556</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B61" s="9">
-        <f>_xll.qlBondSettlementValue2(B31,B50)</f>
-        <v>98.796718729557512</v>
-      </c>
-      <c r="C61" s="9">
-        <f>_xll.qlBondSettlementValue2(C31,C50)</f>
-        <v>98.796718729557512</v>
+      <c r="B62" s="9">
+        <f>_xll.qlBondSettlementValue2(B31,B51)</f>
+        <v>99.613464640060556</v>
+      </c>
+      <c r="C62" s="9">
+        <f>_xll.qlBondSettlementValue2(C31,C51)</f>
+        <v>99.613464640060556</v>
       </c>
     </row>
   </sheetData>
@@ -7907,7 +7911,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27515A30-3B44-433D-8DBF-ACC4ED7765FD}">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.140625" customWidth="1"/>
@@ -8246,7 +8250,7 @@
         <v>93</v>
       </c>
       <c r="B31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" s="3">
         <v>0</v>
@@ -8257,7 +8261,7 @@
         <v>94</v>
       </c>
       <c r="B32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" s="3">
         <v>0</v>
@@ -8306,7 +8310,7 @@
       </c>
       <c r="B37" s="3">
         <f>_xll.qlBondNextCouponRate(B36)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" s="3">
         <f>_xll.qlBondNextCouponRate(C36)</f>
@@ -8513,177 +8517,190 @@
         <v>55</v>
       </c>
       <c r="B53" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]CmsRateBond!R53C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C53" s="3" t="str">
-        <f>_xll.qlFlatForward(#REF!,0.3,"actual360","compounded","Quarterly")</f>
+        <f>_xll.qlFlatForward(#REF!,0.03,"actual360","compounded","Quarterly")</f>
         <v>欣[test_bonds.xlsx]CmsRateBond!R53C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="B54" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(B36,B53)</f>
+        <f>_xll.qlDiscountingBondEngine(B53)</f>
         <v>欣[test_bonds.xlsx]CmsRateBond!R54C2DiscountingBondEngine,A</v>
       </c>
       <c r="C54" s="3" t="str">
-        <f>_xll.qlBondSetDiscountingEngine(C36,C53)</f>
+        <f>_xll.qlDiscountingBondEngine(C53)</f>
         <v>欣[test_bonds.xlsx]CmsRateBond!R54C3DiscountingBondEngine,A</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B55" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(B36,B54)</f>
+        <v>1</v>
+      </c>
+      <c r="C55" s="3" t="b">
+        <f>_xll.qlInstrumentSetPricingEngine(C36,C54)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B56" s="9">
         <f>_xll.qlBondCleanPrice(B36)</f>
-        <v>285.41003697223789</v>
-      </c>
-      <c r="C55" s="9">
+        <v>71.653019933502407</v>
+      </c>
+      <c r="C56" s="9">
         <f>_xll.qlBondCleanPrice(C36)</f>
-        <v>4.7644717638374612</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="10" t="s">
+        <v>85.983623920202888</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="9">
-        <v>0.28928264971926221</v>
-      </c>
-      <c r="C56" s="9">
-        <v>0.28928264971926221</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="B57" s="9">
-        <f>_xll.qlBondCleanPrice2(B36,B56,"actual360","continuous")</f>
-        <v>285.4100334433362</v>
+        <v>2.9888064241409308E-2</v>
       </c>
       <c r="C57" s="9">
-        <f>_xll.qlBondCleanPrice2(C36,C56,"actual360","continuous")</f>
-        <v>4.7644715831310851</v>
+        <v>2.9888064241409308E-2</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B58" s="9">
-        <f>_xll.qlBondDirtyPrice(B36)</f>
-        <v>285.96559252779343</v>
+        <f>_xll.qlBondCleanPrice2(B36,B57,"actual360","continuous")</f>
+        <v>71.653016028468727</v>
       </c>
       <c r="C58" s="9">
-        <f>_xll.qlBondDirtyPrice(C36)</f>
-        <v>4.7644717638374612</v>
+        <f>_xll.qlBondCleanPrice2(C36,C57,"actual360","continuous")</f>
+        <v>85.983619234162475</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B59" s="9">
-        <f>_xll.qlBondDirtyPrice2(B36,B56,"actual360","CONTINUOUS","annual")</f>
-        <v>285.96558899889175</v>
+        <f>_xll.qlBondDirtyPrice(B36)</f>
+        <v>71.653019933502407</v>
       </c>
       <c r="C59" s="9">
-        <f>_xll.qlBondDirtyPrice2(C36,C56,"actual360","CONTINUOUS","annual")</f>
-        <v>4.7644715831310851</v>
+        <f>_xll.qlBondDirtyPrice(C36)</f>
+        <v>85.983623920202888</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" s="9">
+        <f>_xll.qlBondDirtyPrice2(B36,B57,"actual360","CONTINUOUS","annual")</f>
+        <v>71.653016028468727</v>
+      </c>
+      <c r="C60" s="9">
+        <f>_xll.qlBondDirtyPrice2(C36,C57,"actual360","CONTINUOUS","annual")</f>
+        <v>85.983619234162475</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B61" s="9">
         <f>_xll.qlBondYield(B36,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264971926221</v>
-      </c>
-      <c r="C60" s="9">
+        <v>2.9888064241409308E-2</v>
+      </c>
+      <c r="C61" s="9">
         <f>_xll.qlBondYield(C36,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264788123847</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="10" t="s">
+        <v>2.9888064241409308E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B61" s="9" t="str">
-        <f>_xll.qlBondPrice(B55,"clean")</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R61C2BondPrice,A</v>
-      </c>
-      <c r="C61" s="9" t="str">
-        <f>_xll.qlBondPrice(C55,"clean")</f>
-        <v>欣[test_bonds.xlsx]CmsRateBond!R61C3BondPrice,A</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
+      <c r="B62" s="9" t="str">
+        <f>_xll.qlBondPrice(B56,"clean")</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R62C2BondPrice,A</v>
+      </c>
+      <c r="C62" s="9" t="str">
+        <f>_xll.qlBondPrice(C56,"clean")</f>
+        <v>欣[test_bonds.xlsx]CmsRateBond!R62C3BondPrice,A</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="9">
-        <f>_xll.qlBondYield2(B36,B61,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28981883443572526</v>
-      </c>
-      <c r="C62" s="9">
-        <f>_xll.qlBondYield2(C36,C61,"actual360","CONTINUOUS","annual")</f>
-        <v>0.28928264788123847</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="10" t="s">
+      <c r="B63" s="9">
+        <f>_xll.qlBondYield2(B36,B62,"actual360","CONTINUOUS","annual")</f>
+        <v>2.9888064241409308E-2</v>
+      </c>
+      <c r="C63" s="9">
+        <f>_xll.qlBondYield2(C36,C62,"actual360","CONTINUOUS","annual")</f>
+        <v>2.9888064241409308E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B64" s="2">
         <v>45667</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C64" s="2">
         <v>45667</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="9">
-        <f>_xll.qlBondAccruedAmount(B36,B63)</f>
-        <v>0.55555555555555358</v>
-      </c>
-      <c r="C64" s="9">
-        <f>_xll.qlBondAccruedAmount(C36,C63)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B65" s="9">
-        <f>_xll.qlBondSettlementValue(B36)</f>
-        <v>285.96559252779343</v>
+        <f>_xll.qlBondAccruedAmount(B36,B64)</f>
+        <v>0</v>
       </c>
       <c r="C65" s="9">
-        <f>_xll.qlBondSettlementValue(C36)</f>
-        <v>4.7644717638374612</v>
+        <f>_xll.qlBondAccruedAmount(C36,C64)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="9">
+        <f>_xll.qlBondSettlementValue(B36)</f>
+        <v>71.653019933502407</v>
+      </c>
+      <c r="C66" s="9">
+        <f>_xll.qlBondSettlementValue(C36)</f>
+        <v>85.983623920202874</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B66" s="9">
-        <f>_xll.qlBondSettlementValue2(B36,B55)</f>
-        <v>285.96559252779343</v>
-      </c>
-      <c r="C66" s="9">
-        <f>_xll.qlBondSettlementValue2(C36,C55)</f>
-        <v>4.7644717638374612</v>
+      <c r="B67" s="9">
+        <f>_xll.qlBondSettlementValue2(B36,B56)</f>
+        <v>71.653019933502407</v>
+      </c>
+      <c r="C67" s="9">
+        <f>_xll.qlBondSettlementValue2(C36,C56)</f>
+        <v>85.983623920202888</v>
       </c>
     </row>
   </sheetData>
